--- a/data/review/rank_review.xlsx
+++ b/data/review/rank_review.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Review'!$A$1:$T$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Review'!$A$1:$U$140</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T140"/>
+  <dimension ref="A1:U140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -502,12 +502,13 @@
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -583,30 +584,35 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>ORCID (if shown)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Where you saw it</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>person_id</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>affiliation_id</t>
         </is>
@@ -663,16 +669,17 @@
       </c>
       <c r="M2" s="6" t="n"/>
       <c r="N2" s="6" t="n"/>
-      <c r="O2" s="7" t="n"/>
-      <c r="P2" s="6" t="n"/>
+      <c r="O2" s="6" t="n"/>
+      <c r="P2" s="7" t="n"/>
       <c r="Q2" s="6" t="n"/>
-      <c r="R2" s="7" t="n"/>
-      <c r="S2" s="3" t="inlineStr">
+      <c r="R2" s="6" t="n"/>
+      <c r="S2" s="7" t="n"/>
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -729,16 +736,17 @@
       </c>
       <c r="M3" s="6" t="n"/>
       <c r="N3" s="6" t="n"/>
-      <c r="O3" s="7" t="n"/>
-      <c r="P3" s="6" t="n"/>
+      <c r="O3" s="6" t="n"/>
+      <c r="P3" s="7" t="n"/>
       <c r="Q3" s="6" t="n"/>
-      <c r="R3" s="7" t="n"/>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="R3" s="6" t="n"/>
+      <c r="S3" s="7" t="n"/>
+      <c r="T3" s="3" t="inlineStr">
         <is>
           <t>169</t>
         </is>
       </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="U3" s="3" t="inlineStr">
         <is>
           <t>170</t>
         </is>
@@ -795,16 +803,17 @@
       </c>
       <c r="M4" s="6" t="n"/>
       <c r="N4" s="6" t="n"/>
-      <c r="O4" s="7" t="n"/>
-      <c r="P4" s="6" t="n"/>
+      <c r="O4" s="6" t="n"/>
+      <c r="P4" s="7" t="n"/>
       <c r="Q4" s="6" t="n"/>
-      <c r="R4" s="7" t="n"/>
-      <c r="S4" s="3" t="inlineStr">
+      <c r="R4" s="6" t="n"/>
+      <c r="S4" s="7" t="n"/>
+      <c r="T4" s="3" t="inlineStr">
         <is>
           <t>806</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>808</t>
         </is>
@@ -861,16 +870,17 @@
       </c>
       <c r="M5" s="6" t="n"/>
       <c r="N5" s="6" t="n"/>
-      <c r="O5" s="7" t="n"/>
-      <c r="P5" s="6" t="n"/>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="7" t="n"/>
       <c r="Q5" s="6" t="n"/>
-      <c r="R5" s="7" t="n"/>
-      <c r="S5" s="3" t="inlineStr">
+      <c r="R5" s="6" t="n"/>
+      <c r="S5" s="7" t="n"/>
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>797</t>
         </is>
       </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>798</t>
         </is>
@@ -927,16 +937,17 @@
       </c>
       <c r="M6" s="6" t="n"/>
       <c r="N6" s="6" t="n"/>
-      <c r="O6" s="7" t="n"/>
-      <c r="P6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="7" t="n"/>
       <c r="Q6" s="6" t="n"/>
-      <c r="R6" s="7" t="n"/>
-      <c r="S6" s="3" t="inlineStr">
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="7" t="n"/>
+      <c r="T6" s="3" t="inlineStr">
         <is>
           <t>1029</t>
         </is>
       </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="U6" s="3" t="inlineStr">
         <is>
           <t>1031</t>
         </is>
@@ -997,16 +1008,17 @@
       </c>
       <c r="M7" s="6" t="n"/>
       <c r="N7" s="6" t="n"/>
-      <c r="O7" s="7" t="n"/>
-      <c r="P7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="7" t="n"/>
       <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="7" t="n"/>
-      <c r="S7" s="3" t="inlineStr">
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="7" t="n"/>
+      <c r="T7" s="3" t="inlineStr">
         <is>
           <t>645</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="U7" s="3" t="inlineStr">
         <is>
           <t>646</t>
         </is>
@@ -1067,16 +1079,17 @@
       </c>
       <c r="M8" s="6" t="n"/>
       <c r="N8" s="6" t="n"/>
-      <c r="O8" s="7" t="n"/>
-      <c r="P8" s="6" t="n"/>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="7" t="n"/>
       <c r="Q8" s="6" t="n"/>
-      <c r="R8" s="7" t="n"/>
-      <c r="S8" s="3" t="inlineStr">
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="7" t="n"/>
+      <c r="T8" s="3" t="inlineStr">
         <is>
           <t>888</t>
         </is>
       </c>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="U8" s="3" t="inlineStr">
         <is>
           <t>890</t>
         </is>
@@ -1137,16 +1150,17 @@
       </c>
       <c r="M9" s="6" t="n"/>
       <c r="N9" s="6" t="n"/>
-      <c r="O9" s="7" t="n"/>
-      <c r="P9" s="6" t="n"/>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="7" t="n"/>
       <c r="Q9" s="6" t="n"/>
-      <c r="R9" s="7" t="n"/>
-      <c r="S9" s="3" t="inlineStr">
+      <c r="R9" s="6" t="n"/>
+      <c r="S9" s="7" t="n"/>
+      <c r="T9" s="3" t="inlineStr">
         <is>
           <t>749</t>
         </is>
       </c>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="U9" s="3" t="inlineStr">
         <is>
           <t>750</t>
         </is>
@@ -1207,16 +1221,17 @@
       </c>
       <c r="M10" s="6" t="n"/>
       <c r="N10" s="6" t="n"/>
-      <c r="O10" s="7" t="n"/>
-      <c r="P10" s="6" t="n"/>
+      <c r="O10" s="6" t="n"/>
+      <c r="P10" s="7" t="n"/>
       <c r="Q10" s="6" t="n"/>
-      <c r="R10" s="7" t="n"/>
-      <c r="S10" s="3" t="inlineStr">
+      <c r="R10" s="6" t="n"/>
+      <c r="S10" s="7" t="n"/>
+      <c r="T10" s="3" t="inlineStr">
         <is>
           <t>214</t>
         </is>
       </c>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="U10" s="3" t="inlineStr">
         <is>
           <t>215</t>
         </is>
@@ -1277,16 +1292,17 @@
       </c>
       <c r="M11" s="6" t="n"/>
       <c r="N11" s="6" t="n"/>
-      <c r="O11" s="7" t="n"/>
-      <c r="P11" s="6" t="n"/>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="7" t="n"/>
       <c r="Q11" s="6" t="n"/>
-      <c r="R11" s="7" t="n"/>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="R11" s="6" t="n"/>
+      <c r="S11" s="7" t="n"/>
+      <c r="T11" s="3" t="inlineStr">
         <is>
           <t>626</t>
         </is>
       </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="U11" s="3" t="inlineStr">
         <is>
           <t>627</t>
         </is>
@@ -1347,16 +1363,17 @@
       </c>
       <c r="M12" s="6" t="n"/>
       <c r="N12" s="6" t="n"/>
-      <c r="O12" s="7" t="n"/>
-      <c r="P12" s="6" t="n"/>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="7" t="n"/>
       <c r="Q12" s="6" t="n"/>
-      <c r="R12" s="7" t="n"/>
-      <c r="S12" s="3" t="inlineStr">
+      <c r="R12" s="6" t="n"/>
+      <c r="S12" s="7" t="n"/>
+      <c r="T12" s="3" t="inlineStr">
         <is>
           <t>936</t>
         </is>
       </c>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="U12" s="3" t="inlineStr">
         <is>
           <t>938</t>
         </is>
@@ -1417,16 +1434,17 @@
       </c>
       <c r="M13" s="6" t="n"/>
       <c r="N13" s="6" t="n"/>
-      <c r="O13" s="7" t="n"/>
-      <c r="P13" s="6" t="n"/>
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="7" t="n"/>
       <c r="Q13" s="6" t="n"/>
-      <c r="R13" s="7" t="n"/>
-      <c r="S13" s="3" t="inlineStr">
+      <c r="R13" s="6" t="n"/>
+      <c r="S13" s="7" t="n"/>
+      <c r="T13" s="3" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t>537</t>
         </is>
@@ -1487,16 +1505,17 @@
       </c>
       <c r="M14" s="6" t="n"/>
       <c r="N14" s="6" t="n"/>
-      <c r="O14" s="7" t="n"/>
-      <c r="P14" s="6" t="n"/>
+      <c r="O14" s="6" t="n"/>
+      <c r="P14" s="7" t="n"/>
       <c r="Q14" s="6" t="n"/>
-      <c r="R14" s="7" t="n"/>
-      <c r="S14" s="3" t="inlineStr">
+      <c r="R14" s="6" t="n"/>
+      <c r="S14" s="7" t="n"/>
+      <c r="T14" s="3" t="inlineStr">
         <is>
           <t>892</t>
         </is>
       </c>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="U14" s="3" t="inlineStr">
         <is>
           <t>894</t>
         </is>
@@ -1557,16 +1576,17 @@
       </c>
       <c r="M15" s="6" t="n"/>
       <c r="N15" s="6" t="n"/>
-      <c r="O15" s="7" t="n"/>
-      <c r="P15" s="6" t="n"/>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="7" t="n"/>
       <c r="Q15" s="6" t="n"/>
-      <c r="R15" s="7" t="n"/>
-      <c r="S15" s="3" t="inlineStr">
+      <c r="R15" s="6" t="n"/>
+      <c r="S15" s="7" t="n"/>
+      <c r="T15" s="3" t="inlineStr">
         <is>
           <t>743</t>
         </is>
       </c>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="U15" s="3" t="inlineStr">
         <is>
           <t>744</t>
         </is>
@@ -1627,16 +1647,17 @@
       </c>
       <c r="M16" s="6" t="n"/>
       <c r="N16" s="6" t="n"/>
-      <c r="O16" s="7" t="n"/>
-      <c r="P16" s="6" t="n"/>
+      <c r="O16" s="6" t="n"/>
+      <c r="P16" s="7" t="n"/>
       <c r="Q16" s="6" t="n"/>
-      <c r="R16" s="7" t="n"/>
-      <c r="S16" s="3" t="inlineStr">
+      <c r="R16" s="6" t="n"/>
+      <c r="S16" s="7" t="n"/>
+      <c r="T16" s="3" t="inlineStr">
         <is>
           <t>140</t>
         </is>
       </c>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="U16" s="3" t="inlineStr">
         <is>
           <t>141</t>
         </is>
@@ -1697,16 +1718,17 @@
       </c>
       <c r="M17" s="6" t="n"/>
       <c r="N17" s="6" t="n"/>
-      <c r="O17" s="7" t="n"/>
-      <c r="P17" s="6" t="n"/>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="7" t="n"/>
       <c r="Q17" s="6" t="n"/>
-      <c r="R17" s="7" t="n"/>
-      <c r="S17" s="3" t="inlineStr">
+      <c r="R17" s="6" t="n"/>
+      <c r="S17" s="7" t="n"/>
+      <c r="T17" s="3" t="inlineStr">
         <is>
           <t>696</t>
         </is>
       </c>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t>697</t>
         </is>
@@ -1767,16 +1789,17 @@
       </c>
       <c r="M18" s="6" t="n"/>
       <c r="N18" s="6" t="n"/>
-      <c r="O18" s="7" t="n"/>
-      <c r="P18" s="6" t="n"/>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="7" t="n"/>
       <c r="Q18" s="6" t="n"/>
-      <c r="R18" s="7" t="n"/>
-      <c r="S18" s="3" t="inlineStr">
+      <c r="R18" s="6" t="n"/>
+      <c r="S18" s="7" t="n"/>
+      <c r="T18" s="3" t="inlineStr">
         <is>
           <t>643</t>
         </is>
       </c>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="U18" s="3" t="inlineStr">
         <is>
           <t>644</t>
         </is>
@@ -1833,16 +1856,17 @@
       </c>
       <c r="M19" s="6" t="n"/>
       <c r="N19" s="6" t="n"/>
-      <c r="O19" s="7" t="n"/>
-      <c r="P19" s="6" t="n"/>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="7" t="n"/>
       <c r="Q19" s="6" t="n"/>
-      <c r="R19" s="7" t="n"/>
-      <c r="S19" s="3" t="inlineStr">
+      <c r="R19" s="6" t="n"/>
+      <c r="S19" s="7" t="n"/>
+      <c r="T19" s="3" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="T19" s="3" t="inlineStr">
+      <c r="U19" s="3" t="inlineStr">
         <is>
           <t>647</t>
         </is>
@@ -1903,16 +1927,17 @@
       </c>
       <c r="M20" s="6" t="n"/>
       <c r="N20" s="6" t="n"/>
-      <c r="O20" s="7" t="n"/>
-      <c r="P20" s="6" t="n"/>
+      <c r="O20" s="6" t="n"/>
+      <c r="P20" s="7" t="n"/>
       <c r="Q20" s="6" t="n"/>
-      <c r="R20" s="7" t="n"/>
-      <c r="S20" s="3" t="inlineStr">
+      <c r="R20" s="6" t="n"/>
+      <c r="S20" s="7" t="n"/>
+      <c r="T20" s="3" t="inlineStr">
         <is>
           <t>520</t>
         </is>
       </c>
-      <c r="T20" s="3" t="inlineStr">
+      <c r="U20" s="3" t="inlineStr">
         <is>
           <t>521</t>
         </is>
@@ -1969,16 +1994,17 @@
       </c>
       <c r="M21" s="6" t="n"/>
       <c r="N21" s="6" t="n"/>
-      <c r="O21" s="7" t="n"/>
-      <c r="P21" s="6" t="n"/>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="7" t="n"/>
       <c r="Q21" s="6" t="n"/>
-      <c r="R21" s="7" t="n"/>
-      <c r="S21" s="3" t="inlineStr">
+      <c r="R21" s="6" t="n"/>
+      <c r="S21" s="7" t="n"/>
+      <c r="T21" s="3" t="inlineStr">
         <is>
           <t>374</t>
         </is>
       </c>
-      <c r="T21" s="3" t="inlineStr">
+      <c r="U21" s="3" t="inlineStr">
         <is>
           <t>375</t>
         </is>
@@ -2035,16 +2061,17 @@
       </c>
       <c r="M22" s="6" t="n"/>
       <c r="N22" s="6" t="n"/>
-      <c r="O22" s="7" t="n"/>
-      <c r="P22" s="6" t="n"/>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="7" t="n"/>
       <c r="Q22" s="6" t="n"/>
-      <c r="R22" s="7" t="n"/>
-      <c r="S22" s="3" t="inlineStr">
+      <c r="R22" s="6" t="n"/>
+      <c r="S22" s="7" t="n"/>
+      <c r="T22" s="3" t="inlineStr">
         <is>
           <t>878</t>
         </is>
       </c>
-      <c r="T22" s="3" t="inlineStr">
+      <c r="U22" s="3" t="inlineStr">
         <is>
           <t>880</t>
         </is>
@@ -2105,16 +2132,17 @@
       </c>
       <c r="M23" s="6" t="n"/>
       <c r="N23" s="6" t="n"/>
-      <c r="O23" s="7" t="n"/>
-      <c r="P23" s="6" t="n"/>
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="7" t="n"/>
       <c r="Q23" s="6" t="n"/>
-      <c r="R23" s="7" t="n"/>
-      <c r="S23" s="3" t="inlineStr">
+      <c r="R23" s="6" t="n"/>
+      <c r="S23" s="7" t="n"/>
+      <c r="T23" s="3" t="inlineStr">
         <is>
           <t>541</t>
         </is>
       </c>
-      <c r="T23" s="3" t="inlineStr">
+      <c r="U23" s="3" t="inlineStr">
         <is>
           <t>542</t>
         </is>
@@ -2175,16 +2203,17 @@
       </c>
       <c r="M24" s="6" t="n"/>
       <c r="N24" s="6" t="n"/>
-      <c r="O24" s="7" t="n"/>
-      <c r="P24" s="6" t="n"/>
+      <c r="O24" s="6" t="n"/>
+      <c r="P24" s="7" t="n"/>
       <c r="Q24" s="6" t="n"/>
-      <c r="R24" s="7" t="n"/>
-      <c r="S24" s="3" t="inlineStr">
+      <c r="R24" s="6" t="n"/>
+      <c r="S24" s="7" t="n"/>
+      <c r="T24" s="3" t="inlineStr">
         <is>
           <t>243</t>
         </is>
       </c>
-      <c r="T24" s="3" t="inlineStr">
+      <c r="U24" s="3" t="inlineStr">
         <is>
           <t>244</t>
         </is>
@@ -2245,16 +2274,17 @@
       </c>
       <c r="M25" s="6" t="n"/>
       <c r="N25" s="6" t="n"/>
-      <c r="O25" s="7" t="n"/>
-      <c r="P25" s="6" t="n"/>
+      <c r="O25" s="6" t="n"/>
+      <c r="P25" s="7" t="n"/>
       <c r="Q25" s="6" t="n"/>
-      <c r="R25" s="7" t="n"/>
-      <c r="S25" s="3" t="inlineStr">
+      <c r="R25" s="6" t="n"/>
+      <c r="S25" s="7" t="n"/>
+      <c r="T25" s="3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="T25" s="3" t="inlineStr">
+      <c r="U25" s="3" t="inlineStr">
         <is>
           <t>947</t>
         </is>
@@ -2315,16 +2345,17 @@
       </c>
       <c r="M26" s="6" t="n"/>
       <c r="N26" s="6" t="n"/>
-      <c r="O26" s="7" t="n"/>
-      <c r="P26" s="6" t="n"/>
+      <c r="O26" s="6" t="n"/>
+      <c r="P26" s="7" t="n"/>
       <c r="Q26" s="6" t="n"/>
-      <c r="R26" s="7" t="n"/>
-      <c r="S26" s="3" t="inlineStr">
+      <c r="R26" s="6" t="n"/>
+      <c r="S26" s="7" t="n"/>
+      <c r="T26" s="3" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="T26" s="3" t="inlineStr">
+      <c r="U26" s="3" t="inlineStr">
         <is>
           <t>92</t>
         </is>
@@ -2385,16 +2416,17 @@
       </c>
       <c r="M27" s="6" t="n"/>
       <c r="N27" s="6" t="n"/>
-      <c r="O27" s="7" t="n"/>
-      <c r="P27" s="6" t="n"/>
+      <c r="O27" s="6" t="n"/>
+      <c r="P27" s="7" t="n"/>
       <c r="Q27" s="6" t="n"/>
-      <c r="R27" s="7" t="n"/>
-      <c r="S27" s="3" t="inlineStr">
+      <c r="R27" s="6" t="n"/>
+      <c r="S27" s="7" t="n"/>
+      <c r="T27" s="3" t="inlineStr">
         <is>
           <t>954</t>
         </is>
       </c>
-      <c r="T27" s="3" t="inlineStr">
+      <c r="U27" s="3" t="inlineStr">
         <is>
           <t>956</t>
         </is>
@@ -2451,16 +2483,17 @@
       </c>
       <c r="M28" s="6" t="n"/>
       <c r="N28" s="6" t="n"/>
-      <c r="O28" s="7" t="n"/>
-      <c r="P28" s="6" t="n"/>
+      <c r="O28" s="6" t="n"/>
+      <c r="P28" s="7" t="n"/>
       <c r="Q28" s="6" t="n"/>
-      <c r="R28" s="7" t="n"/>
-      <c r="S28" s="3" t="inlineStr">
+      <c r="R28" s="6" t="n"/>
+      <c r="S28" s="7" t="n"/>
+      <c r="T28" s="3" t="inlineStr">
         <is>
           <t>702</t>
         </is>
       </c>
-      <c r="T28" s="3" t="inlineStr">
+      <c r="U28" s="3" t="inlineStr">
         <is>
           <t>703</t>
         </is>
@@ -2521,16 +2554,17 @@
       </c>
       <c r="M29" s="6" t="n"/>
       <c r="N29" s="6" t="n"/>
-      <c r="O29" s="7" t="n"/>
-      <c r="P29" s="6" t="n"/>
+      <c r="O29" s="6" t="n"/>
+      <c r="P29" s="7" t="n"/>
       <c r="Q29" s="6" t="n"/>
-      <c r="R29" s="7" t="n"/>
-      <c r="S29" s="3" t="inlineStr">
+      <c r="R29" s="6" t="n"/>
+      <c r="S29" s="7" t="n"/>
+      <c r="T29" s="3" t="inlineStr">
         <is>
           <t>624</t>
         </is>
       </c>
-      <c r="T29" s="3" t="inlineStr">
+      <c r="U29" s="3" t="inlineStr">
         <is>
           <t>625</t>
         </is>
@@ -2591,16 +2625,17 @@
       </c>
       <c r="M30" s="12" t="n"/>
       <c r="N30" s="12" t="n"/>
-      <c r="O30" s="13" t="n"/>
-      <c r="P30" s="12" t="n"/>
+      <c r="O30" s="12" t="n"/>
+      <c r="P30" s="13" t="n"/>
       <c r="Q30" s="12" t="n"/>
-      <c r="R30" s="13" t="n"/>
-      <c r="S30" s="9" t="inlineStr">
+      <c r="R30" s="12" t="n"/>
+      <c r="S30" s="13" t="n"/>
+      <c r="T30" s="9" t="inlineStr">
         <is>
           <t>373</t>
         </is>
       </c>
-      <c r="T30" s="9" t="inlineStr">
+      <c r="U30" s="9" t="inlineStr">
         <is>
           <t>374</t>
         </is>
@@ -2657,16 +2692,17 @@
       </c>
       <c r="M31" s="6" t="n"/>
       <c r="N31" s="6" t="n"/>
-      <c r="O31" s="7" t="n"/>
-      <c r="P31" s="6" t="n"/>
+      <c r="O31" s="6" t="n"/>
+      <c r="P31" s="7" t="n"/>
       <c r="Q31" s="6" t="n"/>
-      <c r="R31" s="7" t="n"/>
-      <c r="S31" s="3" t="inlineStr">
+      <c r="R31" s="6" t="n"/>
+      <c r="S31" s="7" t="n"/>
+      <c r="T31" s="3" t="inlineStr">
         <is>
           <t>773</t>
         </is>
       </c>
-      <c r="T31" s="3" t="inlineStr">
+      <c r="U31" s="3" t="inlineStr">
         <is>
           <t>774</t>
         </is>
@@ -2727,16 +2763,17 @@
       </c>
       <c r="M32" s="6" t="n"/>
       <c r="N32" s="6" t="n"/>
-      <c r="O32" s="7" t="n"/>
-      <c r="P32" s="6" t="n"/>
+      <c r="O32" s="6" t="n"/>
+      <c r="P32" s="7" t="n"/>
       <c r="Q32" s="6" t="n"/>
-      <c r="R32" s="7" t="n"/>
-      <c r="S32" s="3" t="inlineStr">
+      <c r="R32" s="6" t="n"/>
+      <c r="S32" s="7" t="n"/>
+      <c r="T32" s="3" t="inlineStr">
         <is>
           <t>222</t>
         </is>
       </c>
-      <c r="T32" s="3" t="inlineStr">
+      <c r="U32" s="3" t="inlineStr">
         <is>
           <t>223</t>
         </is>
@@ -2797,16 +2834,17 @@
       </c>
       <c r="M33" s="6" t="n"/>
       <c r="N33" s="6" t="n"/>
-      <c r="O33" s="7" t="n"/>
-      <c r="P33" s="6" t="n"/>
+      <c r="O33" s="6" t="n"/>
+      <c r="P33" s="7" t="n"/>
       <c r="Q33" s="6" t="n"/>
-      <c r="R33" s="7" t="n"/>
-      <c r="S33" s="3" t="inlineStr">
+      <c r="R33" s="6" t="n"/>
+      <c r="S33" s="7" t="n"/>
+      <c r="T33" s="3" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="T33" s="3" t="inlineStr">
+      <c r="U33" s="3" t="inlineStr">
         <is>
           <t>211</t>
         </is>
@@ -2867,16 +2905,17 @@
       </c>
       <c r="M34" s="6" t="n"/>
       <c r="N34" s="6" t="n"/>
-      <c r="O34" s="7" t="n"/>
-      <c r="P34" s="6" t="n"/>
+      <c r="O34" s="6" t="n"/>
+      <c r="P34" s="7" t="n"/>
       <c r="Q34" s="6" t="n"/>
-      <c r="R34" s="7" t="n"/>
-      <c r="S34" s="3" t="inlineStr">
+      <c r="R34" s="6" t="n"/>
+      <c r="S34" s="7" t="n"/>
+      <c r="T34" s="3" t="inlineStr">
         <is>
           <t>539</t>
         </is>
       </c>
-      <c r="T34" s="3" t="inlineStr">
+      <c r="U34" s="3" t="inlineStr">
         <is>
           <t>540</t>
         </is>
@@ -2933,16 +2972,17 @@
       </c>
       <c r="M35" s="6" t="n"/>
       <c r="N35" s="6" t="n"/>
-      <c r="O35" s="7" t="n"/>
-      <c r="P35" s="6" t="n"/>
+      <c r="O35" s="6" t="n"/>
+      <c r="P35" s="7" t="n"/>
       <c r="Q35" s="6" t="n"/>
-      <c r="R35" s="7" t="n"/>
-      <c r="S35" s="3" t="inlineStr">
+      <c r="R35" s="6" t="n"/>
+      <c r="S35" s="7" t="n"/>
+      <c r="T35" s="3" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="T35" s="3" t="inlineStr">
+      <c r="U35" s="3" t="inlineStr">
         <is>
           <t>49</t>
         </is>
@@ -3003,16 +3043,17 @@
       </c>
       <c r="M36" s="6" t="n"/>
       <c r="N36" s="6" t="n"/>
-      <c r="O36" s="7" t="n"/>
-      <c r="P36" s="6" t="n"/>
+      <c r="O36" s="6" t="n"/>
+      <c r="P36" s="7" t="n"/>
       <c r="Q36" s="6" t="n"/>
-      <c r="R36" s="7" t="n"/>
-      <c r="S36" s="3" t="inlineStr">
+      <c r="R36" s="6" t="n"/>
+      <c r="S36" s="7" t="n"/>
+      <c r="T36" s="3" t="inlineStr">
         <is>
           <t>655</t>
         </is>
       </c>
-      <c r="T36" s="3" t="inlineStr">
+      <c r="U36" s="3" t="inlineStr">
         <is>
           <t>656</t>
         </is>
@@ -3073,16 +3114,17 @@
       </c>
       <c r="M37" s="6" t="n"/>
       <c r="N37" s="6" t="n"/>
-      <c r="O37" s="7" t="n"/>
-      <c r="P37" s="6" t="n"/>
+      <c r="O37" s="6" t="n"/>
+      <c r="P37" s="7" t="n"/>
       <c r="Q37" s="6" t="n"/>
-      <c r="R37" s="7" t="n"/>
-      <c r="S37" s="3" t="inlineStr">
+      <c r="R37" s="6" t="n"/>
+      <c r="S37" s="7" t="n"/>
+      <c r="T37" s="3" t="inlineStr">
         <is>
           <t>832</t>
         </is>
       </c>
-      <c r="T37" s="3" t="inlineStr">
+      <c r="U37" s="3" t="inlineStr">
         <is>
           <t>834</t>
         </is>
@@ -3143,16 +3185,17 @@
       </c>
       <c r="M38" s="6" t="n"/>
       <c r="N38" s="6" t="n"/>
-      <c r="O38" s="7" t="n"/>
-      <c r="P38" s="6" t="n"/>
+      <c r="O38" s="6" t="n"/>
+      <c r="P38" s="7" t="n"/>
       <c r="Q38" s="6" t="n"/>
-      <c r="R38" s="7" t="n"/>
-      <c r="S38" s="3" t="inlineStr">
+      <c r="R38" s="6" t="n"/>
+      <c r="S38" s="7" t="n"/>
+      <c r="T38" s="3" t="inlineStr">
         <is>
           <t>127</t>
         </is>
       </c>
-      <c r="T38" s="3" t="inlineStr">
+      <c r="U38" s="3" t="inlineStr">
         <is>
           <t>128</t>
         </is>
@@ -3209,16 +3252,17 @@
       </c>
       <c r="M39" s="6" t="n"/>
       <c r="N39" s="6" t="n"/>
-      <c r="O39" s="7" t="n"/>
-      <c r="P39" s="6" t="n"/>
+      <c r="O39" s="6" t="n"/>
+      <c r="P39" s="7" t="n"/>
       <c r="Q39" s="6" t="n"/>
-      <c r="R39" s="7" t="n"/>
-      <c r="S39" s="3" t="inlineStr">
+      <c r="R39" s="6" t="n"/>
+      <c r="S39" s="7" t="n"/>
+      <c r="T39" s="3" t="inlineStr">
         <is>
           <t>1035</t>
         </is>
       </c>
-      <c r="T39" s="3" t="inlineStr">
+      <c r="U39" s="3" t="inlineStr">
         <is>
           <t>1037</t>
         </is>
@@ -3279,16 +3323,17 @@
       </c>
       <c r="M40" s="6" t="n"/>
       <c r="N40" s="6" t="n"/>
-      <c r="O40" s="7" t="n"/>
-      <c r="P40" s="6" t="n"/>
+      <c r="O40" s="6" t="n"/>
+      <c r="P40" s="7" t="n"/>
       <c r="Q40" s="6" t="n"/>
-      <c r="R40" s="7" t="n"/>
-      <c r="S40" s="3" t="inlineStr">
+      <c r="R40" s="6" t="n"/>
+      <c r="S40" s="7" t="n"/>
+      <c r="T40" s="3" t="inlineStr">
         <is>
           <t>519</t>
         </is>
       </c>
-      <c r="T40" s="3" t="inlineStr">
+      <c r="U40" s="3" t="inlineStr">
         <is>
           <t>520</t>
         </is>
@@ -3349,16 +3394,17 @@
       </c>
       <c r="M41" s="6" t="n"/>
       <c r="N41" s="6" t="n"/>
-      <c r="O41" s="7" t="n"/>
-      <c r="P41" s="6" t="n"/>
+      <c r="O41" s="6" t="n"/>
+      <c r="P41" s="7" t="n"/>
       <c r="Q41" s="6" t="n"/>
-      <c r="R41" s="7" t="n"/>
-      <c r="S41" s="3" t="inlineStr">
+      <c r="R41" s="6" t="n"/>
+      <c r="S41" s="7" t="n"/>
+      <c r="T41" s="3" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="T41" s="3" t="inlineStr">
+      <c r="U41" s="3" t="inlineStr">
         <is>
           <t>555</t>
         </is>
@@ -3419,16 +3465,17 @@
       </c>
       <c r="M42" s="6" t="n"/>
       <c r="N42" s="6" t="n"/>
-      <c r="O42" s="7" t="n"/>
-      <c r="P42" s="6" t="n"/>
+      <c r="O42" s="6" t="n"/>
+      <c r="P42" s="7" t="n"/>
       <c r="Q42" s="6" t="n"/>
-      <c r="R42" s="7" t="n"/>
-      <c r="S42" s="3" t="inlineStr">
+      <c r="R42" s="6" t="n"/>
+      <c r="S42" s="7" t="n"/>
+      <c r="T42" s="3" t="inlineStr">
         <is>
           <t>215</t>
         </is>
       </c>
-      <c r="T42" s="3" t="inlineStr">
+      <c r="U42" s="3" t="inlineStr">
         <is>
           <t>216</t>
         </is>
@@ -3489,16 +3536,17 @@
       </c>
       <c r="M43" s="6" t="n"/>
       <c r="N43" s="6" t="n"/>
-      <c r="O43" s="7" t="n"/>
-      <c r="P43" s="6" t="n"/>
+      <c r="O43" s="6" t="n"/>
+      <c r="P43" s="7" t="n"/>
       <c r="Q43" s="6" t="n"/>
-      <c r="R43" s="7" t="n"/>
-      <c r="S43" s="3" t="inlineStr">
+      <c r="R43" s="6" t="n"/>
+      <c r="S43" s="7" t="n"/>
+      <c r="T43" s="3" t="inlineStr">
         <is>
           <t>427</t>
         </is>
       </c>
-      <c r="T43" s="3" t="inlineStr">
+      <c r="U43" s="3" t="inlineStr">
         <is>
           <t>428</t>
         </is>
@@ -3555,16 +3603,17 @@
       </c>
       <c r="M44" s="6" t="n"/>
       <c r="N44" s="6" t="n"/>
-      <c r="O44" s="7" t="n"/>
-      <c r="P44" s="6" t="n"/>
+      <c r="O44" s="6" t="n"/>
+      <c r="P44" s="7" t="n"/>
       <c r="Q44" s="6" t="n"/>
-      <c r="R44" s="7" t="n"/>
-      <c r="S44" s="3" t="inlineStr">
+      <c r="R44" s="6" t="n"/>
+      <c r="S44" s="7" t="n"/>
+      <c r="T44" s="3" t="inlineStr">
         <is>
           <t>613</t>
         </is>
       </c>
-      <c r="T44" s="3" t="inlineStr">
+      <c r="U44" s="3" t="inlineStr">
         <is>
           <t>614</t>
         </is>
@@ -3625,16 +3674,17 @@
       </c>
       <c r="M45" s="6" t="n"/>
       <c r="N45" s="6" t="n"/>
-      <c r="O45" s="7" t="n"/>
-      <c r="P45" s="6" t="n"/>
+      <c r="O45" s="6" t="n"/>
+      <c r="P45" s="7" t="n"/>
       <c r="Q45" s="6" t="n"/>
-      <c r="R45" s="7" t="n"/>
-      <c r="S45" s="3" t="inlineStr">
+      <c r="R45" s="6" t="n"/>
+      <c r="S45" s="7" t="n"/>
+      <c r="T45" s="3" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="T45" s="3" t="inlineStr">
+      <c r="U45" s="3" t="inlineStr">
         <is>
           <t>946</t>
         </is>
@@ -3695,16 +3745,17 @@
       </c>
       <c r="M46" s="6" t="n"/>
       <c r="N46" s="6" t="n"/>
-      <c r="O46" s="7" t="n"/>
-      <c r="P46" s="6" t="n"/>
+      <c r="O46" s="6" t="n"/>
+      <c r="P46" s="7" t="n"/>
       <c r="Q46" s="6" t="n"/>
-      <c r="R46" s="7" t="n"/>
-      <c r="S46" s="3" t="inlineStr">
+      <c r="R46" s="6" t="n"/>
+      <c r="S46" s="7" t="n"/>
+      <c r="T46" s="3" t="inlineStr">
         <is>
           <t>649</t>
         </is>
       </c>
-      <c r="T46" s="3" t="inlineStr">
+      <c r="U46" s="3" t="inlineStr">
         <is>
           <t>650</t>
         </is>
@@ -3765,16 +3816,17 @@
       </c>
       <c r="M47" s="6" t="n"/>
       <c r="N47" s="6" t="n"/>
-      <c r="O47" s="7" t="n"/>
-      <c r="P47" s="6" t="n"/>
+      <c r="O47" s="6" t="n"/>
+      <c r="P47" s="7" t="n"/>
       <c r="Q47" s="6" t="n"/>
-      <c r="R47" s="7" t="n"/>
-      <c r="S47" s="3" t="inlineStr">
+      <c r="R47" s="6" t="n"/>
+      <c r="S47" s="7" t="n"/>
+      <c r="T47" s="3" t="inlineStr">
         <is>
           <t>972</t>
         </is>
       </c>
-      <c r="T47" s="3" t="inlineStr">
+      <c r="U47" s="3" t="inlineStr">
         <is>
           <t>974</t>
         </is>
@@ -3831,16 +3883,17 @@
       </c>
       <c r="M48" s="6" t="n"/>
       <c r="N48" s="6" t="n"/>
-      <c r="O48" s="7" t="n"/>
-      <c r="P48" s="6" t="n"/>
+      <c r="O48" s="6" t="n"/>
+      <c r="P48" s="7" t="n"/>
       <c r="Q48" s="6" t="n"/>
-      <c r="R48" s="7" t="n"/>
-      <c r="S48" s="3" t="inlineStr">
+      <c r="R48" s="6" t="n"/>
+      <c r="S48" s="7" t="n"/>
+      <c r="T48" s="3" t="inlineStr">
         <is>
           <t>678</t>
         </is>
       </c>
-      <c r="T48" s="3" t="inlineStr">
+      <c r="U48" s="3" t="inlineStr">
         <is>
           <t>679</t>
         </is>
@@ -3901,16 +3954,17 @@
       </c>
       <c r="M49" s="6" t="n"/>
       <c r="N49" s="6" t="n"/>
-      <c r="O49" s="7" t="n"/>
-      <c r="P49" s="6" t="n"/>
+      <c r="O49" s="6" t="n"/>
+      <c r="P49" s="7" t="n"/>
       <c r="Q49" s="6" t="n"/>
-      <c r="R49" s="7" t="n"/>
-      <c r="S49" s="3" t="inlineStr">
+      <c r="R49" s="6" t="n"/>
+      <c r="S49" s="7" t="n"/>
+      <c r="T49" s="3" t="inlineStr">
         <is>
           <t>661</t>
         </is>
       </c>
-      <c r="T49" s="3" t="inlineStr">
+      <c r="U49" s="3" t="inlineStr">
         <is>
           <t>662</t>
         </is>
@@ -3971,16 +4025,17 @@
       </c>
       <c r="M50" s="6" t="n"/>
       <c r="N50" s="6" t="n"/>
-      <c r="O50" s="7" t="n"/>
-      <c r="P50" s="6" t="n"/>
+      <c r="O50" s="6" t="n"/>
+      <c r="P50" s="7" t="n"/>
       <c r="Q50" s="6" t="n"/>
-      <c r="R50" s="7" t="n"/>
-      <c r="S50" s="3" t="inlineStr">
+      <c r="R50" s="6" t="n"/>
+      <c r="S50" s="7" t="n"/>
+      <c r="T50" s="3" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="T50" s="3" t="inlineStr">
+      <c r="U50" s="3" t="inlineStr">
         <is>
           <t>655</t>
         </is>
@@ -4041,16 +4096,17 @@
       </c>
       <c r="M51" s="6" t="n"/>
       <c r="N51" s="6" t="n"/>
-      <c r="O51" s="7" t="n"/>
-      <c r="P51" s="6" t="n"/>
+      <c r="O51" s="6" t="n"/>
+      <c r="P51" s="7" t="n"/>
       <c r="Q51" s="6" t="n"/>
-      <c r="R51" s="7" t="n"/>
-      <c r="S51" s="3" t="inlineStr">
+      <c r="R51" s="6" t="n"/>
+      <c r="S51" s="7" t="n"/>
+      <c r="T51" s="3" t="inlineStr">
         <is>
           <t>869</t>
         </is>
       </c>
-      <c r="T51" s="3" t="inlineStr">
+      <c r="U51" s="3" t="inlineStr">
         <is>
           <t>871</t>
         </is>
@@ -4107,16 +4163,17 @@
       </c>
       <c r="M52" s="6" t="n"/>
       <c r="N52" s="6" t="n"/>
-      <c r="O52" s="7" t="n"/>
-      <c r="P52" s="6" t="n"/>
+      <c r="O52" s="6" t="n"/>
+      <c r="P52" s="7" t="n"/>
       <c r="Q52" s="6" t="n"/>
-      <c r="R52" s="7" t="n"/>
-      <c r="S52" s="3" t="inlineStr">
+      <c r="R52" s="6" t="n"/>
+      <c r="S52" s="7" t="n"/>
+      <c r="T52" s="3" t="inlineStr">
         <is>
           <t>451</t>
         </is>
       </c>
-      <c r="T52" s="3" t="inlineStr">
+      <c r="U52" s="3" t="inlineStr">
         <is>
           <t>452</t>
         </is>
@@ -4173,16 +4230,17 @@
       </c>
       <c r="M53" s="6" t="n"/>
       <c r="N53" s="6" t="n"/>
-      <c r="O53" s="7" t="n"/>
-      <c r="P53" s="6" t="n"/>
+      <c r="O53" s="6" t="n"/>
+      <c r="P53" s="7" t="n"/>
       <c r="Q53" s="6" t="n"/>
-      <c r="R53" s="7" t="n"/>
-      <c r="S53" s="3" t="inlineStr">
+      <c r="R53" s="6" t="n"/>
+      <c r="S53" s="7" t="n"/>
+      <c r="T53" s="3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="T53" s="3" t="inlineStr">
+      <c r="U53" s="3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
@@ -4239,16 +4297,17 @@
       </c>
       <c r="M54" s="6" t="n"/>
       <c r="N54" s="6" t="n"/>
-      <c r="O54" s="7" t="n"/>
-      <c r="P54" s="6" t="n"/>
+      <c r="O54" s="6" t="n"/>
+      <c r="P54" s="7" t="n"/>
       <c r="Q54" s="6" t="n"/>
-      <c r="R54" s="7" t="n"/>
-      <c r="S54" s="3" t="inlineStr">
+      <c r="R54" s="6" t="n"/>
+      <c r="S54" s="7" t="n"/>
+      <c r="T54" s="3" t="inlineStr">
         <is>
           <t>474</t>
         </is>
       </c>
-      <c r="T54" s="3" t="inlineStr">
+      <c r="U54" s="3" t="inlineStr">
         <is>
           <t>475</t>
         </is>
@@ -4309,16 +4368,17 @@
       </c>
       <c r="M55" s="6" t="n"/>
       <c r="N55" s="6" t="n"/>
-      <c r="O55" s="7" t="n"/>
-      <c r="P55" s="6" t="n"/>
+      <c r="O55" s="6" t="n"/>
+      <c r="P55" s="7" t="n"/>
       <c r="Q55" s="6" t="n"/>
-      <c r="R55" s="7" t="n"/>
-      <c r="S55" s="3" t="inlineStr">
+      <c r="R55" s="6" t="n"/>
+      <c r="S55" s="7" t="n"/>
+      <c r="T55" s="3" t="inlineStr">
         <is>
           <t>805</t>
         </is>
       </c>
-      <c r="T55" s="3" t="inlineStr">
+      <c r="U55" s="3" t="inlineStr">
         <is>
           <t>807</t>
         </is>
@@ -4375,16 +4435,17 @@
       </c>
       <c r="M56" s="6" t="n"/>
       <c r="N56" s="6" t="n"/>
-      <c r="O56" s="7" t="n"/>
-      <c r="P56" s="6" t="n"/>
+      <c r="O56" s="6" t="n"/>
+      <c r="P56" s="7" t="n"/>
       <c r="Q56" s="6" t="n"/>
-      <c r="R56" s="7" t="n"/>
-      <c r="S56" s="3" t="inlineStr">
+      <c r="R56" s="6" t="n"/>
+      <c r="S56" s="7" t="n"/>
+      <c r="T56" s="3" t="inlineStr">
         <is>
           <t>1037</t>
         </is>
       </c>
-      <c r="T56" s="3" t="inlineStr">
+      <c r="U56" s="3" t="inlineStr">
         <is>
           <t>1039</t>
         </is>
@@ -4445,16 +4506,17 @@
       </c>
       <c r="M57" s="6" t="n"/>
       <c r="N57" s="6" t="n"/>
-      <c r="O57" s="7" t="n"/>
-      <c r="P57" s="6" t="n"/>
+      <c r="O57" s="6" t="n"/>
+      <c r="P57" s="7" t="n"/>
       <c r="Q57" s="6" t="n"/>
-      <c r="R57" s="7" t="n"/>
-      <c r="S57" s="3" t="inlineStr">
+      <c r="R57" s="6" t="n"/>
+      <c r="S57" s="7" t="n"/>
+      <c r="T57" s="3" t="inlineStr">
         <is>
           <t>424</t>
         </is>
       </c>
-      <c r="T57" s="3" t="inlineStr">
+      <c r="U57" s="3" t="inlineStr">
         <is>
           <t>425</t>
         </is>
@@ -4515,16 +4577,17 @@
       </c>
       <c r="M58" s="6" t="n"/>
       <c r="N58" s="6" t="n"/>
-      <c r="O58" s="7" t="n"/>
-      <c r="P58" s="6" t="n"/>
+      <c r="O58" s="6" t="n"/>
+      <c r="P58" s="7" t="n"/>
       <c r="Q58" s="6" t="n"/>
-      <c r="R58" s="7" t="n"/>
-      <c r="S58" s="3" t="inlineStr">
+      <c r="R58" s="6" t="n"/>
+      <c r="S58" s="7" t="n"/>
+      <c r="T58" s="3" t="inlineStr">
         <is>
           <t>387</t>
         </is>
       </c>
-      <c r="T58" s="3" t="inlineStr">
+      <c r="U58" s="3" t="inlineStr">
         <is>
           <t>388</t>
         </is>
@@ -4585,16 +4648,17 @@
       </c>
       <c r="M59" s="6" t="n"/>
       <c r="N59" s="6" t="n"/>
-      <c r="O59" s="7" t="n"/>
-      <c r="P59" s="6" t="n"/>
+      <c r="O59" s="6" t="n"/>
+      <c r="P59" s="7" t="n"/>
       <c r="Q59" s="6" t="n"/>
-      <c r="R59" s="7" t="n"/>
-      <c r="S59" s="3" t="inlineStr">
+      <c r="R59" s="6" t="n"/>
+      <c r="S59" s="7" t="n"/>
+      <c r="T59" s="3" t="inlineStr">
         <is>
           <t>922</t>
         </is>
       </c>
-      <c r="T59" s="3" t="inlineStr">
+      <c r="U59" s="3" t="inlineStr">
         <is>
           <t>924</t>
         </is>
@@ -4655,16 +4719,17 @@
       </c>
       <c r="M60" s="6" t="n"/>
       <c r="N60" s="6" t="n"/>
-      <c r="O60" s="7" t="n"/>
-      <c r="P60" s="6" t="n"/>
+      <c r="O60" s="6" t="n"/>
+      <c r="P60" s="7" t="n"/>
       <c r="Q60" s="6" t="n"/>
-      <c r="R60" s="7" t="n"/>
-      <c r="S60" s="3" t="inlineStr">
+      <c r="R60" s="6" t="n"/>
+      <c r="S60" s="7" t="n"/>
+      <c r="T60" s="3" t="inlineStr">
         <is>
           <t>845</t>
         </is>
       </c>
-      <c r="T60" s="3" t="inlineStr">
+      <c r="U60" s="3" t="inlineStr">
         <is>
           <t>847</t>
         </is>
@@ -4721,16 +4786,17 @@
       </c>
       <c r="M61" s="6" t="n"/>
       <c r="N61" s="6" t="n"/>
-      <c r="O61" s="7" t="n"/>
-      <c r="P61" s="6" t="n"/>
+      <c r="O61" s="6" t="n"/>
+      <c r="P61" s="7" t="n"/>
       <c r="Q61" s="6" t="n"/>
-      <c r="R61" s="7" t="n"/>
-      <c r="S61" s="3" t="inlineStr">
+      <c r="R61" s="6" t="n"/>
+      <c r="S61" s="7" t="n"/>
+      <c r="T61" s="3" t="inlineStr">
         <is>
           <t>263</t>
         </is>
       </c>
-      <c r="T61" s="3" t="inlineStr">
+      <c r="U61" s="3" t="inlineStr">
         <is>
           <t>264</t>
         </is>
@@ -4791,16 +4857,17 @@
       </c>
       <c r="M62" s="6" t="n"/>
       <c r="N62" s="6" t="n"/>
-      <c r="O62" s="7" t="n"/>
-      <c r="P62" s="6" t="n"/>
+      <c r="O62" s="6" t="n"/>
+      <c r="P62" s="7" t="n"/>
       <c r="Q62" s="6" t="n"/>
-      <c r="R62" s="7" t="n"/>
-      <c r="S62" s="3" t="inlineStr">
+      <c r="R62" s="6" t="n"/>
+      <c r="S62" s="7" t="n"/>
+      <c r="T62" s="3" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="T62" s="3" t="inlineStr">
+      <c r="U62" s="3" t="inlineStr">
         <is>
           <t>238</t>
         </is>
@@ -4861,16 +4928,17 @@
       </c>
       <c r="M63" s="6" t="n"/>
       <c r="N63" s="6" t="n"/>
-      <c r="O63" s="7" t="n"/>
-      <c r="P63" s="6" t="n"/>
+      <c r="O63" s="6" t="n"/>
+      <c r="P63" s="7" t="n"/>
       <c r="Q63" s="6" t="n"/>
-      <c r="R63" s="7" t="n"/>
-      <c r="S63" s="3" t="inlineStr">
+      <c r="R63" s="6" t="n"/>
+      <c r="S63" s="7" t="n"/>
+      <c r="T63" s="3" t="inlineStr">
         <is>
           <t>213</t>
         </is>
       </c>
-      <c r="T63" s="3" t="inlineStr">
+      <c r="U63" s="3" t="inlineStr">
         <is>
           <t>214</t>
         </is>
@@ -4927,16 +4995,17 @@
       </c>
       <c r="M64" s="6" t="n"/>
       <c r="N64" s="6" t="n"/>
-      <c r="O64" s="7" t="n"/>
-      <c r="P64" s="6" t="n"/>
+      <c r="O64" s="6" t="n"/>
+      <c r="P64" s="7" t="n"/>
       <c r="Q64" s="6" t="n"/>
-      <c r="R64" s="7" t="n"/>
-      <c r="S64" s="3" t="inlineStr">
+      <c r="R64" s="6" t="n"/>
+      <c r="S64" s="7" t="n"/>
+      <c r="T64" s="3" t="inlineStr">
         <is>
           <t>453</t>
         </is>
       </c>
-      <c r="T64" s="3" t="inlineStr">
+      <c r="U64" s="3" t="inlineStr">
         <is>
           <t>454</t>
         </is>
@@ -4997,16 +5066,17 @@
       </c>
       <c r="M65" s="6" t="n"/>
       <c r="N65" s="6" t="n"/>
-      <c r="O65" s="7" t="n"/>
-      <c r="P65" s="6" t="n"/>
+      <c r="O65" s="6" t="n"/>
+      <c r="P65" s="7" t="n"/>
       <c r="Q65" s="6" t="n"/>
-      <c r="R65" s="7" t="n"/>
-      <c r="S65" s="3" t="inlineStr">
+      <c r="R65" s="6" t="n"/>
+      <c r="S65" s="7" t="n"/>
+      <c r="T65" s="3" t="inlineStr">
         <is>
           <t>898</t>
         </is>
       </c>
-      <c r="T65" s="3" t="inlineStr">
+      <c r="U65" s="3" t="inlineStr">
         <is>
           <t>900</t>
         </is>
@@ -5067,16 +5137,17 @@
       </c>
       <c r="M66" s="6" t="n"/>
       <c r="N66" s="6" t="n"/>
-      <c r="O66" s="7" t="n"/>
-      <c r="P66" s="6" t="n"/>
+      <c r="O66" s="6" t="n"/>
+      <c r="P66" s="7" t="n"/>
       <c r="Q66" s="6" t="n"/>
-      <c r="R66" s="7" t="n"/>
-      <c r="S66" s="3" t="inlineStr">
+      <c r="R66" s="6" t="n"/>
+      <c r="S66" s="7" t="n"/>
+      <c r="T66" s="3" t="inlineStr">
         <is>
           <t>802</t>
         </is>
       </c>
-      <c r="T66" s="3" t="inlineStr">
+      <c r="U66" s="3" t="inlineStr">
         <is>
           <t>803</t>
         </is>
@@ -5137,16 +5208,17 @@
       </c>
       <c r="M67" s="6" t="n"/>
       <c r="N67" s="6" t="n"/>
-      <c r="O67" s="7" t="n"/>
-      <c r="P67" s="6" t="n"/>
+      <c r="O67" s="6" t="n"/>
+      <c r="P67" s="7" t="n"/>
       <c r="Q67" s="6" t="n"/>
-      <c r="R67" s="7" t="n"/>
-      <c r="S67" s="3" t="inlineStr">
+      <c r="R67" s="6" t="n"/>
+      <c r="S67" s="7" t="n"/>
+      <c r="T67" s="3" t="inlineStr">
         <is>
           <t>614</t>
         </is>
       </c>
-      <c r="T67" s="3" t="inlineStr">
+      <c r="U67" s="3" t="inlineStr">
         <is>
           <t>615</t>
         </is>
@@ -5207,16 +5279,17 @@
       </c>
       <c r="M68" s="6" t="n"/>
       <c r="N68" s="6" t="n"/>
-      <c r="O68" s="7" t="n"/>
-      <c r="P68" s="6" t="n"/>
+      <c r="O68" s="6" t="n"/>
+      <c r="P68" s="7" t="n"/>
       <c r="Q68" s="6" t="n"/>
-      <c r="R68" s="7" t="n"/>
-      <c r="S68" s="3" t="inlineStr">
+      <c r="R68" s="6" t="n"/>
+      <c r="S68" s="7" t="n"/>
+      <c r="T68" s="3" t="inlineStr">
         <is>
           <t>796</t>
         </is>
       </c>
-      <c r="T68" s="3" t="inlineStr">
+      <c r="U68" s="3" t="inlineStr">
         <is>
           <t>797</t>
         </is>
@@ -5277,16 +5350,17 @@
       </c>
       <c r="M69" s="6" t="n"/>
       <c r="N69" s="6" t="n"/>
-      <c r="O69" s="7" t="n"/>
-      <c r="P69" s="6" t="n"/>
+      <c r="O69" s="6" t="n"/>
+      <c r="P69" s="7" t="n"/>
       <c r="Q69" s="6" t="n"/>
-      <c r="R69" s="7" t="n"/>
-      <c r="S69" s="3" t="inlineStr">
+      <c r="R69" s="6" t="n"/>
+      <c r="S69" s="7" t="n"/>
+      <c r="T69" s="3" t="inlineStr">
         <is>
           <t>959</t>
         </is>
       </c>
-      <c r="T69" s="3" t="inlineStr">
+      <c r="U69" s="3" t="inlineStr">
         <is>
           <t>961</t>
         </is>
@@ -5343,16 +5417,17 @@
       </c>
       <c r="M70" s="6" t="n"/>
       <c r="N70" s="6" t="n"/>
-      <c r="O70" s="7" t="n"/>
-      <c r="P70" s="6" t="n"/>
+      <c r="O70" s="6" t="n"/>
+      <c r="P70" s="7" t="n"/>
       <c r="Q70" s="6" t="n"/>
-      <c r="R70" s="7" t="n"/>
-      <c r="S70" s="3" t="inlineStr">
+      <c r="R70" s="6" t="n"/>
+      <c r="S70" s="7" t="n"/>
+      <c r="T70" s="3" t="inlineStr">
         <is>
           <t>449</t>
         </is>
       </c>
-      <c r="T70" s="3" t="inlineStr">
+      <c r="U70" s="3" t="inlineStr">
         <is>
           <t>450</t>
         </is>
@@ -5413,16 +5488,17 @@
       </c>
       <c r="M71" s="6" t="n"/>
       <c r="N71" s="6" t="n"/>
-      <c r="O71" s="7" t="n"/>
-      <c r="P71" s="6" t="n"/>
+      <c r="O71" s="6" t="n"/>
+      <c r="P71" s="7" t="n"/>
       <c r="Q71" s="6" t="n"/>
-      <c r="R71" s="7" t="n"/>
-      <c r="S71" s="3" t="inlineStr">
+      <c r="R71" s="6" t="n"/>
+      <c r="S71" s="7" t="n"/>
+      <c r="T71" s="3" t="inlineStr">
         <is>
           <t>820</t>
         </is>
       </c>
-      <c r="T71" s="3" t="inlineStr">
+      <c r="U71" s="3" t="inlineStr">
         <is>
           <t>822</t>
         </is>
@@ -5483,16 +5559,17 @@
       </c>
       <c r="M72" s="6" t="n"/>
       <c r="N72" s="6" t="n"/>
-      <c r="O72" s="7" t="n"/>
-      <c r="P72" s="6" t="n"/>
+      <c r="O72" s="6" t="n"/>
+      <c r="P72" s="7" t="n"/>
       <c r="Q72" s="6" t="n"/>
-      <c r="R72" s="7" t="n"/>
-      <c r="S72" s="3" t="inlineStr">
+      <c r="R72" s="6" t="n"/>
+      <c r="S72" s="7" t="n"/>
+      <c r="T72" s="3" t="inlineStr">
         <is>
           <t>783</t>
         </is>
       </c>
-      <c r="T72" s="3" t="inlineStr">
+      <c r="U72" s="3" t="inlineStr">
         <is>
           <t>784</t>
         </is>
@@ -5549,16 +5626,17 @@
       </c>
       <c r="M73" s="6" t="n"/>
       <c r="N73" s="6" t="n"/>
-      <c r="O73" s="7" t="n"/>
-      <c r="P73" s="6" t="n"/>
+      <c r="O73" s="6" t="n"/>
+      <c r="P73" s="7" t="n"/>
       <c r="Q73" s="6" t="n"/>
-      <c r="R73" s="7" t="n"/>
-      <c r="S73" s="3" t="inlineStr">
+      <c r="R73" s="6" t="n"/>
+      <c r="S73" s="7" t="n"/>
+      <c r="T73" s="3" t="inlineStr">
         <is>
           <t>442</t>
         </is>
       </c>
-      <c r="T73" s="3" t="inlineStr">
+      <c r="U73" s="3" t="inlineStr">
         <is>
           <t>443</t>
         </is>
@@ -5619,16 +5697,17 @@
       </c>
       <c r="M74" s="6" t="n"/>
       <c r="N74" s="6" t="n"/>
-      <c r="O74" s="7" t="n"/>
-      <c r="P74" s="6" t="n"/>
+      <c r="O74" s="6" t="n"/>
+      <c r="P74" s="7" t="n"/>
       <c r="Q74" s="6" t="n"/>
-      <c r="R74" s="7" t="n"/>
-      <c r="S74" s="3" t="inlineStr">
+      <c r="R74" s="6" t="n"/>
+      <c r="S74" s="7" t="n"/>
+      <c r="T74" s="3" t="inlineStr">
         <is>
           <t>513</t>
         </is>
       </c>
-      <c r="T74" s="3" t="inlineStr">
+      <c r="U74" s="3" t="inlineStr">
         <is>
           <t>514</t>
         </is>
@@ -5689,16 +5768,17 @@
       </c>
       <c r="M75" s="6" t="n"/>
       <c r="N75" s="6" t="n"/>
-      <c r="O75" s="7" t="n"/>
-      <c r="P75" s="6" t="n"/>
+      <c r="O75" s="6" t="n"/>
+      <c r="P75" s="7" t="n"/>
       <c r="Q75" s="6" t="n"/>
-      <c r="R75" s="7" t="n"/>
-      <c r="S75" s="3" t="inlineStr">
+      <c r="R75" s="6" t="n"/>
+      <c r="S75" s="7" t="n"/>
+      <c r="T75" s="3" t="inlineStr">
         <is>
           <t>311</t>
         </is>
       </c>
-      <c r="T75" s="3" t="inlineStr">
+      <c r="U75" s="3" t="inlineStr">
         <is>
           <t>312</t>
         </is>
@@ -5759,16 +5839,17 @@
       </c>
       <c r="M76" s="6" t="n"/>
       <c r="N76" s="6" t="n"/>
-      <c r="O76" s="7" t="n"/>
-      <c r="P76" s="6" t="n"/>
+      <c r="O76" s="6" t="n"/>
+      <c r="P76" s="7" t="n"/>
       <c r="Q76" s="6" t="n"/>
-      <c r="R76" s="7" t="n"/>
-      <c r="S76" s="3" t="inlineStr">
+      <c r="R76" s="6" t="n"/>
+      <c r="S76" s="7" t="n"/>
+      <c r="T76" s="3" t="inlineStr">
         <is>
           <t>980</t>
         </is>
       </c>
-      <c r="T76" s="3" t="inlineStr">
+      <c r="U76" s="3" t="inlineStr">
         <is>
           <t>982</t>
         </is>
@@ -5829,16 +5910,17 @@
       </c>
       <c r="M77" s="6" t="n"/>
       <c r="N77" s="6" t="n"/>
-      <c r="O77" s="7" t="n"/>
-      <c r="P77" s="6" t="n"/>
+      <c r="O77" s="6" t="n"/>
+      <c r="P77" s="7" t="n"/>
       <c r="Q77" s="6" t="n"/>
-      <c r="R77" s="7" t="n"/>
-      <c r="S77" s="3" t="inlineStr">
+      <c r="R77" s="6" t="n"/>
+      <c r="S77" s="7" t="n"/>
+      <c r="T77" s="3" t="inlineStr">
         <is>
           <t>662</t>
         </is>
       </c>
-      <c r="T77" s="3" t="inlineStr">
+      <c r="U77" s="3" t="inlineStr">
         <is>
           <t>663</t>
         </is>
@@ -5899,16 +5981,17 @@
       </c>
       <c r="M78" s="6" t="n"/>
       <c r="N78" s="6" t="n"/>
-      <c r="O78" s="7" t="n"/>
-      <c r="P78" s="6" t="n"/>
+      <c r="O78" s="6" t="n"/>
+      <c r="P78" s="7" t="n"/>
       <c r="Q78" s="6" t="n"/>
-      <c r="R78" s="7" t="n"/>
-      <c r="S78" s="3" t="inlineStr">
+      <c r="R78" s="6" t="n"/>
+      <c r="S78" s="7" t="n"/>
+      <c r="T78" s="3" t="inlineStr">
         <is>
           <t>837</t>
         </is>
       </c>
-      <c r="T78" s="3" t="inlineStr">
+      <c r="U78" s="3" t="inlineStr">
         <is>
           <t>839</t>
         </is>
@@ -5969,16 +6052,17 @@
       </c>
       <c r="M79" s="6" t="n"/>
       <c r="N79" s="6" t="n"/>
-      <c r="O79" s="7" t="n"/>
-      <c r="P79" s="6" t="n"/>
+      <c r="O79" s="6" t="n"/>
+      <c r="P79" s="7" t="n"/>
       <c r="Q79" s="6" t="n"/>
-      <c r="R79" s="7" t="n"/>
-      <c r="S79" s="3" t="inlineStr">
+      <c r="R79" s="6" t="n"/>
+      <c r="S79" s="7" t="n"/>
+      <c r="T79" s="3" t="inlineStr">
         <is>
           <t>391</t>
         </is>
       </c>
-      <c r="T79" s="3" t="inlineStr">
+      <c r="U79" s="3" t="inlineStr">
         <is>
           <t>392</t>
         </is>
@@ -6039,16 +6123,17 @@
       </c>
       <c r="M80" s="12" t="n"/>
       <c r="N80" s="12" t="n"/>
-      <c r="O80" s="13" t="n"/>
-      <c r="P80" s="12" t="n"/>
+      <c r="O80" s="12" t="n"/>
+      <c r="P80" s="13" t="n"/>
       <c r="Q80" s="12" t="n"/>
-      <c r="R80" s="13" t="n"/>
-      <c r="S80" s="9" t="inlineStr">
+      <c r="R80" s="12" t="n"/>
+      <c r="S80" s="13" t="n"/>
+      <c r="T80" s="9" t="inlineStr">
         <is>
           <t>441</t>
         </is>
       </c>
-      <c r="T80" s="9" t="inlineStr">
+      <c r="U80" s="9" t="inlineStr">
         <is>
           <t>442</t>
         </is>
@@ -6109,16 +6194,17 @@
       </c>
       <c r="M81" s="6" t="n"/>
       <c r="N81" s="6" t="n"/>
-      <c r="O81" s="7" t="n"/>
-      <c r="P81" s="6" t="n"/>
+      <c r="O81" s="6" t="n"/>
+      <c r="P81" s="7" t="n"/>
       <c r="Q81" s="6" t="n"/>
-      <c r="R81" s="7" t="n"/>
-      <c r="S81" s="3" t="inlineStr">
+      <c r="R81" s="6" t="n"/>
+      <c r="S81" s="7" t="n"/>
+      <c r="T81" s="3" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="T81" s="3" t="inlineStr">
+      <c r="U81" s="3" t="inlineStr">
         <is>
           <t>68</t>
         </is>
@@ -6179,16 +6265,17 @@
       </c>
       <c r="M82" s="6" t="n"/>
       <c r="N82" s="6" t="n"/>
-      <c r="O82" s="7" t="n"/>
-      <c r="P82" s="6" t="n"/>
+      <c r="O82" s="6" t="n"/>
+      <c r="P82" s="7" t="n"/>
       <c r="Q82" s="6" t="n"/>
-      <c r="R82" s="7" t="n"/>
-      <c r="S82" s="3" t="inlineStr">
+      <c r="R82" s="6" t="n"/>
+      <c r="S82" s="7" t="n"/>
+      <c r="T82" s="3" t="inlineStr">
         <is>
           <t>547</t>
         </is>
       </c>
-      <c r="T82" s="3" t="inlineStr">
+      <c r="U82" s="3" t="inlineStr">
         <is>
           <t>548</t>
         </is>
@@ -6249,16 +6336,17 @@
       </c>
       <c r="M83" s="6" t="n"/>
       <c r="N83" s="6" t="n"/>
-      <c r="O83" s="7" t="n"/>
-      <c r="P83" s="6" t="n"/>
+      <c r="O83" s="6" t="n"/>
+      <c r="P83" s="7" t="n"/>
       <c r="Q83" s="6" t="n"/>
-      <c r="R83" s="7" t="n"/>
-      <c r="S83" s="3" t="inlineStr">
+      <c r="R83" s="6" t="n"/>
+      <c r="S83" s="7" t="n"/>
+      <c r="T83" s="3" t="inlineStr">
         <is>
           <t>428</t>
         </is>
       </c>
-      <c r="T83" s="3" t="inlineStr">
+      <c r="U83" s="3" t="inlineStr">
         <is>
           <t>429</t>
         </is>
@@ -6319,16 +6407,17 @@
       </c>
       <c r="M84" s="6" t="n"/>
       <c r="N84" s="6" t="n"/>
-      <c r="O84" s="7" t="n"/>
-      <c r="P84" s="6" t="n"/>
+      <c r="O84" s="6" t="n"/>
+      <c r="P84" s="7" t="n"/>
       <c r="Q84" s="6" t="n"/>
-      <c r="R84" s="7" t="n"/>
-      <c r="S84" s="3" t="inlineStr">
+      <c r="R84" s="6" t="n"/>
+      <c r="S84" s="7" t="n"/>
+      <c r="T84" s="3" t="inlineStr">
         <is>
           <t>979</t>
         </is>
       </c>
-      <c r="T84" s="3" t="inlineStr">
+      <c r="U84" s="3" t="inlineStr">
         <is>
           <t>981</t>
         </is>
@@ -6385,16 +6474,17 @@
       </c>
       <c r="M85" s="6" t="n"/>
       <c r="N85" s="6" t="n"/>
-      <c r="O85" s="7" t="n"/>
-      <c r="P85" s="6" t="n"/>
+      <c r="O85" s="6" t="n"/>
+      <c r="P85" s="7" t="n"/>
       <c r="Q85" s="6" t="n"/>
-      <c r="R85" s="7" t="n"/>
-      <c r="S85" s="3" t="inlineStr">
+      <c r="R85" s="6" t="n"/>
+      <c r="S85" s="7" t="n"/>
+      <c r="T85" s="3" t="inlineStr">
         <is>
           <t>731</t>
         </is>
       </c>
-      <c r="T85" s="3" t="inlineStr">
+      <c r="U85" s="3" t="inlineStr">
         <is>
           <t>732</t>
         </is>
@@ -6451,16 +6541,17 @@
       </c>
       <c r="M86" s="6" t="n"/>
       <c r="N86" s="6" t="n"/>
-      <c r="O86" s="7" t="n"/>
-      <c r="P86" s="6" t="n"/>
+      <c r="O86" s="6" t="n"/>
+      <c r="P86" s="7" t="n"/>
       <c r="Q86" s="6" t="n"/>
-      <c r="R86" s="7" t="n"/>
-      <c r="S86" s="3" t="inlineStr">
+      <c r="R86" s="6" t="n"/>
+      <c r="S86" s="7" t="n"/>
+      <c r="T86" s="3" t="inlineStr">
         <is>
           <t>1026</t>
         </is>
       </c>
-      <c r="T86" s="3" t="inlineStr">
+      <c r="U86" s="3" t="inlineStr">
         <is>
           <t>1028</t>
         </is>
@@ -6521,16 +6612,17 @@
       </c>
       <c r="M87" s="6" t="n"/>
       <c r="N87" s="6" t="n"/>
-      <c r="O87" s="7" t="n"/>
-      <c r="P87" s="6" t="n"/>
+      <c r="O87" s="6" t="n"/>
+      <c r="P87" s="7" t="n"/>
       <c r="Q87" s="6" t="n"/>
-      <c r="R87" s="7" t="n"/>
-      <c r="S87" s="3" t="inlineStr">
+      <c r="R87" s="6" t="n"/>
+      <c r="S87" s="7" t="n"/>
+      <c r="T87" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T87" s="3" t="inlineStr">
+      <c r="U87" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -6591,16 +6683,17 @@
       </c>
       <c r="M88" s="6" t="n"/>
       <c r="N88" s="6" t="n"/>
-      <c r="O88" s="7" t="n"/>
-      <c r="P88" s="6" t="n"/>
+      <c r="O88" s="6" t="n"/>
+      <c r="P88" s="7" t="n"/>
       <c r="Q88" s="6" t="n"/>
-      <c r="R88" s="7" t="n"/>
-      <c r="S88" s="3" t="inlineStr">
+      <c r="R88" s="6" t="n"/>
+      <c r="S88" s="7" t="n"/>
+      <c r="T88" s="3" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="T88" s="3" t="inlineStr">
+      <c r="U88" s="3" t="inlineStr">
         <is>
           <t>83</t>
         </is>
@@ -6661,16 +6754,17 @@
       </c>
       <c r="M89" s="6" t="n"/>
       <c r="N89" s="6" t="n"/>
-      <c r="O89" s="7" t="n"/>
-      <c r="P89" s="6" t="n"/>
+      <c r="O89" s="6" t="n"/>
+      <c r="P89" s="7" t="n"/>
       <c r="Q89" s="6" t="n"/>
-      <c r="R89" s="7" t="n"/>
-      <c r="S89" s="3" t="inlineStr">
+      <c r="R89" s="6" t="n"/>
+      <c r="S89" s="7" t="n"/>
+      <c r="T89" s="3" t="inlineStr">
         <is>
           <t>679</t>
         </is>
       </c>
-      <c r="T89" s="3" t="inlineStr">
+      <c r="U89" s="3" t="inlineStr">
         <is>
           <t>680</t>
         </is>
@@ -6731,16 +6825,17 @@
       </c>
       <c r="M90" s="6" t="n"/>
       <c r="N90" s="6" t="n"/>
-      <c r="O90" s="7" t="n"/>
-      <c r="P90" s="6" t="n"/>
+      <c r="O90" s="6" t="n"/>
+      <c r="P90" s="7" t="n"/>
       <c r="Q90" s="6" t="n"/>
-      <c r="R90" s="7" t="n"/>
-      <c r="S90" s="3" t="inlineStr">
+      <c r="R90" s="6" t="n"/>
+      <c r="S90" s="7" t="n"/>
+      <c r="T90" s="3" t="inlineStr">
         <is>
           <t>489</t>
         </is>
       </c>
-      <c r="T90" s="3" t="inlineStr">
+      <c r="U90" s="3" t="inlineStr">
         <is>
           <t>490</t>
         </is>
@@ -6789,7 +6884,11 @@
       <c r="J91" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K91" s="3" t="n"/>
+      <c r="K91" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -6797,16 +6896,17 @@
       </c>
       <c r="M91" s="6" t="n"/>
       <c r="N91" s="6" t="n"/>
-      <c r="O91" s="7" t="n"/>
-      <c r="P91" s="6" t="n"/>
+      <c r="O91" s="6" t="n"/>
+      <c r="P91" s="7" t="n"/>
       <c r="Q91" s="6" t="n"/>
-      <c r="R91" s="7" t="n"/>
-      <c r="S91" s="3" t="inlineStr">
+      <c r="R91" s="6" t="n"/>
+      <c r="S91" s="7" t="n"/>
+      <c r="T91" s="3" t="inlineStr">
         <is>
           <t>730</t>
         </is>
       </c>
-      <c r="T91" s="3" t="inlineStr">
+      <c r="U91" s="3" t="inlineStr">
         <is>
           <t>731</t>
         </is>
@@ -6863,16 +6963,17 @@
       </c>
       <c r="M92" s="6" t="n"/>
       <c r="N92" s="6" t="n"/>
-      <c r="O92" s="7" t="n"/>
-      <c r="P92" s="6" t="n"/>
+      <c r="O92" s="6" t="n"/>
+      <c r="P92" s="7" t="n"/>
       <c r="Q92" s="6" t="n"/>
-      <c r="R92" s="7" t="n"/>
-      <c r="S92" s="3" t="inlineStr">
+      <c r="R92" s="6" t="n"/>
+      <c r="S92" s="7" t="n"/>
+      <c r="T92" s="3" t="inlineStr">
         <is>
           <t>704</t>
         </is>
       </c>
-      <c r="T92" s="3" t="inlineStr">
+      <c r="U92" s="3" t="inlineStr">
         <is>
           <t>705</t>
         </is>
@@ -6933,16 +7034,17 @@
       </c>
       <c r="M93" s="6" t="n"/>
       <c r="N93" s="6" t="n"/>
-      <c r="O93" s="7" t="n"/>
-      <c r="P93" s="6" t="n"/>
+      <c r="O93" s="6" t="n"/>
+      <c r="P93" s="7" t="n"/>
       <c r="Q93" s="6" t="n"/>
-      <c r="R93" s="7" t="n"/>
-      <c r="S93" s="3" t="inlineStr">
+      <c r="R93" s="6" t="n"/>
+      <c r="S93" s="7" t="n"/>
+      <c r="T93" s="3" t="inlineStr">
         <is>
           <t>602</t>
         </is>
       </c>
-      <c r="T93" s="3" t="inlineStr">
+      <c r="U93" s="3" t="inlineStr">
         <is>
           <t>603</t>
         </is>
@@ -7003,16 +7105,17 @@
       </c>
       <c r="M94" s="6" t="n"/>
       <c r="N94" s="6" t="n"/>
-      <c r="O94" s="7" t="n"/>
-      <c r="P94" s="6" t="n"/>
+      <c r="O94" s="6" t="n"/>
+      <c r="P94" s="7" t="n"/>
       <c r="Q94" s="6" t="n"/>
-      <c r="R94" s="7" t="n"/>
-      <c r="S94" s="3" t="inlineStr">
+      <c r="R94" s="6" t="n"/>
+      <c r="S94" s="7" t="n"/>
+      <c r="T94" s="3" t="inlineStr">
         <is>
           <t>273</t>
         </is>
       </c>
-      <c r="T94" s="3" t="inlineStr">
+      <c r="U94" s="3" t="inlineStr">
         <is>
           <t>274</t>
         </is>
@@ -7073,16 +7176,17 @@
       </c>
       <c r="M95" s="6" t="n"/>
       <c r="N95" s="6" t="n"/>
-      <c r="O95" s="7" t="n"/>
-      <c r="P95" s="6" t="n"/>
+      <c r="O95" s="6" t="n"/>
+      <c r="P95" s="7" t="n"/>
       <c r="Q95" s="6" t="n"/>
-      <c r="R95" s="7" t="n"/>
-      <c r="S95" s="3" t="inlineStr">
+      <c r="R95" s="6" t="n"/>
+      <c r="S95" s="7" t="n"/>
+      <c r="T95" s="3" t="inlineStr">
         <is>
           <t>62</t>
         </is>
       </c>
-      <c r="T95" s="3" t="inlineStr">
+      <c r="U95" s="3" t="inlineStr">
         <is>
           <t>62</t>
         </is>
@@ -7139,16 +7243,17 @@
       </c>
       <c r="M96" s="6" t="n"/>
       <c r="N96" s="6" t="n"/>
-      <c r="O96" s="7" t="n"/>
-      <c r="P96" s="6" t="n"/>
+      <c r="O96" s="6" t="n"/>
+      <c r="P96" s="7" t="n"/>
       <c r="Q96" s="6" t="n"/>
-      <c r="R96" s="7" t="n"/>
-      <c r="S96" s="3" t="inlineStr">
+      <c r="R96" s="6" t="n"/>
+      <c r="S96" s="7" t="n"/>
+      <c r="T96" s="3" t="inlineStr">
         <is>
           <t>913</t>
         </is>
       </c>
-      <c r="T96" s="3" t="inlineStr">
+      <c r="U96" s="3" t="inlineStr">
         <is>
           <t>915</t>
         </is>
@@ -7209,16 +7314,17 @@
       </c>
       <c r="M97" s="6" t="n"/>
       <c r="N97" s="6" t="n"/>
-      <c r="O97" s="7" t="n"/>
-      <c r="P97" s="6" t="n"/>
+      <c r="O97" s="6" t="n"/>
+      <c r="P97" s="7" t="n"/>
       <c r="Q97" s="6" t="n"/>
-      <c r="R97" s="7" t="n"/>
-      <c r="S97" s="3" t="inlineStr">
+      <c r="R97" s="6" t="n"/>
+      <c r="S97" s="7" t="n"/>
+      <c r="T97" s="3" t="inlineStr">
         <is>
           <t>912</t>
         </is>
       </c>
-      <c r="T97" s="3" t="inlineStr">
+      <c r="U97" s="3" t="inlineStr">
         <is>
           <t>914</t>
         </is>
@@ -7279,16 +7385,17 @@
       </c>
       <c r="M98" s="6" t="n"/>
       <c r="N98" s="6" t="n"/>
-      <c r="O98" s="7" t="n"/>
-      <c r="P98" s="6" t="n"/>
+      <c r="O98" s="6" t="n"/>
+      <c r="P98" s="7" t="n"/>
       <c r="Q98" s="6" t="n"/>
-      <c r="R98" s="7" t="n"/>
-      <c r="S98" s="3" t="inlineStr">
+      <c r="R98" s="6" t="n"/>
+      <c r="S98" s="7" t="n"/>
+      <c r="T98" s="3" t="inlineStr">
         <is>
           <t>754</t>
         </is>
       </c>
-      <c r="T98" s="3" t="inlineStr">
+      <c r="U98" s="3" t="inlineStr">
         <is>
           <t>755</t>
         </is>
@@ -7349,16 +7456,17 @@
       </c>
       <c r="M99" s="6" t="n"/>
       <c r="N99" s="6" t="n"/>
-      <c r="O99" s="7" t="n"/>
-      <c r="P99" s="6" t="n"/>
+      <c r="O99" s="6" t="n"/>
+      <c r="P99" s="7" t="n"/>
       <c r="Q99" s="6" t="n"/>
-      <c r="R99" s="7" t="n"/>
-      <c r="S99" s="3" t="inlineStr">
+      <c r="R99" s="6" t="n"/>
+      <c r="S99" s="7" t="n"/>
+      <c r="T99" s="3" t="inlineStr">
         <is>
           <t>923</t>
         </is>
       </c>
-      <c r="T99" s="3" t="inlineStr">
+      <c r="U99" s="3" t="inlineStr">
         <is>
           <t>925</t>
         </is>
@@ -7415,16 +7523,17 @@
       </c>
       <c r="M100" s="6" t="n"/>
       <c r="N100" s="6" t="n"/>
-      <c r="O100" s="7" t="n"/>
-      <c r="P100" s="6" t="n"/>
+      <c r="O100" s="6" t="n"/>
+      <c r="P100" s="7" t="n"/>
       <c r="Q100" s="6" t="n"/>
-      <c r="R100" s="7" t="n"/>
-      <c r="S100" s="3" t="inlineStr">
+      <c r="R100" s="6" t="n"/>
+      <c r="S100" s="7" t="n"/>
+      <c r="T100" s="3" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="T100" s="3" t="inlineStr">
+      <c r="U100" s="3" t="inlineStr">
         <is>
           <t>481</t>
         </is>
@@ -7485,16 +7594,17 @@
       </c>
       <c r="M101" s="6" t="n"/>
       <c r="N101" s="6" t="n"/>
-      <c r="O101" s="7" t="n"/>
-      <c r="P101" s="6" t="n"/>
+      <c r="O101" s="6" t="n"/>
+      <c r="P101" s="7" t="n"/>
       <c r="Q101" s="6" t="n"/>
-      <c r="R101" s="7" t="n"/>
-      <c r="S101" s="3" t="inlineStr">
+      <c r="R101" s="6" t="n"/>
+      <c r="S101" s="7" t="n"/>
+      <c r="T101" s="3" t="inlineStr">
         <is>
           <t>733</t>
         </is>
       </c>
-      <c r="T101" s="3" t="inlineStr">
+      <c r="U101" s="3" t="inlineStr">
         <is>
           <t>734</t>
         </is>
@@ -7555,16 +7665,17 @@
       </c>
       <c r="M102" s="6" t="n"/>
       <c r="N102" s="6" t="n"/>
-      <c r="O102" s="7" t="n"/>
-      <c r="P102" s="6" t="n"/>
+      <c r="O102" s="6" t="n"/>
+      <c r="P102" s="7" t="n"/>
       <c r="Q102" s="6" t="n"/>
-      <c r="R102" s="7" t="n"/>
-      <c r="S102" s="3" t="inlineStr">
+      <c r="R102" s="6" t="n"/>
+      <c r="S102" s="7" t="n"/>
+      <c r="T102" s="3" t="inlineStr">
         <is>
           <t>581</t>
         </is>
       </c>
-      <c r="T102" s="3" t="inlineStr">
+      <c r="U102" s="3" t="inlineStr">
         <is>
           <t>582</t>
         </is>
@@ -7625,16 +7736,17 @@
       </c>
       <c r="M103" s="6" t="n"/>
       <c r="N103" s="6" t="n"/>
-      <c r="O103" s="7" t="n"/>
-      <c r="P103" s="6" t="n"/>
+      <c r="O103" s="6" t="n"/>
+      <c r="P103" s="7" t="n"/>
       <c r="Q103" s="6" t="n"/>
-      <c r="R103" s="7" t="n"/>
-      <c r="S103" s="3" t="inlineStr">
+      <c r="R103" s="6" t="n"/>
+      <c r="S103" s="7" t="n"/>
+      <c r="T103" s="3" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="T103" s="3" t="inlineStr">
+      <c r="U103" s="3" t="inlineStr">
         <is>
           <t>77</t>
         </is>
@@ -7695,16 +7807,17 @@
       </c>
       <c r="M104" s="6" t="n"/>
       <c r="N104" s="6" t="n"/>
-      <c r="O104" s="7" t="n"/>
-      <c r="P104" s="6" t="n"/>
+      <c r="O104" s="6" t="n"/>
+      <c r="P104" s="7" t="n"/>
       <c r="Q104" s="6" t="n"/>
-      <c r="R104" s="7" t="n"/>
-      <c r="S104" s="3" t="inlineStr">
+      <c r="R104" s="6" t="n"/>
+      <c r="S104" s="7" t="n"/>
+      <c r="T104" s="3" t="inlineStr">
         <is>
           <t>778</t>
         </is>
       </c>
-      <c r="T104" s="3" t="inlineStr">
+      <c r="U104" s="3" t="inlineStr">
         <is>
           <t>779</t>
         </is>
@@ -7765,16 +7878,17 @@
       </c>
       <c r="M105" s="6" t="n"/>
       <c r="N105" s="6" t="n"/>
-      <c r="O105" s="7" t="n"/>
-      <c r="P105" s="6" t="n"/>
+      <c r="O105" s="6" t="n"/>
+      <c r="P105" s="7" t="n"/>
       <c r="Q105" s="6" t="n"/>
-      <c r="R105" s="7" t="n"/>
-      <c r="S105" s="3" t="inlineStr">
+      <c r="R105" s="6" t="n"/>
+      <c r="S105" s="7" t="n"/>
+      <c r="T105" s="3" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="T105" s="3" t="inlineStr">
+      <c r="U105" s="3" t="inlineStr">
         <is>
           <t>163</t>
         </is>
@@ -7835,16 +7949,17 @@
       </c>
       <c r="M106" s="6" t="n"/>
       <c r="N106" s="6" t="n"/>
-      <c r="O106" s="7" t="n"/>
-      <c r="P106" s="6" t="n"/>
+      <c r="O106" s="6" t="n"/>
+      <c r="P106" s="7" t="n"/>
       <c r="Q106" s="6" t="n"/>
-      <c r="R106" s="7" t="n"/>
-      <c r="S106" s="3" t="inlineStr">
+      <c r="R106" s="6" t="n"/>
+      <c r="S106" s="7" t="n"/>
+      <c r="T106" s="3" t="inlineStr">
         <is>
           <t>701</t>
         </is>
       </c>
-      <c r="T106" s="3" t="inlineStr">
+      <c r="U106" s="3" t="inlineStr">
         <is>
           <t>702</t>
         </is>
@@ -7901,16 +8016,17 @@
       </c>
       <c r="M107" s="6" t="n"/>
       <c r="N107" s="6" t="n"/>
-      <c r="O107" s="7" t="n"/>
-      <c r="P107" s="6" t="n"/>
+      <c r="O107" s="6" t="n"/>
+      <c r="P107" s="7" t="n"/>
       <c r="Q107" s="6" t="n"/>
-      <c r="R107" s="7" t="n"/>
-      <c r="S107" s="3" t="inlineStr">
+      <c r="R107" s="6" t="n"/>
+      <c r="S107" s="7" t="n"/>
+      <c r="T107" s="3" t="inlineStr">
         <is>
           <t>466</t>
         </is>
       </c>
-      <c r="T107" s="3" t="inlineStr">
+      <c r="U107" s="3" t="inlineStr">
         <is>
           <t>467</t>
         </is>
@@ -7971,16 +8087,17 @@
       </c>
       <c r="M108" s="6" t="n"/>
       <c r="N108" s="6" t="n"/>
-      <c r="O108" s="7" t="n"/>
-      <c r="P108" s="6" t="n"/>
+      <c r="O108" s="6" t="n"/>
+      <c r="P108" s="7" t="n"/>
       <c r="Q108" s="6" t="n"/>
-      <c r="R108" s="7" t="n"/>
-      <c r="S108" s="3" t="inlineStr">
+      <c r="R108" s="6" t="n"/>
+      <c r="S108" s="7" t="n"/>
+      <c r="T108" s="3" t="inlineStr">
         <is>
           <t>958</t>
         </is>
       </c>
-      <c r="T108" s="3" t="inlineStr">
+      <c r="U108" s="3" t="inlineStr">
         <is>
           <t>960</t>
         </is>
@@ -8041,16 +8158,17 @@
       </c>
       <c r="M109" s="6" t="n"/>
       <c r="N109" s="6" t="n"/>
-      <c r="O109" s="7" t="n"/>
-      <c r="P109" s="6" t="n"/>
+      <c r="O109" s="6" t="n"/>
+      <c r="P109" s="7" t="n"/>
       <c r="Q109" s="6" t="n"/>
-      <c r="R109" s="7" t="n"/>
-      <c r="S109" s="3" t="inlineStr">
+      <c r="R109" s="6" t="n"/>
+      <c r="S109" s="7" t="n"/>
+      <c r="T109" s="3" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="T109" s="3" t="inlineStr">
+      <c r="U109" s="3" t="inlineStr">
         <is>
           <t>151</t>
         </is>
@@ -8111,16 +8229,17 @@
       </c>
       <c r="M110" s="6" t="n"/>
       <c r="N110" s="6" t="n"/>
-      <c r="O110" s="7" t="n"/>
-      <c r="P110" s="6" t="n"/>
+      <c r="O110" s="6" t="n"/>
+      <c r="P110" s="7" t="n"/>
       <c r="Q110" s="6" t="n"/>
-      <c r="R110" s="7" t="n"/>
-      <c r="S110" s="3" t="inlineStr">
+      <c r="R110" s="6" t="n"/>
+      <c r="S110" s="7" t="n"/>
+      <c r="T110" s="3" t="inlineStr">
         <is>
           <t>488</t>
         </is>
       </c>
-      <c r="T110" s="3" t="inlineStr">
+      <c r="U110" s="3" t="inlineStr">
         <is>
           <t>489</t>
         </is>
@@ -8181,16 +8300,17 @@
       </c>
       <c r="M111" s="6" t="n"/>
       <c r="N111" s="6" t="n"/>
-      <c r="O111" s="7" t="n"/>
-      <c r="P111" s="6" t="n"/>
+      <c r="O111" s="6" t="n"/>
+      <c r="P111" s="7" t="n"/>
       <c r="Q111" s="6" t="n"/>
-      <c r="R111" s="7" t="n"/>
-      <c r="S111" s="3" t="inlineStr">
+      <c r="R111" s="6" t="n"/>
+      <c r="S111" s="7" t="n"/>
+      <c r="T111" s="3" t="inlineStr">
         <is>
           <t>894</t>
         </is>
       </c>
-      <c r="T111" s="3" t="inlineStr">
+      <c r="U111" s="3" t="inlineStr">
         <is>
           <t>896</t>
         </is>
@@ -8251,16 +8371,17 @@
       </c>
       <c r="M112" s="6" t="n"/>
       <c r="N112" s="6" t="n"/>
-      <c r="O112" s="7" t="n"/>
-      <c r="P112" s="6" t="n"/>
+      <c r="O112" s="6" t="n"/>
+      <c r="P112" s="7" t="n"/>
       <c r="Q112" s="6" t="n"/>
-      <c r="R112" s="7" t="n"/>
-      <c r="S112" s="3" t="inlineStr">
+      <c r="R112" s="6" t="n"/>
+      <c r="S112" s="7" t="n"/>
+      <c r="T112" s="3" t="inlineStr">
         <is>
           <t>409</t>
         </is>
       </c>
-      <c r="T112" s="3" t="inlineStr">
+      <c r="U112" s="3" t="inlineStr">
         <is>
           <t>410</t>
         </is>
@@ -8321,16 +8442,17 @@
       </c>
       <c r="M113" s="6" t="n"/>
       <c r="N113" s="6" t="n"/>
-      <c r="O113" s="7" t="n"/>
-      <c r="P113" s="6" t="n"/>
+      <c r="O113" s="6" t="n"/>
+      <c r="P113" s="7" t="n"/>
       <c r="Q113" s="6" t="n"/>
-      <c r="R113" s="7" t="n"/>
-      <c r="S113" s="3" t="inlineStr">
+      <c r="R113" s="6" t="n"/>
+      <c r="S113" s="7" t="n"/>
+      <c r="T113" s="3" t="inlineStr">
         <is>
           <t>278</t>
         </is>
       </c>
-      <c r="T113" s="3" t="inlineStr">
+      <c r="U113" s="3" t="inlineStr">
         <is>
           <t>279</t>
         </is>
@@ -8387,16 +8509,17 @@
       </c>
       <c r="M114" s="6" t="n"/>
       <c r="N114" s="6" t="n"/>
-      <c r="O114" s="7" t="n"/>
-      <c r="P114" s="6" t="n"/>
+      <c r="O114" s="6" t="n"/>
+      <c r="P114" s="7" t="n"/>
       <c r="Q114" s="6" t="n"/>
-      <c r="R114" s="7" t="n"/>
-      <c r="S114" s="3" t="inlineStr">
+      <c r="R114" s="6" t="n"/>
+      <c r="S114" s="7" t="n"/>
+      <c r="T114" s="3" t="inlineStr">
         <is>
           <t>652</t>
         </is>
       </c>
-      <c r="T114" s="3" t="inlineStr">
+      <c r="U114" s="3" t="inlineStr">
         <is>
           <t>653</t>
         </is>
@@ -8457,16 +8580,17 @@
       </c>
       <c r="M115" s="6" t="n"/>
       <c r="N115" s="6" t="n"/>
-      <c r="O115" s="7" t="n"/>
-      <c r="P115" s="6" t="n"/>
+      <c r="O115" s="6" t="n"/>
+      <c r="P115" s="7" t="n"/>
       <c r="Q115" s="6" t="n"/>
-      <c r="R115" s="7" t="n"/>
-      <c r="S115" s="3" t="inlineStr">
+      <c r="R115" s="6" t="n"/>
+      <c r="S115" s="7" t="n"/>
+      <c r="T115" s="3" t="inlineStr">
         <is>
           <t>381</t>
         </is>
       </c>
-      <c r="T115" s="3" t="inlineStr">
+      <c r="U115" s="3" t="inlineStr">
         <is>
           <t>382</t>
         </is>
@@ -8527,16 +8651,17 @@
       </c>
       <c r="M116" s="6" t="n"/>
       <c r="N116" s="6" t="n"/>
-      <c r="O116" s="7" t="n"/>
-      <c r="P116" s="6" t="n"/>
+      <c r="O116" s="6" t="n"/>
+      <c r="P116" s="7" t="n"/>
       <c r="Q116" s="6" t="n"/>
-      <c r="R116" s="7" t="n"/>
-      <c r="S116" s="3" t="inlineStr">
+      <c r="R116" s="6" t="n"/>
+      <c r="S116" s="7" t="n"/>
+      <c r="T116" s="3" t="inlineStr">
         <is>
           <t>378</t>
         </is>
       </c>
-      <c r="T116" s="3" t="inlineStr">
+      <c r="U116" s="3" t="inlineStr">
         <is>
           <t>379</t>
         </is>
@@ -8593,16 +8718,17 @@
       </c>
       <c r="M117" s="6" t="n"/>
       <c r="N117" s="6" t="n"/>
-      <c r="O117" s="7" t="n"/>
-      <c r="P117" s="6" t="n"/>
+      <c r="O117" s="6" t="n"/>
+      <c r="P117" s="7" t="n"/>
       <c r="Q117" s="6" t="n"/>
-      <c r="R117" s="7" t="n"/>
-      <c r="S117" s="3" t="inlineStr">
+      <c r="R117" s="6" t="n"/>
+      <c r="S117" s="7" t="n"/>
+      <c r="T117" s="3" t="inlineStr">
         <is>
           <t>406</t>
         </is>
       </c>
-      <c r="T117" s="3" t="inlineStr">
+      <c r="U117" s="3" t="inlineStr">
         <is>
           <t>407</t>
         </is>
@@ -8663,16 +8789,17 @@
       </c>
       <c r="M118" s="6" t="n"/>
       <c r="N118" s="6" t="n"/>
-      <c r="O118" s="7" t="n"/>
-      <c r="P118" s="6" t="n"/>
+      <c r="O118" s="6" t="n"/>
+      <c r="P118" s="7" t="n"/>
       <c r="Q118" s="6" t="n"/>
-      <c r="R118" s="7" t="n"/>
-      <c r="S118" s="3" t="inlineStr">
+      <c r="R118" s="6" t="n"/>
+      <c r="S118" s="7" t="n"/>
+      <c r="T118" s="3" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="T118" s="3" t="inlineStr">
+      <c r="U118" s="3" t="inlineStr">
         <is>
           <t>444</t>
         </is>
@@ -8733,16 +8860,17 @@
       </c>
       <c r="M119" s="6" t="n"/>
       <c r="N119" s="6" t="n"/>
-      <c r="O119" s="7" t="n"/>
-      <c r="P119" s="6" t="n"/>
+      <c r="O119" s="6" t="n"/>
+      <c r="P119" s="7" t="n"/>
       <c r="Q119" s="6" t="n"/>
-      <c r="R119" s="7" t="n"/>
-      <c r="S119" s="3" t="inlineStr">
+      <c r="R119" s="6" t="n"/>
+      <c r="S119" s="7" t="n"/>
+      <c r="T119" s="3" t="inlineStr">
         <is>
           <t>463</t>
         </is>
       </c>
-      <c r="T119" s="3" t="inlineStr">
+      <c r="U119" s="3" t="inlineStr">
         <is>
           <t>464</t>
         </is>
@@ -8803,16 +8931,17 @@
       </c>
       <c r="M120" s="6" t="n"/>
       <c r="N120" s="6" t="n"/>
-      <c r="O120" s="7" t="n"/>
-      <c r="P120" s="6" t="n"/>
+      <c r="O120" s="6" t="n"/>
+      <c r="P120" s="7" t="n"/>
       <c r="Q120" s="6" t="n"/>
-      <c r="R120" s="7" t="n"/>
-      <c r="S120" s="3" t="inlineStr">
+      <c r="R120" s="6" t="n"/>
+      <c r="S120" s="7" t="n"/>
+      <c r="T120" s="3" t="inlineStr">
         <is>
           <t>332</t>
         </is>
       </c>
-      <c r="T120" s="3" t="inlineStr">
+      <c r="U120" s="3" t="inlineStr">
         <is>
           <t>333</t>
         </is>
@@ -8873,16 +9002,17 @@
       </c>
       <c r="M121" s="6" t="n"/>
       <c r="N121" s="6" t="n"/>
-      <c r="O121" s="7" t="n"/>
-      <c r="P121" s="6" t="n"/>
+      <c r="O121" s="6" t="n"/>
+      <c r="P121" s="7" t="n"/>
       <c r="Q121" s="6" t="n"/>
-      <c r="R121" s="7" t="n"/>
-      <c r="S121" s="3" t="inlineStr">
+      <c r="R121" s="6" t="n"/>
+      <c r="S121" s="7" t="n"/>
+      <c r="T121" s="3" t="inlineStr">
         <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="T121" s="3" t="inlineStr">
+      <c r="U121" s="3" t="inlineStr">
         <is>
           <t>1019</t>
         </is>
@@ -8939,16 +9069,17 @@
       </c>
       <c r="M122" s="6" t="n"/>
       <c r="N122" s="6" t="n"/>
-      <c r="O122" s="7" t="n"/>
-      <c r="P122" s="6" t="n"/>
+      <c r="O122" s="6" t="n"/>
+      <c r="P122" s="7" t="n"/>
       <c r="Q122" s="6" t="n"/>
-      <c r="R122" s="7" t="n"/>
-      <c r="S122" s="3" t="inlineStr">
+      <c r="R122" s="6" t="n"/>
+      <c r="S122" s="7" t="n"/>
+      <c r="T122" s="3" t="inlineStr">
         <is>
           <t>882</t>
         </is>
       </c>
-      <c r="T122" s="3" t="inlineStr">
+      <c r="U122" s="3" t="inlineStr">
         <is>
           <t>884</t>
         </is>
@@ -9005,16 +9136,17 @@
       </c>
       <c r="M123" s="6" t="n"/>
       <c r="N123" s="6" t="n"/>
-      <c r="O123" s="7" t="n"/>
-      <c r="P123" s="6" t="n"/>
+      <c r="O123" s="6" t="n"/>
+      <c r="P123" s="7" t="n"/>
       <c r="Q123" s="6" t="n"/>
-      <c r="R123" s="7" t="n"/>
-      <c r="S123" s="3" t="inlineStr">
+      <c r="R123" s="6" t="n"/>
+      <c r="S123" s="7" t="n"/>
+      <c r="T123" s="3" t="inlineStr">
         <is>
           <t>468</t>
         </is>
       </c>
-      <c r="T123" s="3" t="inlineStr">
+      <c r="U123" s="3" t="inlineStr">
         <is>
           <t>469</t>
         </is>
@@ -9075,16 +9207,17 @@
       </c>
       <c r="M124" s="6" t="n"/>
       <c r="N124" s="6" t="n"/>
-      <c r="O124" s="7" t="n"/>
-      <c r="P124" s="6" t="n"/>
+      <c r="O124" s="6" t="n"/>
+      <c r="P124" s="7" t="n"/>
       <c r="Q124" s="6" t="n"/>
-      <c r="R124" s="7" t="n"/>
-      <c r="S124" s="3" t="inlineStr">
+      <c r="R124" s="6" t="n"/>
+      <c r="S124" s="7" t="n"/>
+      <c r="T124" s="3" t="inlineStr">
         <is>
           <t>418</t>
         </is>
       </c>
-      <c r="T124" s="3" t="inlineStr">
+      <c r="U124" s="3" t="inlineStr">
         <is>
           <t>419</t>
         </is>
@@ -9141,16 +9274,17 @@
       </c>
       <c r="M125" s="6" t="n"/>
       <c r="N125" s="6" t="n"/>
-      <c r="O125" s="7" t="n"/>
-      <c r="P125" s="6" t="n"/>
+      <c r="O125" s="6" t="n"/>
+      <c r="P125" s="7" t="n"/>
       <c r="Q125" s="6" t="n"/>
-      <c r="R125" s="7" t="n"/>
-      <c r="S125" s="3" t="inlineStr">
+      <c r="R125" s="6" t="n"/>
+      <c r="S125" s="7" t="n"/>
+      <c r="T125" s="3" t="inlineStr">
         <is>
           <t>634</t>
         </is>
       </c>
-      <c r="T125" s="3" t="inlineStr">
+      <c r="U125" s="3" t="inlineStr">
         <is>
           <t>635</t>
         </is>
@@ -9207,16 +9341,17 @@
       </c>
       <c r="M126" s="6" t="n"/>
       <c r="N126" s="6" t="n"/>
-      <c r="O126" s="7" t="n"/>
-      <c r="P126" s="6" t="n"/>
+      <c r="O126" s="6" t="n"/>
+      <c r="P126" s="7" t="n"/>
       <c r="Q126" s="6" t="n"/>
-      <c r="R126" s="7" t="n"/>
-      <c r="S126" s="3" t="inlineStr">
+      <c r="R126" s="6" t="n"/>
+      <c r="S126" s="7" t="n"/>
+      <c r="T126" s="3" t="inlineStr">
         <is>
           <t>467</t>
         </is>
       </c>
-      <c r="T126" s="3" t="inlineStr">
+      <c r="U126" s="3" t="inlineStr">
         <is>
           <t>468</t>
         </is>
@@ -9277,16 +9412,17 @@
       </c>
       <c r="M127" s="6" t="n"/>
       <c r="N127" s="6" t="n"/>
-      <c r="O127" s="7" t="n"/>
-      <c r="P127" s="6" t="n"/>
+      <c r="O127" s="6" t="n"/>
+      <c r="P127" s="7" t="n"/>
       <c r="Q127" s="6" t="n"/>
-      <c r="R127" s="7" t="n"/>
-      <c r="S127" s="3" t="inlineStr">
+      <c r="R127" s="6" t="n"/>
+      <c r="S127" s="7" t="n"/>
+      <c r="T127" s="3" t="inlineStr">
         <is>
           <t>571</t>
         </is>
       </c>
-      <c r="T127" s="3" t="inlineStr">
+      <c r="U127" s="3" t="inlineStr">
         <is>
           <t>572</t>
         </is>
@@ -9347,16 +9483,17 @@
       </c>
       <c r="M128" s="6" t="n"/>
       <c r="N128" s="6" t="n"/>
-      <c r="O128" s="7" t="n"/>
-      <c r="P128" s="6" t="n"/>
+      <c r="O128" s="6" t="n"/>
+      <c r="P128" s="7" t="n"/>
       <c r="Q128" s="6" t="n"/>
-      <c r="R128" s="7" t="n"/>
-      <c r="S128" s="3" t="inlineStr">
+      <c r="R128" s="6" t="n"/>
+      <c r="S128" s="7" t="n"/>
+      <c r="T128" s="3" t="inlineStr">
         <is>
           <t>143</t>
         </is>
       </c>
-      <c r="T128" s="3" t="inlineStr">
+      <c r="U128" s="3" t="inlineStr">
         <is>
           <t>144</t>
         </is>
@@ -9413,16 +9550,17 @@
       </c>
       <c r="M129" s="6" t="n"/>
       <c r="N129" s="6" t="n"/>
-      <c r="O129" s="7" t="n"/>
-      <c r="P129" s="6" t="n"/>
+      <c r="O129" s="6" t="n"/>
+      <c r="P129" s="7" t="n"/>
       <c r="Q129" s="6" t="n"/>
-      <c r="R129" s="7" t="n"/>
-      <c r="S129" s="3" t="inlineStr">
+      <c r="R129" s="6" t="n"/>
+      <c r="S129" s="7" t="n"/>
+      <c r="T129" s="3" t="inlineStr">
         <is>
           <t>425</t>
         </is>
       </c>
-      <c r="T129" s="3" t="inlineStr">
+      <c r="U129" s="3" t="inlineStr">
         <is>
           <t>426</t>
         </is>
@@ -9483,16 +9621,17 @@
       </c>
       <c r="M130" s="6" t="n"/>
       <c r="N130" s="6" t="n"/>
-      <c r="O130" s="7" t="n"/>
-      <c r="P130" s="6" t="n"/>
+      <c r="O130" s="6" t="n"/>
+      <c r="P130" s="7" t="n"/>
       <c r="Q130" s="6" t="n"/>
-      <c r="R130" s="7" t="n"/>
-      <c r="S130" s="3" t="inlineStr">
+      <c r="R130" s="6" t="n"/>
+      <c r="S130" s="7" t="n"/>
+      <c r="T130" s="3" t="inlineStr">
         <is>
           <t>618</t>
         </is>
       </c>
-      <c r="T130" s="3" t="inlineStr">
+      <c r="U130" s="3" t="inlineStr">
         <is>
           <t>619</t>
         </is>
@@ -9553,16 +9692,17 @@
       </c>
       <c r="M131" s="6" t="n"/>
       <c r="N131" s="6" t="n"/>
-      <c r="O131" s="7" t="n"/>
-      <c r="P131" s="6" t="n"/>
+      <c r="O131" s="6" t="n"/>
+      <c r="P131" s="7" t="n"/>
       <c r="Q131" s="6" t="n"/>
-      <c r="R131" s="7" t="n"/>
-      <c r="S131" s="3" t="inlineStr">
+      <c r="R131" s="6" t="n"/>
+      <c r="S131" s="7" t="n"/>
+      <c r="T131" s="3" t="inlineStr">
         <is>
           <t>834</t>
         </is>
       </c>
-      <c r="T131" s="3" t="inlineStr">
+      <c r="U131" s="3" t="inlineStr">
         <is>
           <t>836</t>
         </is>
@@ -9623,16 +9763,17 @@
       </c>
       <c r="M132" s="6" t="n"/>
       <c r="N132" s="6" t="n"/>
-      <c r="O132" s="7" t="n"/>
-      <c r="P132" s="6" t="n"/>
+      <c r="O132" s="6" t="n"/>
+      <c r="P132" s="7" t="n"/>
       <c r="Q132" s="6" t="n"/>
-      <c r="R132" s="7" t="n"/>
-      <c r="S132" s="3" t="inlineStr">
+      <c r="R132" s="6" t="n"/>
+      <c r="S132" s="7" t="n"/>
+      <c r="T132" s="3" t="inlineStr">
         <is>
           <t>550</t>
         </is>
       </c>
-      <c r="T132" s="3" t="inlineStr">
+      <c r="U132" s="3" t="inlineStr">
         <is>
           <t>551</t>
         </is>
@@ -9693,16 +9834,17 @@
       </c>
       <c r="M133" s="6" t="n"/>
       <c r="N133" s="6" t="n"/>
-      <c r="O133" s="7" t="n"/>
-      <c r="P133" s="6" t="n"/>
+      <c r="O133" s="6" t="n"/>
+      <c r="P133" s="7" t="n"/>
       <c r="Q133" s="6" t="n"/>
-      <c r="R133" s="7" t="n"/>
-      <c r="S133" s="3" t="inlineStr">
+      <c r="R133" s="6" t="n"/>
+      <c r="S133" s="7" t="n"/>
+      <c r="T133" s="3" t="inlineStr">
         <is>
           <t>549</t>
         </is>
       </c>
-      <c r="T133" s="3" t="inlineStr">
+      <c r="U133" s="3" t="inlineStr">
         <is>
           <t>550</t>
         </is>
@@ -9759,16 +9901,17 @@
       </c>
       <c r="M134" s="6" t="n"/>
       <c r="N134" s="6" t="n"/>
-      <c r="O134" s="7" t="n"/>
-      <c r="P134" s="6" t="n"/>
+      <c r="O134" s="6" t="n"/>
+      <c r="P134" s="7" t="n"/>
       <c r="Q134" s="6" t="n"/>
-      <c r="R134" s="7" t="n"/>
-      <c r="S134" s="3" t="inlineStr">
+      <c r="R134" s="6" t="n"/>
+      <c r="S134" s="7" t="n"/>
+      <c r="T134" s="3" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="T134" s="3" t="inlineStr">
+      <c r="U134" s="3" t="inlineStr">
         <is>
           <t>598</t>
         </is>
@@ -9829,16 +9972,17 @@
       </c>
       <c r="M135" s="6" t="n"/>
       <c r="N135" s="6" t="n"/>
-      <c r="O135" s="7" t="n"/>
-      <c r="P135" s="6" t="n"/>
+      <c r="O135" s="6" t="n"/>
+      <c r="P135" s="7" t="n"/>
       <c r="Q135" s="6" t="n"/>
-      <c r="R135" s="7" t="n"/>
-      <c r="S135" s="3" t="inlineStr">
+      <c r="R135" s="6" t="n"/>
+      <c r="S135" s="7" t="n"/>
+      <c r="T135" s="3" t="inlineStr">
         <is>
           <t>510</t>
         </is>
       </c>
-      <c r="T135" s="3" t="inlineStr">
+      <c r="U135" s="3" t="inlineStr">
         <is>
           <t>511</t>
         </is>
@@ -9899,16 +10043,17 @@
       </c>
       <c r="M136" s="6" t="n"/>
       <c r="N136" s="6" t="n"/>
-      <c r="O136" s="7" t="n"/>
-      <c r="P136" s="6" t="n"/>
+      <c r="O136" s="6" t="n"/>
+      <c r="P136" s="7" t="n"/>
       <c r="Q136" s="6" t="n"/>
-      <c r="R136" s="7" t="n"/>
-      <c r="S136" s="3" t="inlineStr">
+      <c r="R136" s="6" t="n"/>
+      <c r="S136" s="7" t="n"/>
+      <c r="T136" s="3" t="inlineStr">
         <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="T136" s="3" t="inlineStr">
+      <c r="U136" s="3" t="inlineStr">
         <is>
           <t>1018</t>
         </is>
@@ -9969,16 +10114,17 @@
       </c>
       <c r="M137" s="6" t="n"/>
       <c r="N137" s="6" t="n"/>
-      <c r="O137" s="7" t="n"/>
-      <c r="P137" s="6" t="n"/>
+      <c r="O137" s="6" t="n"/>
+      <c r="P137" s="7" t="n"/>
       <c r="Q137" s="6" t="n"/>
-      <c r="R137" s="7" t="n"/>
-      <c r="S137" s="3" t="inlineStr">
+      <c r="R137" s="6" t="n"/>
+      <c r="S137" s="7" t="n"/>
+      <c r="T137" s="3" t="inlineStr">
         <is>
           <t>804</t>
         </is>
       </c>
-      <c r="T137" s="3" t="inlineStr">
+      <c r="U137" s="3" t="inlineStr">
         <is>
           <t>806</t>
         </is>
@@ -10039,16 +10185,17 @@
       </c>
       <c r="M138" s="6" t="n"/>
       <c r="N138" s="6" t="n"/>
-      <c r="O138" s="7" t="n"/>
-      <c r="P138" s="6" t="n"/>
+      <c r="O138" s="6" t="n"/>
+      <c r="P138" s="7" t="n"/>
       <c r="Q138" s="6" t="n"/>
-      <c r="R138" s="7" t="n"/>
-      <c r="S138" s="3" t="inlineStr">
+      <c r="R138" s="6" t="n"/>
+      <c r="S138" s="7" t="n"/>
+      <c r="T138" s="3" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="T138" s="3" t="inlineStr">
+      <c r="U138" s="3" t="inlineStr">
         <is>
           <t>1002</t>
         </is>
@@ -10109,16 +10256,17 @@
       </c>
       <c r="M139" s="6" t="n"/>
       <c r="N139" s="6" t="n"/>
-      <c r="O139" s="7" t="n"/>
-      <c r="P139" s="6" t="n"/>
+      <c r="O139" s="6" t="n"/>
+      <c r="P139" s="7" t="n"/>
       <c r="Q139" s="6" t="n"/>
-      <c r="R139" s="7" t="n"/>
-      <c r="S139" s="3" t="inlineStr">
+      <c r="R139" s="6" t="n"/>
+      <c r="S139" s="7" t="n"/>
+      <c r="T139" s="3" t="inlineStr">
         <is>
           <t>753</t>
         </is>
       </c>
-      <c r="T139" s="3" t="inlineStr">
+      <c r="U139" s="3" t="inlineStr">
         <is>
           <t>754</t>
         </is>
@@ -10179,23 +10327,24 @@
       </c>
       <c r="M140" s="6" t="n"/>
       <c r="N140" s="6" t="n"/>
-      <c r="O140" s="7" t="n"/>
-      <c r="P140" s="6" t="n"/>
+      <c r="O140" s="6" t="n"/>
+      <c r="P140" s="7" t="n"/>
       <c r="Q140" s="6" t="n"/>
-      <c r="R140" s="7" t="n"/>
-      <c r="S140" s="3" t="inlineStr">
+      <c r="R140" s="6" t="n"/>
+      <c r="S140" s="7" t="n"/>
+      <c r="T140" s="3" t="inlineStr">
         <is>
           <t>874</t>
         </is>
       </c>
-      <c r="T140" s="3" t="inlineStr">
+      <c r="U140" s="3" t="inlineStr">
         <is>
           <t>876</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T140"/>
+  <autoFilter ref="A1:U140"/>
   <dataValidations count="1">
     <dataValidation sqref="M2 M3 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 M46 M47 M48 M49 M50 M51 M52 M53 M54 M55 M56 M57 M58 M59 M60 M61 M62 M63 M64 M65 M66 M67 M68 M69 M70 M71 M72 M73 M74 M75 M76 M77 M78 M79 M80 M81 M82 M83 M84 M85 M86 M87 M88 M89 M90 M91 M92 M93 M94 M95 M96 M97 M98 M99 M100 M101 M102 M103 M104 M105 M106 M107 M108 M109 M110 M111 M112 M113 M114 M115 M116 M117 M118 M119 M120 M121 M122 M123 M124 M125 M126 M127 M128 M129 M130 M131 M132 M133 M134 M135 M136 M137 M138 M139 M140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Actual rank" prompt="What the program website or profile shows today. Leave blank to decide later." type="list">
       <formula1>"assistant,associate,full,emeritus,adjunct or lecturer,left the program,unclear"</formula1>
@@ -10356,93 +10505,94 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId242"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10454,7 +10604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -10497,119 +10647,136 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>The options</t>
+          <t>ORCID (if shown)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>assistant / associate / full   their tenure-line rank today. Picking the same rank that is on file records that it was checked, so the person is not raised again for seven years.</t>
+          <t>If the faculty page shows an ORCID (a 16-digit id like 0000-0002-1825-0097, often as a green icon or a link to orcid.org), copy it in. Skip it if the page does not show one; do not search for it elsewhere. This is the one identifier we cannot get any other way, and it is worth filling in even on rows where you leave the rank blank.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>emeritus                        retired with the title. They come off the site.</t>
-        </is>
-      </c>
+      <c r="A9" s="15" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>adjunct or lecturer             not a tenure-line post (lecturer, instructor, professor of practice, adjunct, research or clinical). They come off the site; the roster tracks tenure-line faculty only.</t>
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>The options</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>left the program                no longer at this program. Note where they went if you can see it.</t>
+          <t>assistant / associate / full   their tenure-line rank today. Picking the same rank that is on file records that it was checked, so the person is not raised again for seven years.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>unclear                         you looked and could not tell. Say why in Notes.</t>
+          <t>emeritus                        retired with the title. They come off the site.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr"/>
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>adjunct or lecturer             not a tenure-line post (lecturer, instructor, professor of practice, adjunct, research or clinical). They come off the site; the roster tracks tenure-line faculty only.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Reading the evidence columns</t>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>left the program                no longer at this program. Note where they went if you can see it.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
+          <t>unclear                         you looked and could not tell. Say why in Notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Reading the evidence columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
           <t>Years / Basis          how long we think they have held the rank, and why we think so. 'rank start not on record' means we are going by years since the PhD.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Scholar profile says   the affiliation line on their profile, exactly as written. If it says 'Associate Professor' and Rank on file says 'assistant', that is your answer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Pct in rank            their citation count as a percentile among the people we hold at the same rank. 0.98 for an assistant professor is a strong hint the rank is stale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>Bands</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="15" t="inlineStr">
         <is>
+          <t>Pct in rank            their citation count as a percentile among the people we hold at the same rank. 0.98 for an assistant professor is a strong hint the rank is stale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Bands</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
           <t>A  14 or more years. Almost certainly a stale rank, or not a tenure-track post at all.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>B  10 to 13 years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>C  7 to 9 years.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>When you are done</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>C  7 to 9 years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>When you are done</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>python -m pipeline.import_rank_review data/review/rank_review.xlsx</t>
         </is>

--- a/data/review/rank_review.xlsx
+++ b/data/review/rank_review.xlsx
@@ -860,7 +860,7 @@
         <v>118</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="5" t="inlineStr">
@@ -927,7 +927,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="5" t="inlineStr">
@@ -2749,7 +2749,7 @@
         <v>89</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>53</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="K44" s="3" t="n"/>
       <c r="L44" s="5" t="inlineStr">
@@ -4985,7 +4985,7 @@
         <v>68</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="K64" s="3" t="n"/>
       <c r="L64" s="5" t="inlineStr">
@@ -5407,7 +5407,7 @@
         <v>137</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="K70" s="3" t="n"/>
       <c r="L70" s="5" t="inlineStr">
@@ -5474,7 +5474,7 @@
         <v>236</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>46</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>105</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="K85" s="3" t="n"/>
       <c r="L85" s="5" t="inlineStr">
@@ -6953,7 +6953,7 @@
         <v>60</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="K92" s="3" t="n"/>
       <c r="L92" s="5" t="inlineStr">
@@ -7235,7 +7235,11 @@
       <c r="J96" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="K96" s="3" t="n"/>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -7651,7 +7655,7 @@
         <v>231</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="K102" s="5" t="inlineStr">
         <is>
@@ -8286,7 +8290,7 @@
         <v>153</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="K111" s="5" t="inlineStr">
         <is>
@@ -8428,7 +8432,7 @@
         <v>197</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>0.42</v>
+        <v>0.41</v>
       </c>
       <c r="K113" s="5" t="inlineStr">
         <is>
@@ -9052,16 +9056,20 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>University of Texas at Arlington</t>
         </is>
       </c>
       <c r="I122" s="3" t="n">
-        <v>13</v>
+        <v>256</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K122" s="3" t="n"/>
+        <v>0.47</v>
+      </c>
+      <c r="K122" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -10514,85 +10522,87 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId161"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId244"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/review/rank_review.xlsx
+++ b/data/review/rank_review.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to use this" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Review'!$A$1:$U$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Review'!$A$1:$U$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U140"/>
+  <dimension ref="A1:U100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -656,10 +656,10 @@
         </is>
       </c>
       <c r="I2" s="3" t="n">
-        <v>401</v>
+        <v>4</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.59</v>
+        <v>0.05</v>
       </c>
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="5" t="inlineStr">
@@ -726,7 +726,7 @@
         <v>84</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="5" t="inlineStr">
@@ -793,7 +793,7 @@
         <v>388</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="5" t="inlineStr">
@@ -860,7 +860,7 @@
         <v>118</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="5" t="inlineStr">
@@ -927,7 +927,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="5" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Rosanna Rivero</t>
+          <t>Elizabeth Sweet</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>University of Georgia</t>
+          <t>University of Massachusetts-Boston</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -975,26 +975,26 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>assistant 20 years after the 2006 PhD; rank start not on record</t>
+          <t>assistant 18 years after the 2008 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>College of Environment and Design, University of Georgia</t>
+          <t>University of Mass Boston Urban Planning and Community Development</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1213</v>
+        <v>1180</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
@@ -1015,12 +1015,12 @@
       <c r="S7" s="7" t="n"/>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>749</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>750</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Katherine Lieberknecht</t>
+          <t>Rachel Berney</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>University of Texas, Austin</t>
+          <t>University of Washington</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1046,26 +1046,26 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>assistant 19 years after the 2007 PhD; rank start not on record</t>
+          <t>assistant 18 years after the 2008 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>The University of Texas at Austin</t>
+          <t>University of Washington, Seattle</t>
         </is>
       </c>
       <c r="I8" s="3" t="n">
-        <v>948</v>
+        <v>477</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
@@ -1086,12 +1086,12 @@
       <c r="S8" s="7" t="n"/>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>936</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>938</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Elizabeth Sweet</t>
+          <t>Genevieve Cloutier</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>University of Massachusetts-Boston</t>
+          <t>Universite Laval</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1117,26 +1117,26 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>assistant 18 years after the 2008 PhD; rank start not on record</t>
+          <t>assistant 17 years after the 2009 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>University of Mass Boston Urban Planning and Community Development</t>
+          <t>Centre de recherche en aménagement et développement (CRAD)</t>
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>1180</v>
+        <v>1207</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
@@ -1157,12 +1157,12 @@
       <c r="S9" s="7" t="n"/>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>536</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>537</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Gabriella Carolini</t>
+          <t>Gian Claudia Sciara</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>University of Texas, Austin</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1188,26 +1188,26 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>assistant 18 years after the 2008 PhD; rank start not on record</t>
+          <t>assistant 17 years after the 2009 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>Associate Professor of Urban Planning and International Development</t>
+          <t>University of Texas</t>
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1529</v>
+        <v>859</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       <c r="S10" s="7" t="n"/>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>892</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>894</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Nina David</t>
+          <t>Lorena Estrada-Martinez</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>University of Delaware</t>
+          <t>University of Massachusetts-Boston</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1259,26 +1259,26 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>assistant 18 years after the 2008 PhD; rank start not on record</t>
+          <t>assistant 17 years after the 2009 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>University of Delaware</t>
+          <t>Associate Professor of Environment and Public Health, UPCD/SFE, UMass Boston</t>
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>482</v>
+        <v>615</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
@@ -1299,12 +1299,12 @@
       <c r="S11" s="7" t="n"/>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>743</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>744</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Rachel Berney</t>
+          <t>Rachel Meltzer</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>University of Washington</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1330,26 +1330,26 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>assistant 18 years after the 2008 PhD; rank start not on record</t>
+          <t>assistant 17 years after the 2009 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>University of Washington, Seattle</t>
+          <t>Urban Planning, Graduate School of Design, Harvard University</t>
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>477</v>
+        <v>2141</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.63</v>
+        <v>0.93</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
@@ -1370,12 +1370,12 @@
       <c r="S12" s="7" t="n"/>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>140</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>141</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Genevieve Cloutier</t>
+          <t>Scott Spak</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Universite Laval</t>
+          <t>University of Iowa</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1413,14 +1413,14 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Centre de recherche en aménagement et développement (CRAD)</t>
+          <t>University of Iowa</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1207</v>
+        <v>3248</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.83</v>
+        <v>0.97</v>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
@@ -1441,12 +1441,12 @@
       <c r="S13" s="7" t="n"/>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>696</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>537</t>
+          <t>697</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Gian Claudia Sciara</t>
+          <t>Stephen Ramos</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>University of Texas, Austin</t>
+          <t>University of Georgia</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>University of Texas</t>
+          <t>University of Georgia</t>
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>859</v>
+        <v>437</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.77</v>
+        <v>0.64</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
@@ -1512,12 +1512,12 @@
       <c r="S14" s="7" t="n"/>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>643</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>644</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Lorena Estrada-Martinez</t>
+          <t>Ryan Devlin</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>University of Massachusetts-Boston</t>
+          <t>Temple University</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1543,32 +1543,28 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>assistant 17 years after the 2009 PhD; rank start not on record</t>
+          <t>assistant 16 years after the 2010 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>Associate Professor of Environment and Public Health, UPCD/SFE, UMass Boston</t>
+          <t>(no Scholar profile)</t>
         </is>
       </c>
       <c r="I15" s="3" t="n">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.73</v>
+      </c>
+      <c r="K15" s="3" t="n"/>
       <c r="L15" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -1583,12 +1579,12 @@
       <c r="S15" s="7" t="n"/>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>374</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>375</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1596,12 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Rachel Meltzer</t>
+          <t>Alexandre Lebel</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Harvard University</t>
+          <t>Universite Laval</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1614,23 +1610,23 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>assistant 17 years after the 2009 PhD; rank start not on record</t>
+          <t>assistant 15 years after the 2011 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Urban Planning, Graduate School of Design, Harvard University</t>
+          <t>Associate professor</t>
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2141</v>
+        <v>1843</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>0.91</v>
@@ -1654,12 +1650,12 @@
       <c r="S16" s="7" t="n"/>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>541</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>542</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1667,12 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Scott Spak</t>
+          <t>Greg Newmark</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>University of Iowa</t>
+          <t>Morgan State University</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1685,26 +1681,26 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>assistant 17 years after the 2009 PhD; rank start not on record</t>
+          <t>assistant 15 years after the 2011 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>University of Iowa</t>
+          <t>Morgan State University</t>
         </is>
       </c>
       <c r="I17" s="3" t="n">
-        <v>3248</v>
+        <v>518</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.95</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
@@ -1725,12 +1721,12 @@
       <c r="S17" s="7" t="n"/>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>243</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>244</t>
         </is>
       </c>
     </row>
@@ -1742,12 +1738,12 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Stephen Ramos</t>
+          <t>Mikiko Terashima</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>University of Georgia</t>
+          <t>Dalhousie University</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1756,26 +1752,26 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>assistant 17 years after the 2009 PhD; rank start not on record</t>
+          <t>assistant 15 years after the 2011 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>University of Georgia</t>
+          <t>Dalhousie University</t>
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>437</v>
+        <v>561</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
@@ -1796,12 +1792,12 @@
       <c r="S18" s="7" t="n"/>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>91</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>92</t>
         </is>
       </c>
     </row>
@@ -1813,12 +1809,12 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Alison Smith</t>
+          <t>Lisa Bjorkman</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>University of Georgia</t>
+          <t>University of Louisville</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1827,14 +1823,14 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>assistant 16 years after the 2010 PhD; rank start not on record</t>
+          <t>assistant 14 years after the 2012 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1843,10 +1839,10 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>102</v>
+        <v>1041</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.26</v>
+        <v>0.83</v>
       </c>
       <c r="K19" s="3" t="n"/>
       <c r="L19" s="5" t="inlineStr">
@@ -1863,12 +1859,12 @@
       <c r="S19" s="7" t="n"/>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>702</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>703</t>
         </is>
       </c>
     </row>
@@ -1880,12 +1876,12 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Andrew Whittemore</t>
+          <t>Manish Shirgaokar</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>UNC</t>
+          <t>University of Colorado, Denver</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1894,26 +1890,26 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>assistant 16 years after the 2010 PhD; rank start not on record</t>
+          <t>assistant 14 years after the 2012 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>University of North Carolina, Chapel Hill</t>
+          <t>University of Colorado Denver</t>
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1168</v>
+        <v>1077</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
@@ -1934,96 +1930,100 @@
       <c r="S20" s="7" t="n"/>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>624</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>625</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Ryan Devlin</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Temple University</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>2010</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>assistant 16 years after the 2010 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>(no Scholar profile)</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>603</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M21" s="6" t="n"/>
-      <c r="N21" s="6" t="n"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="7" t="n"/>
-      <c r="Q21" s="6" t="n"/>
-      <c r="R21" s="6" t="n"/>
-      <c r="S21" s="7" t="n"/>
-      <c r="T21" s="3" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Rui Li</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>State University of New York at Albany</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>2012</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>assistant 14 years after the 2012 PhD; rank start not on record</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>University at Albany, SUNY</t>
+        </is>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>1457</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="K21" s="11" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>open site</t>
+        </is>
+      </c>
+      <c r="M21" s="12" t="n"/>
+      <c r="N21" s="12" t="n"/>
+      <c r="O21" s="12" t="n"/>
+      <c r="P21" s="13" t="n"/>
+      <c r="Q21" s="12" t="n"/>
+      <c r="R21" s="12" t="n"/>
+      <c r="S21" s="13" t="n"/>
+      <c r="T21" s="9" t="inlineStr">
+        <is>
+          <t>373</t>
+        </is>
+      </c>
+      <c r="U21" s="9" t="inlineStr">
         <is>
           <t>374</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="inlineStr">
-        <is>
-          <t>375</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Yuseung Kim</t>
+          <t>Fernando Burga</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>University of Southern Maine</t>
+          <t>University of Minnesota</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -2032,14 +2032,14 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>assistant 16 years after the 2010 PhD; rank start not on record</t>
+          <t>assistant 13 years after the 2013 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="I22" s="3" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.16</v>
+        <v>0.06</v>
       </c>
       <c r="K22" s="3" t="n"/>
       <c r="L22" s="5" t="inlineStr">
@@ -2068,29 +2068,29 @@
       <c r="S22" s="7" t="n"/>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>773</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>774</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Alexandre Lebel</t>
+          <t>Mariana Arcaya</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Universite Laval</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -2099,26 +2099,26 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>assistant 15 years after the 2011 PhD; rank start not on record</t>
+          <t>assistant 13 years after the 2013 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Associate professor</t>
+          <t>Department of Urban Studies and Planning, MIT</t>
         </is>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1843</v>
+        <v>6062</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
@@ -2139,29 +2139,29 @@
       <c r="S23" s="7" t="n"/>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>210</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>211</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Greg Newmark</t>
+          <t>Roxane Lavoie</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Morgan State University</t>
+          <t>Universite Laval</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -2170,26 +2170,26 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>assistant 15 years after the 2011 PhD; rank start not on record</t>
+          <t>assistant 13 years after the 2013 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Morgan State University</t>
+          <t>Université Laval</t>
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>518</v>
+        <v>394</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.66</v>
+        <v>0.6</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
@@ -2210,29 +2210,29 @@
       <c r="S24" s="7" t="n"/>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>539</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t>244</t>
+          <t>540</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Janice Barry</t>
+          <t>Ryan Sandwick</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>University of Waterloo, Ontario</t>
+          <t>Cal Poly, San Luis Obispo</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -2241,32 +2241,28 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>assistant 15 years after the 2011 PhD; rank start not on record</t>
+          <t>assistant 13 years after the 2013 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>School of Planning, University of Waterloo</t>
+          <t>(no Scholar profile)</t>
         </is>
       </c>
       <c r="I25" s="3" t="n">
-        <v>1181</v>
+        <v>1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="K25" s="3" t="n"/>
       <c r="L25" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -2281,29 +2277,29 @@
       <c r="S25" s="7" t="n"/>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>49</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Mikiko Terashima</t>
+          <t>Akira Drake Rodriguez</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Dalhousie University</t>
+          <t>University of Pennsylvania</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -2312,26 +2308,26 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>assistant 15 years after the 2011 PhD; rank start not on record</t>
+          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>Dalhousie University</t>
+          <t>University of Pennsylvania</t>
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>561</v>
+        <v>227</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.68</v>
+        <v>0.46</v>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
@@ -2352,29 +2348,29 @@
       <c r="S26" s="7" t="n"/>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>832</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>834</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Leia Minaker</t>
+          <t>Alina Gross</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>University of Waterloo, Ontario</t>
+          <t>Westfield State University</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -2383,32 +2379,28 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>assistant 14 years after the 2012 PhD; rank start not on record</t>
+          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>(no Scholar profile)</t>
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3775</v>
+        <v>82</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.22</v>
+      </c>
+      <c r="K27" s="3" t="n"/>
       <c r="L27" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -2423,29 +2415,29 @@
       <c r="S27" s="7" t="n"/>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1037</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Lisa Bjorkman</t>
+          <t>Allie Thomas</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>University of Louisville</t>
+          <t>UNC</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -2454,28 +2446,32 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>assistant 14 years after the 2012 PhD; rank start not on record</t>
+          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>University of North Carolina -Chapel Hill</t>
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1041</v>
+        <v>160</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K28" s="3" t="n"/>
+        <v>0.37</v>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -2490,29 +2486,29 @@
       <c r="S28" s="7" t="n"/>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>519</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>520</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Manish Shirgaokar</t>
+          <t>Jordana Maisel</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>University of Colorado, Denver</t>
+          <t>University at Buffalo, The State University of New York</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
@@ -2521,26 +2517,26 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>assistant 14 years after the 2012 PhD; rank start not on record</t>
+          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>University of Colorado Denver</t>
+          <t>University at Buffalo</t>
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1077</v>
+        <v>2470</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
@@ -2561,83 +2557,83 @@
       <c r="S29" s="7" t="n"/>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>554</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>555</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Rui Li</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>State University of New York at Albany</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>2012</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="G30" s="10" t="inlineStr">
-        <is>
-          <t>assistant 14 years after the 2012 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>University at Albany, SUNY</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="n">
-        <v>1457</v>
-      </c>
-      <c r="J30" s="9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K30" s="11" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Karilyn Crockett</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>2014</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Professor or urban history, public policy &amp; planning</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>open profile</t>
         </is>
       </c>
-      <c r="L30" s="11" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M30" s="12" t="n"/>
-      <c r="N30" s="12" t="n"/>
-      <c r="O30" s="12" t="n"/>
-      <c r="P30" s="13" t="n"/>
-      <c r="Q30" s="12" t="n"/>
-      <c r="R30" s="12" t="n"/>
-      <c r="S30" s="13" t="n"/>
-      <c r="T30" s="9" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="U30" s="9" t="inlineStr">
-        <is>
-          <t>374</t>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>open site</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="n"/>
+      <c r="N30" s="6" t="n"/>
+      <c r="O30" s="6" t="n"/>
+      <c r="P30" s="7" t="n"/>
+      <c r="Q30" s="6" t="n"/>
+      <c r="R30" s="6" t="n"/>
+      <c r="S30" s="7" t="n"/>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>216</t>
         </is>
       </c>
     </row>
@@ -2649,12 +2645,12 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Fernando Burga</t>
+          <t>Kristin Skrabut</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>University of Minnesota</t>
+          <t>Tufts University</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -2663,28 +2659,32 @@
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>assistant 13 years after the 2013 PhD; rank start not on record</t>
+          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>Tufts University</t>
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="K31" s="3" t="n"/>
+        <v>0.18</v>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -2699,12 +2699,12 @@
       <c r="S31" s="7" t="n"/>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>427</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>428</t>
         </is>
       </c>
     </row>
@@ -2716,12 +2716,12 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Jason Jackson</t>
+          <t>Nicholas Brunet</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>University of Guelph</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -2730,26 +2730,26 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>assistant 13 years after the 2013 PhD; rank start not on record</t>
+          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Associate Professor of Political Economy</t>
+          <t>Associate Professor</t>
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>89</v>
+        <v>1560</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.22</v>
+        <v>0.88</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
@@ -2770,12 +2770,12 @@
       <c r="S32" s="7" t="n"/>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>649</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>650</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Mariana Arcaya</t>
+          <t>Sevin Yildiz</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>University of Illinois, Chicago</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -2801,32 +2801,28 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>assistant 13 years after the 2013 PhD; rank start not on record</t>
+          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Department of Urban Studies and Planning, MIT</t>
+          <t>(no Scholar profile)</t>
         </is>
       </c>
       <c r="I33" s="3" t="n">
-        <v>6062</v>
+        <v>9</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K33" s="3" t="n"/>
       <c r="L33" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -2841,12 +2837,12 @@
       <c r="S33" s="7" t="n"/>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>678</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>679</t>
         </is>
       </c>
     </row>
@@ -2858,12 +2854,12 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Roxane Lavoie</t>
+          <t>Dan Milz</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Universite Laval</t>
+          <t>University of Hawaii</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -2872,26 +2868,26 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>assistant 13 years after the 2013 PhD; rank start not on record</t>
+          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Université Laval</t>
+          <t>Department of Urban &amp; Regional Planning | Matsunaga Institute for Peace and Conflict Resolution</t>
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>394</v>
+        <v>516</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.58</v>
+        <v>0.68</v>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
@@ -2912,12 +2908,12 @@
       <c r="S34" s="7" t="n"/>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>661</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>662</t>
         </is>
       </c>
     </row>
@@ -2929,12 +2925,12 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Ryan Sandwick</t>
+          <t>Ehab Diab</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Cal Poly, San Luis Obispo</t>
+          <t>University of Saskatchewan</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
@@ -2943,28 +2939,32 @@
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>assistant 13 years after the 2013 PhD; rank start not on record</t>
+          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>Department of Geography and Planning, University of Saskatchewan</t>
         </is>
       </c>
       <c r="I35" s="3" t="n">
-        <v>1</v>
+        <v>2583</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3" t="n"/>
+        <v>0.95</v>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -2979,12 +2979,12 @@
       <c r="S35" s="7" t="n"/>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>869</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>871</t>
         </is>
       </c>
     </row>
@@ -2996,12 +2996,12 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Silvia Sarapura</t>
+          <t>Kelema Moses</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>University of Guelph</t>
+          <t>UC San Diego</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -3010,32 +3010,28 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>assistant 13 years after the 2013 PhD; rank start not on record</t>
+          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>University of Guelph</t>
+          <t>(no Scholar profile)</t>
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>545</v>
+        <v>3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K36" s="3" t="n"/>
       <c r="L36" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -3050,12 +3046,12 @@
       <c r="S36" s="7" t="n"/>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>474</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>475</t>
         </is>
       </c>
     </row>
@@ -3067,12 +3063,12 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Akira Drake Rodriguez</t>
+          <t>Mark Groulx</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>University of Pennsylvania</t>
+          <t>University of Northern British Columbia</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -3081,26 +3077,26 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
+          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>University of Pennsylvania</t>
+          <t>University of Northern British Columbia</t>
         </is>
       </c>
       <c r="I37" s="3" t="n">
-        <v>227</v>
+        <v>1631</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
@@ -3121,12 +3117,12 @@
       <c r="S37" s="7" t="n"/>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>805</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>807</t>
         </is>
       </c>
     </row>
@@ -3138,12 +3134,12 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Alberto Fuentes</t>
+          <t>Samuel Ndegeah</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>Westfield State University</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -3152,32 +3148,28 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
+          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Georgia Tech</t>
+          <t>(no Scholar profile)</t>
         </is>
       </c>
       <c r="I38" s="3" t="n">
-        <v>353</v>
+        <v>3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="K38" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -3192,12 +3184,12 @@
       <c r="S38" s="7" t="n"/>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>1039</t>
         </is>
       </c>
     </row>
@@ -3209,12 +3201,12 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Alina Gross</t>
+          <t>Shan Jiang</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Westfield State University</t>
+          <t>Tufts University</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -3223,28 +3215,32 @@
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
+          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>Tufts University</t>
         </is>
       </c>
       <c r="I39" s="3" t="n">
-        <v>82</v>
+        <v>3782</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="K39" s="3" t="n"/>
+        <v>0.98</v>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -3259,12 +3255,12 @@
       <c r="S39" s="7" t="n"/>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>424</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>425</t>
         </is>
       </c>
     </row>
@@ -3276,12 +3272,12 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Allie Thomas</t>
+          <t>Youngre Noh</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>UNC</t>
+          <t>Texas A&amp;M University</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
@@ -3290,26 +3286,26 @@
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
+          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>University of North Carolina -Chapel Hill</t>
+          <t>Assistant Professor, Texas A&amp;M University</t>
         </is>
       </c>
       <c r="I40" s="3" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
@@ -3330,12 +3326,12 @@
       <c r="S40" s="7" t="n"/>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>387</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>388</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3343,12 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Jordana Maisel</t>
+          <t>Andy Hong</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>University at Buffalo, The State University of New York</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
@@ -3361,26 +3357,26 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
+          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>University at Buffalo</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="I41" s="3" t="n">
-        <v>2470</v>
+        <v>2252</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
@@ -3401,12 +3397,12 @@
       <c r="S41" s="7" t="n"/>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>922</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>924</t>
         </is>
       </c>
     </row>
@@ -3418,12 +3414,12 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Karilyn Crockett</t>
+          <t>Cara Michell</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Northeastern University</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -3432,32 +3428,28 @@
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
+          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Professor or urban history, public policy &amp; planning</t>
+          <t>(no Scholar profile)</t>
         </is>
       </c>
       <c r="I42" s="3" t="n">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="K42" s="3" t="n"/>
       <c r="L42" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -3472,12 +3464,12 @@
       <c r="S42" s="7" t="n"/>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>263</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>264</t>
         </is>
       </c>
     </row>
@@ -3489,12 +3481,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Kristin Skrabut</t>
+          <t>Devin Bunten</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Tufts University</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -3503,26 +3495,26 @@
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
+          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Tufts University</t>
+          <t>Department of Urban Studies and Planning, MIT</t>
         </is>
       </c>
       <c r="I43" s="3" t="n">
-        <v>57</v>
+        <v>512</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.16</v>
+        <v>0.68</v>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
@@ -3543,12 +3535,12 @@
       <c r="S43" s="7" t="n"/>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>213</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>214</t>
         </is>
       </c>
     </row>
@@ -3560,12 +3552,12 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Leah Hollstein</t>
+          <t>Eli Knaap</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>University of Cincinnati</t>
+          <t>UC Irvine</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
@@ -3574,14 +3566,14 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
+          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3590,10 +3582,10 @@
         </is>
       </c>
       <c r="I44" s="3" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="K44" s="3" t="n"/>
       <c r="L44" s="5" t="inlineStr">
@@ -3610,12 +3602,12 @@
       <c r="S44" s="7" t="n"/>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>613</t>
+          <t>453</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>454</t>
         </is>
       </c>
     </row>
@@ -3627,12 +3619,12 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Martine August</t>
+          <t>Guang Tian</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>University of Waterloo, Ontario</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -3641,26 +3633,26 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
+          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>University of Waterloo</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="I45" s="3" t="n">
-        <v>2403</v>
+        <v>2630</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
@@ -3681,12 +3673,12 @@
       <c r="S45" s="7" t="n"/>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>802</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>803</t>
         </is>
       </c>
     </row>
@@ -3698,12 +3690,12 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Nicholas Brunet</t>
+          <t>Hyesun Jeong</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>University of Guelph</t>
+          <t>University of Cincinnati</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
@@ -3712,26 +3704,26 @@
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
+          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Associate Professor</t>
+          <t>University of Cincinnati</t>
         </is>
       </c>
       <c r="I46" s="3" t="n">
-        <v>1560</v>
+        <v>177</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.87</v>
+        <v>0.39</v>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
@@ -3752,12 +3744,12 @@
       <c r="S46" s="7" t="n"/>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>614</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>615</t>
         </is>
       </c>
     </row>
@@ -3769,12 +3761,12 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Revel Sims</t>
+          <t>Jessica Garrison</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>University of Wisconsin, Madison</t>
+          <t>UC Irvine</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -3783,32 +3775,28 @@
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
+          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor, University of Wisconsin-Madison</t>
+          <t>(no Scholar profile)</t>
         </is>
       </c>
       <c r="I47" s="3" t="n">
-        <v>298</v>
+        <v>137</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.33</v>
+      </c>
+      <c r="K47" s="3" t="n"/>
       <c r="L47" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -3823,12 +3811,12 @@
       <c r="S47" s="7" t="n"/>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>449</t>
         </is>
       </c>
       <c r="U47" s="3" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>450</t>
         </is>
       </c>
     </row>
@@ -3840,12 +3828,12 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Sevin Yildiz</t>
+          <t>Jose Melendez</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>University of Illinois, Chicago</t>
+          <t>University of Oregon</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -3854,28 +3842,32 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>assistant 12 years after the 2014 PhD; rank start not on record</t>
+          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>Associate Professor of Planning, School of Planning, Public Policy, and Management, University of</t>
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>9</v>
+        <v>236</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K48" s="3" t="n"/>
+        <v>0.47</v>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -3890,12 +3882,12 @@
       <c r="S48" s="7" t="n"/>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>820</t>
         </is>
       </c>
       <c r="U48" s="3" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>822</t>
         </is>
       </c>
     </row>
@@ -3907,12 +3899,12 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Dan Milz</t>
+          <t>Julia Crowley</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>University of Hawaii</t>
+          <t>University of Missouri-Kansas City</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -3921,26 +3913,26 @@
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
+          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Department of Urban &amp; Regional Planning | Matsunaga Institute for Peace and Conflict Resolution</t>
+          <t>University of Missouri-Kansas City</t>
         </is>
       </c>
       <c r="I49" s="3" t="n">
-        <v>516</v>
+        <v>294</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
@@ -3961,12 +3953,12 @@
       <c r="S49" s="7" t="n"/>
       <c r="T49" s="3" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>783</t>
         </is>
       </c>
       <c r="U49" s="3" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>784</t>
         </is>
       </c>
     </row>
@@ -3978,12 +3970,12 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Dave Guyadeen</t>
+          <t>Justin Hosbey</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>University of Guelph</t>
+          <t>UC Berkeley</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -3992,32 +3984,28 @@
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
+          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor, Rural Planning and Development, University of</t>
+          <t>(no Scholar profile)</t>
         </is>
       </c>
       <c r="I50" s="3" t="n">
-        <v>795</v>
+        <v>473</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.66</v>
+      </c>
+      <c r="K50" s="3" t="n"/>
       <c r="L50" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -4032,12 +4020,12 @@
       <c r="S50" s="7" t="n"/>
       <c r="T50" s="3" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>442</t>
         </is>
       </c>
       <c r="U50" s="3" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>443</t>
         </is>
       </c>
     </row>
@@ -4049,12 +4037,12 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Ehab Diab</t>
+          <t>Matthew Palm</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>University of Saskatchewan</t>
+          <t>UNC</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -4063,26 +4051,26 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
+          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Department of Geography and Planning, University of Saskatchewan</t>
+          <t>Assistant Professor, City and Regional Planning, UNC Chapel Hill</t>
         </is>
       </c>
       <c r="I51" s="3" t="n">
-        <v>2583</v>
+        <v>1585</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
@@ -4103,12 +4091,12 @@
       <c r="S51" s="7" t="n"/>
       <c r="T51" s="3" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>513</t>
         </is>
       </c>
       <c r="U51" s="3" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>514</t>
         </is>
       </c>
     </row>
@@ -4120,12 +4108,12 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Hun Kim</t>
+          <t>Santina Contreras</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>UC Irvine</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -4134,28 +4122,32 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
+          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>Assistant Professor of Urban Planning and Spatial Analysis, University of Southern California</t>
         </is>
       </c>
       <c r="I52" s="3" t="n">
-        <v>160</v>
+        <v>975</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K52" s="3" t="n"/>
+        <v>0.82</v>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -4170,12 +4162,12 @@
       <c r="S52" s="7" t="n"/>
       <c r="T52" s="3" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>980</t>
         </is>
       </c>
       <c r="U52" s="3" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>982</t>
         </is>
       </c>
     </row>
@@ -4187,12 +4179,12 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>John West</t>
+          <t>Subhashni Raj</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Ball State University</t>
+          <t>University of Hawaii</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -4201,28 +4193,32 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
+          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>Assistant Professor, Department of Urban and Regional Planning, University of Hawai‘i at Mānoa</t>
         </is>
       </c>
       <c r="I53" s="3" t="n">
-        <v>44</v>
+        <v>397</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="K53" s="3" t="n"/>
+        <v>0.6</v>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -4237,12 +4233,12 @@
       <c r="S53" s="7" t="n"/>
       <c r="T53" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>662</t>
         </is>
       </c>
       <c r="U53" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>663</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4250,12 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Kelema Moses</t>
+          <t>Xiaojiang Li</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>UC San Diego</t>
+          <t>University of Pennsylvania</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -4268,28 +4264,32 @@
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
+          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>University of Pennsylvania</t>
         </is>
       </c>
       <c r="I54" s="3" t="n">
-        <v>3</v>
+        <v>6134</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K54" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -4304,100 +4304,100 @@
       <c r="S54" s="7" t="n"/>
       <c r="T54" s="3" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>837</t>
         </is>
       </c>
       <c r="U54" s="3" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>839</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>Mark Groulx</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>University of Northern British Columbia</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>2015</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>University of Northern British Columbia</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="n">
-        <v>1631</v>
-      </c>
-      <c r="J55" s="3" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>Zoe Hamstead</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>UC Berkeley</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>2016</v>
+      </c>
+      <c r="F55" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Assistant Professor, University of California, Berkeley</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="n">
+        <v>5534</v>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K55" s="11" t="inlineStr">
         <is>
           <t>open profile</t>
         </is>
       </c>
-      <c r="L55" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M55" s="6" t="n"/>
-      <c r="N55" s="6" t="n"/>
-      <c r="O55" s="6" t="n"/>
-      <c r="P55" s="7" t="n"/>
-      <c r="Q55" s="6" t="n"/>
-      <c r="R55" s="6" t="n"/>
-      <c r="S55" s="7" t="n"/>
-      <c r="T55" s="3" t="inlineStr">
-        <is>
-          <t>805</t>
-        </is>
-      </c>
-      <c r="U55" s="3" t="inlineStr">
-        <is>
-          <t>807</t>
+      <c r="L55" s="11" t="inlineStr">
+        <is>
+          <t>open site</t>
+        </is>
+      </c>
+      <c r="M55" s="12" t="n"/>
+      <c r="N55" s="12" t="n"/>
+      <c r="O55" s="12" t="n"/>
+      <c r="P55" s="13" t="n"/>
+      <c r="Q55" s="12" t="n"/>
+      <c r="R55" s="12" t="n"/>
+      <c r="S55" s="13" t="n"/>
+      <c r="T55" s="9" t="inlineStr">
+        <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="U55" s="9" t="inlineStr">
+        <is>
+          <t>442</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Samuel Ndegeah</t>
+          <t>Anthony Vanky</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Westfield State University</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -4406,28 +4406,32 @@
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
+          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>Columbia University</t>
         </is>
       </c>
       <c r="I56" s="3" t="n">
-        <v>3</v>
+        <v>196</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K56" s="3" t="n"/>
+        <v>0.42</v>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -4442,29 +4446,29 @@
       <c r="S56" s="7" t="n"/>
       <c r="T56" s="3" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>68</t>
         </is>
       </c>
       <c r="U56" s="3" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Shan Jiang</t>
+          <t>Fallon Samuels Aidoo</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Tufts University</t>
+          <t>Tulane University</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -4473,26 +4477,26 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
+          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Tufts University</t>
+          <t>Tulane University School of Architecture and Built Environment</t>
         </is>
       </c>
       <c r="I57" s="3" t="n">
-        <v>3782</v>
+        <v>46</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.97</v>
+        <v>0.16</v>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
@@ -4513,29 +4517,29 @@
       <c r="S57" s="7" t="n"/>
       <c r="T57" s="3" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>428</t>
         </is>
       </c>
       <c r="U57" s="3" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>429</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Youngre Noh</t>
+          <t>John Park</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Texas A&amp;M University</t>
+          <t>University of Maryland</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -4544,32 +4548,28 @@
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>assistant 11 years after the 2015 PhD; rank start not on record</t>
+          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor, Texas A&amp;M University</t>
+          <t>(no Scholar profile)</t>
         </is>
       </c>
       <c r="I58" s="3" t="n">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.27</v>
+      </c>
+      <c r="K58" s="3" t="n"/>
       <c r="L58" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -4584,29 +4584,29 @@
       <c r="S58" s="7" t="n"/>
       <c r="T58" s="3" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>731</t>
         </is>
       </c>
       <c r="U58" s="3" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>732</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Andy Hong</t>
+          <t>Jordan Yin</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Alabama A&amp;M University</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -4615,26 +4615,26 @@
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Alabama A&amp;M University, Department of Community and Regional Planning</t>
         </is>
       </c>
       <c r="I59" s="3" t="n">
-        <v>2252</v>
+        <v>339</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.93</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
@@ -4655,29 +4655,29 @@
       <c r="S59" s="7" t="n"/>
       <c r="T59" s="3" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>6</t>
         </is>
       </c>
       <c r="U59" s="3" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Angeliz Encarnacion Burgos</t>
+          <t>Lindsay Braun</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>University of Puerto Rico</t>
+          <t>University of Illinois, Urbana-Champaign</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -4686,26 +4686,26 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor, University of Puerto Rico, Graduate School of Planning</t>
+          <t>Assistant Professor, University of Illinois at Urbana-Champaign</t>
         </is>
       </c>
       <c r="I60" s="3" t="n">
-        <v>382</v>
+        <v>1094</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.57</v>
+        <v>0.84</v>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
@@ -4726,29 +4726,29 @@
       <c r="S60" s="7" t="n"/>
       <c r="T60" s="3" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>679</t>
         </is>
       </c>
       <c r="U60" s="3" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>680</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Cara Michell</t>
+          <t>Liz Koslov</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -4757,28 +4757,32 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>University of California, Los Angeles</t>
         </is>
       </c>
       <c r="I61" s="3" t="n">
-        <v>2</v>
+        <v>841</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="K61" s="3" t="n"/>
+        <v>0.79</v>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -4793,29 +4797,29 @@
       <c r="S61" s="7" t="n"/>
       <c r="T61" s="3" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>489</t>
         </is>
       </c>
       <c r="U61" s="3" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>490</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Delia Wendel</t>
+          <t>Michelle Magalong</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>University of Maryland</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -4824,26 +4828,26 @@
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Assistant Professor of Historic Preservation, University of Maryland</t>
         </is>
       </c>
       <c r="I62" s="3" t="n">
-        <v>70</v>
+        <v>149</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.19</v>
+        <v>0.35</v>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
@@ -4864,29 +4868,29 @@
       <c r="S62" s="7" t="n"/>
       <c r="T62" s="3" t="inlineStr">
         <is>
-          <t>237</t>
+          <t>730</t>
         </is>
       </c>
       <c r="U62" s="3" t="inlineStr">
         <is>
-          <t>238</t>
+          <t>731</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Devin Bunten</t>
+          <t>Patrick Exmeyer</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>University of Louisville</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -4895,32 +4899,28 @@
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>Department of Urban Studies and Planning, MIT</t>
+          <t>(no Scholar profile)</t>
         </is>
       </c>
       <c r="I63" s="3" t="n">
-        <v>512</v>
+        <v>60</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.18</v>
+      </c>
+      <c r="K63" s="3" t="n"/>
       <c r="L63" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -4935,29 +4935,29 @@
       <c r="S63" s="7" t="n"/>
       <c r="T63" s="3" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>704</t>
         </is>
       </c>
       <c r="U63" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>705</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Eli Knaap</t>
+          <t>Rebecca Pedersen</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>UC Irvine</t>
+          <t>University of Calgary</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
@@ -4966,28 +4966,32 @@
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>Associate Professor of Electrical Engineering and Computer Science and Mat. Science &amp; Eng.</t>
         </is>
       </c>
       <c r="I64" s="3" t="n">
-        <v>68</v>
+        <v>4943</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="K64" s="3" t="n"/>
+        <v>0.98</v>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -5002,29 +5006,29 @@
       <c r="S64" s="7" t="n"/>
       <c r="T64" s="3" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>602</t>
         </is>
       </c>
       <c r="U64" s="3" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>603</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Esteban López Ochoa</t>
+          <t>Thomas Hilde</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>University of Texas, San Antonio</t>
+          <t>Cleveland State University</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -5033,26 +5037,26 @@
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor University of Texas at San Antonio</t>
+          <t>Cleveland State University</t>
         </is>
       </c>
       <c r="I65" s="3" t="n">
-        <v>335</v>
+        <v>136</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.53</v>
+        <v>0.32</v>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
@@ -5073,29 +5077,29 @@
       <c r="S65" s="7" t="n"/>
       <c r="T65" s="3" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>62</t>
         </is>
       </c>
       <c r="U65" s="3" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Guang Tian</t>
+          <t>Tyeshia Redden</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>University of Toronto</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
@@ -5104,26 +5108,26 @@
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Assistant Professor of Urban Planning, University of Toronto</t>
         </is>
       </c>
       <c r="I66" s="3" t="n">
-        <v>2630</v>
+        <v>23</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
@@ -5144,29 +5148,29 @@
       <c r="S66" s="7" t="n"/>
       <c r="T66" s="3" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>912</t>
         </is>
       </c>
       <c r="U66" s="3" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>914</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Hyesun Jeong</t>
+          <t>Andrew Guthrie</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>University of Cincinnati</t>
+          <t>University of Memphis</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -5175,26 +5179,26 @@
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>University of Cincinnati</t>
+          <t>Assistant Professor of City and Regional Planning, University of Memphis</t>
         </is>
       </c>
       <c r="I67" s="3" t="n">
-        <v>177</v>
+        <v>1228</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.38</v>
+        <v>0.86</v>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
@@ -5215,29 +5219,29 @@
       <c r="S67" s="7" t="n"/>
       <c r="T67" s="3" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>754</t>
         </is>
       </c>
       <c r="U67" s="3" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>755</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Jennifer Tucker</t>
+          <t>Behram Wali</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>University of New Mexico</t>
+          <t>UC San Diego</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -5246,32 +5250,28 @@
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor of Community and Regional Planning</t>
+          <t>(no Scholar profile)</t>
         </is>
       </c>
       <c r="I68" s="3" t="n">
-        <v>314</v>
+        <v>1820</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="K68" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.91</v>
+      </c>
+      <c r="K68" s="3" t="n"/>
       <c r="L68" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -5286,29 +5286,29 @@
       <c r="S68" s="7" t="n"/>
       <c r="T68" s="3" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>480</t>
         </is>
       </c>
       <c r="U68" s="3" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>481</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Jeremy Pittman</t>
+          <t>Ding Fei</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>University of Waterloo, Ontario</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
@@ -5317,26 +5317,26 @@
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>University of Waterloo</t>
+          <t>Assistant Professor, City and Regional Planning, Cornell University</t>
         </is>
       </c>
       <c r="I69" s="3" t="n">
-        <v>5358</v>
+        <v>863</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.98</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
@@ -5357,29 +5357,29 @@
       <c r="S69" s="7" t="n"/>
       <c r="T69" s="3" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>77</t>
         </is>
       </c>
       <c r="U69" s="3" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>77</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Jessica Garrison</t>
+          <t>Fayola Jacobs</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>UC Irvine</t>
+          <t>University of Minnesota</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
@@ -5388,28 +5388,32 @@
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>Assistant Professor at Humphrey School of Public Affairs, University of Minnesota</t>
         </is>
       </c>
       <c r="I70" s="3" t="n">
-        <v>137</v>
+        <v>381</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="K70" s="3" t="n"/>
+        <v>0.59</v>
+      </c>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -5424,29 +5428,29 @@
       <c r="S70" s="7" t="n"/>
       <c r="T70" s="3" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>778</t>
         </is>
       </c>
       <c r="U70" s="3" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>779</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Jose Melendez</t>
+          <t>Jiwnath Ghimire</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>University of Oregon</t>
+          <t>Iowa State University</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
@@ -5455,26 +5459,26 @@
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>Associate Professor of Planning, School of Planning, Public Policy, and Management, University of</t>
+          <t>Iowa State University</t>
         </is>
       </c>
       <c r="I71" s="3" t="n">
-        <v>236</v>
+        <v>365</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
@@ -5495,29 +5499,29 @@
       <c r="S71" s="7" t="n"/>
       <c r="T71" s="3" t="inlineStr">
         <is>
-          <t>820</t>
+          <t>162</t>
         </is>
       </c>
       <c r="U71" s="3" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>163</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Julia Crowley</t>
+          <t>Joel Mendez</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>University of Missouri-Kansas City</t>
+          <t>University of Kansas</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
@@ -5526,26 +5530,26 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>University of Missouri-Kansas City</t>
+          <t>Assistant Professor of Urban Planning, University of Kansas</t>
         </is>
       </c>
       <c r="I72" s="3" t="n">
-        <v>294</v>
+        <v>23</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.5</v>
+        <v>0.14</v>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
@@ -5566,29 +5570,29 @@
       <c r="S72" s="7" t="n"/>
       <c r="T72" s="3" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>701</t>
         </is>
       </c>
       <c r="U72" s="3" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>702</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Justin Hosbey</t>
+          <t>John Arroyo</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>UC Berkeley</t>
+          <t>UC San Diego</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
@@ -5597,14 +5601,14 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -5613,10 +5617,10 @@
         </is>
       </c>
       <c r="I73" s="3" t="n">
-        <v>473</v>
+        <v>114</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.63</v>
+        <v>0.28</v>
       </c>
       <c r="K73" s="3" t="n"/>
       <c r="L73" s="5" t="inlineStr">
@@ -5633,29 +5637,29 @@
       <c r="S73" s="7" t="n"/>
       <c r="T73" s="3" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>466</t>
         </is>
       </c>
       <c r="U73" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>467</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Matthew Palm</t>
+          <t>Katherine Perrott</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>UNC</t>
+          <t>University of Waterloo, Ontario</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
@@ -5664,26 +5668,26 @@
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor, City and Regional Planning, UNC Chapel Hill</t>
+          <t>University of Waterloo</t>
         </is>
       </c>
       <c r="I74" s="3" t="n">
-        <v>1585</v>
+        <v>223</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.88</v>
+        <v>0.45</v>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
@@ -5704,29 +5708,29 @@
       <c r="S74" s="7" t="n"/>
       <c r="T74" s="3" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>958</t>
         </is>
       </c>
       <c r="U74" s="3" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>960</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Maxwell Hartt</t>
+          <t>Mehdi Heris</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>Queen's University</t>
+          <t>Hunter College</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -5735,26 +5739,26 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>Queen's University</t>
+          <t>Hunter College City University of New York</t>
         </is>
       </c>
       <c r="I75" s="3" t="n">
-        <v>2123</v>
+        <v>2118</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
@@ -5775,29 +5779,29 @@
       <c r="S75" s="7" t="n"/>
       <c r="T75" s="3" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>150</t>
         </is>
       </c>
       <c r="U75" s="3" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>151</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Santina Contreras</t>
+          <t>Minjee Kim</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -5806,26 +5810,26 @@
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor of Urban Planning and Spatial Analysis, University of Southern California</t>
+          <t>UCLA</t>
         </is>
       </c>
       <c r="I76" s="3" t="n">
-        <v>975</v>
+        <v>277</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
@@ -5846,29 +5850,29 @@
       <c r="S76" s="7" t="n"/>
       <c r="T76" s="3" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>488</t>
         </is>
       </c>
       <c r="U76" s="3" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>489</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Subhashni Raj</t>
+          <t>Nemoy Lewis</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>University of Hawaii</t>
+          <t>Toronto Metropolitan University</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
@@ -5877,26 +5881,26 @@
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor, Department of Urban and Regional Planning, University of Hawai‘i at Mānoa</t>
+          <t>Toronto Metropolitan University</t>
         </is>
       </c>
       <c r="I77" s="3" t="n">
-        <v>397</v>
+        <v>98</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>0.58</v>
+        <v>0.26</v>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
@@ -5917,29 +5921,29 @@
       <c r="S77" s="7" t="n"/>
       <c r="T77" s="3" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>409</t>
         </is>
       </c>
       <c r="U77" s="3" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>410</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Xiaojiang Li</t>
+          <t>Ricardo Cardoso</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>University of Pennsylvania</t>
+          <t>Ohio State University</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -5948,26 +5952,26 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>University of Pennsylvania</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
       <c r="I78" s="3" t="n">
-        <v>6134</v>
+        <v>197</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
@@ -5988,24 +5992,24 @@
       <c r="S78" s="7" t="n"/>
       <c r="T78" s="3" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>278</t>
         </is>
       </c>
       <c r="U78" s="3" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>279</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Yang Song</t>
+          <t>Xinyu Fu</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -6019,14 +6023,14 @@
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
+          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6035,10 +6039,10 @@
         </is>
       </c>
       <c r="I79" s="3" t="n">
-        <v>1210</v>
+        <v>1480</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
@@ -6059,83 +6063,79 @@
       <c r="S79" s="7" t="n"/>
       <c r="T79" s="3" t="inlineStr">
         <is>
-          <t>391</t>
+          <t>378</t>
         </is>
       </c>
       <c r="U79" s="3" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>379</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>Zoe Hamstead</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>UC Berkeley</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E80" s="9" t="n">
-        <v>2016</v>
-      </c>
-      <c r="F80" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G80" s="10" t="inlineStr">
-        <is>
-          <t>assistant 10 years after the 2016 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H80" s="10" t="inlineStr">
-        <is>
-          <t>Assistant Professor, University of California, Berkeley</t>
-        </is>
-      </c>
-      <c r="I80" s="9" t="n">
-        <v>5534</v>
-      </c>
-      <c r="J80" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="K80" s="11" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L80" s="11" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M80" s="12" t="n"/>
-      <c r="N80" s="12" t="n"/>
-      <c r="O80" s="12" t="n"/>
-      <c r="P80" s="13" t="n"/>
-      <c r="Q80" s="12" t="n"/>
-      <c r="R80" s="12" t="n"/>
-      <c r="S80" s="13" t="n"/>
-      <c r="T80" s="9" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="U80" s="9" t="inlineStr">
-        <is>
-          <t>442</t>
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Yemi Adediji</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Toronto Metropolitan University</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>assistant</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>(no Scholar profile)</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K80" s="3" t="n"/>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>open site</t>
+        </is>
+      </c>
+      <c r="M80" s="6" t="n"/>
+      <c r="N80" s="6" t="n"/>
+      <c r="O80" s="6" t="n"/>
+      <c r="P80" s="7" t="n"/>
+      <c r="Q80" s="6" t="n"/>
+      <c r="R80" s="6" t="n"/>
+      <c r="S80" s="7" t="n"/>
+      <c r="T80" s="3" t="inlineStr">
+        <is>
+          <t>406</t>
+        </is>
+      </c>
+      <c r="U80" s="3" t="inlineStr">
+        <is>
+          <t>407</t>
         </is>
       </c>
     </row>
@@ -6147,12 +6147,12 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Anthony Vanky</t>
+          <t>Zachary Lamb</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>UC Berkeley</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -6161,26 +6161,26 @@
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>Columbia University</t>
+          <t>Assistant Professor of City and Regional Planning, UC Berkeley</t>
         </is>
       </c>
       <c r="I81" s="3" t="n">
-        <v>196</v>
+        <v>2141</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.41</v>
+        <v>0.93</v>
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
@@ -6201,12 +6201,12 @@
       <c r="S81" s="7" t="n"/>
       <c r="T81" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>443</t>
         </is>
       </c>
       <c r="U81" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>444</t>
         </is>
       </c>
     </row>
@@ -6218,12 +6218,12 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Emmanuel Boamah</t>
+          <t>Andrea Restrepo-Mieth</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>University at Buffalo, The State University of New York</t>
+          <t>Rutgers University</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -6232,26 +6232,26 @@
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>University at Buffalo, The State University of New York</t>
+          <t>Assistant Professor, Rutgers University</t>
         </is>
       </c>
       <c r="I82" s="3" t="n">
-        <v>1462</v>
+        <v>126</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>0.86</v>
+        <v>0.3</v>
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
@@ -6272,12 +6272,12 @@
       <c r="S82" s="7" t="n"/>
       <c r="T82" s="3" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>332</t>
         </is>
       </c>
       <c r="U82" s="3" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>333</t>
         </is>
       </c>
     </row>
@@ -6289,12 +6289,12 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Fallon Samuels Aidoo</t>
+          <t>Andrew Guinn</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Tulane University</t>
+          <t>Wayne State University</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -6303,26 +6303,26 @@
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>Tulane University School of Architecture and Built Environment</t>
+          <t>Assistant Professor of Urban Studies and Planning, Wayne State University</t>
         </is>
       </c>
       <c r="I83" s="3" t="n">
-        <v>46</v>
+        <v>642</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.13</v>
+        <v>0.75</v>
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
@@ -6343,12 +6343,12 @@
       <c r="S83" s="7" t="n"/>
       <c r="T83" s="3" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="U83" s="3" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>1019</t>
         </is>
       </c>
     </row>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Geoff Boeing</t>
+          <t>Ariadna Reyes-Sanchez</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>University of Texas, Arlington</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -6374,26 +6374,26 @@
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>University of Texas at Arlington</t>
         </is>
       </c>
       <c r="I84" s="3" t="n">
-        <v>7944</v>
+        <v>256</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>1</v>
+        <v>0.49</v>
       </c>
       <c r="K84" s="5" t="inlineStr">
         <is>
@@ -6414,12 +6414,12 @@
       <c r="S84" s="7" t="n"/>
       <c r="T84" s="3" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>882</t>
         </is>
       </c>
       <c r="U84" s="3" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>884</t>
         </is>
       </c>
     </row>
@@ -6431,12 +6431,12 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>John Park</t>
+          <t>Caroline Collins</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>UC San Diego</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -6445,14 +6445,14 @@
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6461,10 +6461,10 @@
         </is>
       </c>
       <c r="I85" s="3" t="n">
-        <v>105</v>
+        <v>141</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="K85" s="3" t="n"/>
       <c r="L85" s="5" t="inlineStr">
@@ -6481,12 +6481,12 @@
       <c r="S85" s="7" t="n"/>
       <c r="T85" s="3" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>468</t>
         </is>
       </c>
       <c r="U85" s="3" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>469</t>
         </is>
       </c>
     </row>
@@ -6498,12 +6498,12 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Jongwoong Kim</t>
+          <t>Christine Wen</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>West Chester University</t>
+          <t>Toronto Metropolitan University</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -6512,28 +6512,32 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>Assistant Professor, Toronto Metropolitan University</t>
         </is>
       </c>
       <c r="I86" s="3" t="n">
-        <v>9</v>
+        <v>128</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K86" s="3" t="n"/>
+        <v>0.31</v>
+      </c>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -6548,12 +6552,12 @@
       <c r="S86" s="7" t="n"/>
       <c r="T86" s="3" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>418</t>
         </is>
       </c>
       <c r="U86" s="3" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>419</t>
         </is>
       </c>
     </row>
@@ -6565,12 +6569,12 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Jordan Yin</t>
+          <t>Cleary Larkin</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Alabama A&amp;M University</t>
+          <t>University of Florida</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -6579,32 +6583,28 @@
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Alabama A&amp;M University, Department of Community and Regional Planning</t>
+          <t>(no Scholar profile)</t>
         </is>
       </c>
       <c r="I87" s="3" t="n">
-        <v>339</v>
+        <v>1</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="K87" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="K87" s="3" t="n"/>
       <c r="L87" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -6619,12 +6619,12 @@
       <c r="S87" s="7" t="n"/>
       <c r="T87" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>634</t>
         </is>
       </c>
       <c r="U87" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>635</t>
         </is>
       </c>
     </row>
@@ -6636,12 +6636,12 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Linda Shi</t>
+          <t>Deepti Chatti</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>UC San Diego</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -6650,32 +6650,28 @@
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Cornell Department of City and Regional Planning</t>
+          <t>(no Scholar profile)</t>
         </is>
       </c>
       <c r="I88" s="3" t="n">
-        <v>3749</v>
+        <v>194</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="K88" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="K88" s="3" t="n"/>
       <c r="L88" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -6690,12 +6686,12 @@
       <c r="S88" s="7" t="n"/>
       <c r="T88" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>467</t>
         </is>
       </c>
       <c r="U88" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>468</t>
         </is>
       </c>
     </row>
@@ -6707,12 +6703,12 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Lindsay Braun</t>
+          <t>Emily Grisé</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>University of Illinois, Urbana-Champaign</t>
+          <t>University of Alberta</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
@@ -6721,26 +6717,26 @@
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor, University of Illinois at Urbana-Champaign</t>
+          <t>University of Alberta School of Urban &amp; Regional Planning</t>
         </is>
       </c>
       <c r="I89" s="3" t="n">
-        <v>1094</v>
+        <v>1345</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
@@ -6761,12 +6757,12 @@
       <c r="S89" s="7" t="n"/>
       <c r="T89" s="3" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>571</t>
         </is>
       </c>
       <c r="U89" s="3" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>572</t>
         </is>
       </c>
     </row>
@@ -6778,12 +6774,12 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Liz Koslov</t>
+          <t>Hannah Teicher</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>UCLA</t>
+          <t>Harvard University</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
@@ -6792,26 +6788,26 @@
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles</t>
+          <t>Assistant Professor, Harvard University Graduate School of Design</t>
         </is>
       </c>
       <c r="I90" s="3" t="n">
-        <v>841</v>
+        <v>1248</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
@@ -6832,12 +6828,12 @@
       <c r="S90" s="7" t="n"/>
       <c r="T90" s="3" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>143</t>
         </is>
       </c>
       <c r="U90" s="3" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>144</t>
         </is>
       </c>
     </row>
@@ -6849,12 +6845,12 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Michelle Magalong</t>
+          <t>Hassaan Furqan Khan</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>University of Maryland</t>
+          <t>Tufts University</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
@@ -6863,14 +6859,14 @@
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -6879,16 +6875,12 @@
         </is>
       </c>
       <c r="I91" s="3" t="n">
-        <v>133</v>
+        <v>425</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K91" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.62</v>
+      </c>
+      <c r="K91" s="3" t="n"/>
       <c r="L91" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -6903,12 +6895,12 @@
       <c r="S91" s="7" t="n"/>
       <c r="T91" s="3" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>425</t>
         </is>
       </c>
       <c r="U91" s="3" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>426</t>
         </is>
       </c>
     </row>
@@ -6920,12 +6912,12 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>Patrick Exmeyer</t>
+          <t>Jamaal Green</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>University of Louisville</t>
+          <t>University of Pennsylvania</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -6934,28 +6926,32 @@
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>University of Pennsylvania</t>
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>60</v>
+        <v>576</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K92" s="3" t="n"/>
+        <v>0.72</v>
+      </c>
+      <c r="K92" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -6970,12 +6966,12 @@
       <c r="S92" s="7" t="n"/>
       <c r="T92" s="3" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>834</t>
         </is>
       </c>
       <c r="U92" s="3" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>836</t>
         </is>
       </c>
     </row>
@@ -6987,12 +6983,12 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>Rebecca Pedersen</t>
+          <t>Kelly Gregg</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>University of Calgary</t>
+          <t>University at Buffalo, The State University of New York</t>
         </is>
       </c>
       <c r="D93" s="3" t="inlineStr">
@@ -7001,26 +6997,26 @@
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>Associate Professor of Electrical Engineering and Computer Science and Mat. Science &amp; Eng.</t>
+          <t>Assistant Professor Department of Urban and Regional Planning at University at Buffalo</t>
         </is>
       </c>
       <c r="I93" s="3" t="n">
-        <v>4943</v>
+        <v>291</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>0.98</v>
+        <v>0.52</v>
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
@@ -7041,12 +7037,12 @@
       <c r="S93" s="7" t="n"/>
       <c r="T93" s="3" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>550</t>
         </is>
       </c>
       <c r="U93" s="3" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>551</t>
         </is>
       </c>
     </row>
@@ -7058,12 +7054,12 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>Steven Gehrke</t>
+          <t>Lauren Fischer</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>Northern Arizona University</t>
+          <t>University at Buffalo, The State University of New York</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
@@ -7072,26 +7068,26 @@
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Northern Arizona University</t>
+          <t>University at Buffalo, School of Architecture and Planning</t>
         </is>
       </c>
       <c r="I94" s="3" t="n">
-        <v>1580</v>
+        <v>454</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>0.87</v>
+        <v>0.65</v>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
@@ -7112,12 +7108,12 @@
       <c r="S94" s="7" t="n"/>
       <c r="T94" s="3" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>549</t>
         </is>
       </c>
       <c r="U94" s="3" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>550</t>
         </is>
       </c>
     </row>
@@ -7129,12 +7125,12 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Thomas Hilde</t>
+          <t>Maggie Low</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Cleveland State University</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
@@ -7143,32 +7139,28 @@
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>Cleveland State University</t>
+          <t>(no Scholar profile)</t>
         </is>
       </c>
       <c r="I95" s="3" t="n">
-        <v>136</v>
+        <v>13</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="K95" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
+        <v>0.09</v>
+      </c>
+      <c r="K95" s="3" t="n"/>
       <c r="L95" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -7183,12 +7175,12 @@
       <c r="S95" s="7" t="n"/>
       <c r="T95" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>597</t>
         </is>
       </c>
       <c r="U95" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>598</t>
         </is>
       </c>
     </row>
@@ -7200,12 +7192,12 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Tim Ross</t>
+          <t>Patrick Cooper-McCann</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>University of Toronto</t>
+          <t>Wayne State University</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
@@ -7214,26 +7206,26 @@
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>Assistant Professor, Wayne State University</t>
         </is>
       </c>
       <c r="I96" s="3" t="n">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
@@ -7254,12 +7246,12 @@
       <c r="S96" s="7" t="n"/>
       <c r="T96" s="3" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="U96" s="3" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>1018</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7263,12 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Tyeshia Redden</t>
+          <t>Rylan Graham</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>University of Toronto</t>
+          <t>University of Northern British Columbia</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
@@ -7285,26 +7277,26 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>assistant 9 years after the 2017 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor of Urban Planning, University of Toronto</t>
+          <t>University of Northern British Columbia</t>
         </is>
       </c>
       <c r="I97" s="3" t="n">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
       <c r="K97" s="5" t="inlineStr">
         <is>
@@ -7325,12 +7317,12 @@
       <c r="S97" s="7" t="n"/>
       <c r="T97" s="3" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>804</t>
         </is>
       </c>
       <c r="U97" s="3" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>806</t>
         </is>
       </c>
     </row>
@@ -7342,12 +7334,12 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Andrew Guthrie</t>
+          <t>Shruti Syal</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>University of Memphis</t>
+          <t>Virginia Commonwealth University</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
@@ -7356,26 +7348,26 @@
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor of City and Regional Planning, University of Memphis</t>
+          <t>Virginia Commonwealth University</t>
         </is>
       </c>
       <c r="I98" s="3" t="n">
-        <v>1228</v>
+        <v>98</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>0.84</v>
+        <v>0.26</v>
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
@@ -7396,12 +7388,12 @@
       <c r="S98" s="7" t="n"/>
       <c r="T98" s="3" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="U98" s="3" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>1002</t>
         </is>
       </c>
     </row>
@@ -7413,12 +7405,12 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Aujean Lee</t>
+          <t>Stephen Kofi Diko</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>University of Memphis</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
@@ -7427,26 +7419,26 @@
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>Assistant Professor, University of Utah</t>
+          <t>University of Memphis</t>
         </is>
       </c>
       <c r="I99" s="3" t="n">
-        <v>482</v>
+        <v>843</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.64</v>
+        <v>0.8</v>
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
@@ -7467,12 +7459,12 @@
       <c r="S99" s="7" t="n"/>
       <c r="T99" s="3" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>753</t>
         </is>
       </c>
       <c r="U99" s="3" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>754</t>
         </is>
       </c>
     </row>
@@ -7484,12 +7476,12 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Behram Wali</t>
+          <t>Youjung Kim</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>UC San Diego</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
@@ -7498,28 +7490,32 @@
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
+          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>(no Scholar profile)</t>
+          <t>University of South Florida</t>
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>1820</v>
+        <v>426</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="K100" s="3" t="n"/>
+        <v>0.62</v>
+      </c>
+      <c r="K100" s="5" t="inlineStr">
+        <is>
+          <t>open profile</t>
+        </is>
+      </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
           <t>open site</t>
@@ -7534,2827 +7530,19 @@
       <c r="S100" s="7" t="n"/>
       <c r="T100" s="3" t="inlineStr">
         <is>
-          <t>480</t>
+          <t>874</t>
         </is>
       </c>
       <c r="U100" s="3" t="inlineStr">
         <is>
-          <t>481</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>Camille Barchers</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>University of Massachusetts-Amherst</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G101" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="inlineStr">
-        <is>
-          <t>University of Massachusetts</t>
-        </is>
-      </c>
-      <c r="I101" s="3" t="n">
-        <v>174</v>
-      </c>
-      <c r="J101" s="3" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="K101" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L101" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M101" s="6" t="n"/>
-      <c r="N101" s="6" t="n"/>
-      <c r="O101" s="6" t="n"/>
-      <c r="P101" s="7" t="n"/>
-      <c r="Q101" s="6" t="n"/>
-      <c r="R101" s="6" t="n"/>
-      <c r="S101" s="7" t="n"/>
-      <c r="T101" s="3" t="inlineStr">
-        <is>
-          <t>733</t>
-        </is>
-      </c>
-      <c r="U101" s="3" t="inlineStr">
-        <is>
-          <t>734</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>Daniel Kuhlmann</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>University of Arizona</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F102" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G102" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>Assistant Professor, University of Arizona</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="n">
-        <v>231</v>
-      </c>
-      <c r="J102" s="3" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="K102" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L102" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M102" s="6" t="n"/>
-      <c r="N102" s="6" t="n"/>
-      <c r="O102" s="6" t="n"/>
-      <c r="P102" s="7" t="n"/>
-      <c r="Q102" s="6" t="n"/>
-      <c r="R102" s="6" t="n"/>
-      <c r="S102" s="7" t="n"/>
-      <c r="T102" s="3" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="U102" s="3" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>Ding Fei</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>Cornell University</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G103" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H103" s="4" t="inlineStr">
-        <is>
-          <t>Assistant Professor, City and Regional Planning, Cornell University</t>
-        </is>
-      </c>
-      <c r="I103" s="3" t="n">
-        <v>863</v>
-      </c>
-      <c r="J103" s="3" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="K103" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L103" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M103" s="6" t="n"/>
-      <c r="N103" s="6" t="n"/>
-      <c r="O103" s="6" t="n"/>
-      <c r="P103" s="7" t="n"/>
-      <c r="Q103" s="6" t="n"/>
-      <c r="R103" s="6" t="n"/>
-      <c r="S103" s="7" t="n"/>
-      <c r="T103" s="3" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="U103" s="3" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>Fayola Jacobs</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>University of Minnesota</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G104" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>Assistant Professor at Humphrey School of Public Affairs, University of Minnesota</t>
-        </is>
-      </c>
-      <c r="I104" s="3" t="n">
-        <v>381</v>
-      </c>
-      <c r="J104" s="3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="K104" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L104" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M104" s="6" t="n"/>
-      <c r="N104" s="6" t="n"/>
-      <c r="O104" s="6" t="n"/>
-      <c r="P104" s="7" t="n"/>
-      <c r="Q104" s="6" t="n"/>
-      <c r="R104" s="6" t="n"/>
-      <c r="S104" s="7" t="n"/>
-      <c r="T104" s="3" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
-      <c r="U104" s="3" t="inlineStr">
-        <is>
-          <t>779</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>Jiwnath Ghimire</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>Iowa State University</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F105" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G105" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t>Iowa State University</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="n">
-        <v>365</v>
-      </c>
-      <c r="J105" s="3" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="K105" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L105" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M105" s="6" t="n"/>
-      <c r="N105" s="6" t="n"/>
-      <c r="O105" s="6" t="n"/>
-      <c r="P105" s="7" t="n"/>
-      <c r="Q105" s="6" t="n"/>
-      <c r="R105" s="6" t="n"/>
-      <c r="S105" s="7" t="n"/>
-      <c r="T105" s="3" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="U105" s="3" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>Joel Mendez</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>University of Kansas</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F106" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G106" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>Assistant Professor of Urban Planning, University of Kansas</t>
-        </is>
-      </c>
-      <c r="I106" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="J106" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K106" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L106" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M106" s="6" t="n"/>
-      <c r="N106" s="6" t="n"/>
-      <c r="O106" s="6" t="n"/>
-      <c r="P106" s="7" t="n"/>
-      <c r="Q106" s="6" t="n"/>
-      <c r="R106" s="6" t="n"/>
-      <c r="S106" s="7" t="n"/>
-      <c r="T106" s="3" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="U106" s="3" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>John Arroyo</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>UC San Diego</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G107" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H107" s="4" t="inlineStr">
-        <is>
-          <t>(no Scholar profile)</t>
-        </is>
-      </c>
-      <c r="I107" s="3" t="n">
-        <v>114</v>
-      </c>
-      <c r="J107" s="3" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="K107" s="3" t="n"/>
-      <c r="L107" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M107" s="6" t="n"/>
-      <c r="N107" s="6" t="n"/>
-      <c r="O107" s="6" t="n"/>
-      <c r="P107" s="7" t="n"/>
-      <c r="Q107" s="6" t="n"/>
-      <c r="R107" s="6" t="n"/>
-      <c r="S107" s="7" t="n"/>
-      <c r="T107" s="3" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="U107" s="3" t="inlineStr">
-        <is>
-          <t>467</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>Katherine Perrott</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>University of Waterloo, Ontario</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F108" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G108" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H108" s="4" t="inlineStr">
-        <is>
-          <t>University of Waterloo</t>
-        </is>
-      </c>
-      <c r="I108" s="3" t="n">
-        <v>223</v>
-      </c>
-      <c r="J108" s="3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="K108" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L108" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M108" s="6" t="n"/>
-      <c r="N108" s="6" t="n"/>
-      <c r="O108" s="6" t="n"/>
-      <c r="P108" s="7" t="n"/>
-      <c r="Q108" s="6" t="n"/>
-      <c r="R108" s="6" t="n"/>
-      <c r="S108" s="7" t="n"/>
-      <c r="T108" s="3" t="inlineStr">
-        <is>
-          <t>958</t>
-        </is>
-      </c>
-      <c r="U108" s="3" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>Mehdi Heris</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>Hunter College</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F109" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G109" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H109" s="4" t="inlineStr">
-        <is>
-          <t>Hunter College City University of New York</t>
-        </is>
-      </c>
-      <c r="I109" s="3" t="n">
-        <v>2118</v>
-      </c>
-      <c r="J109" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K109" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L109" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M109" s="6" t="n"/>
-      <c r="N109" s="6" t="n"/>
-      <c r="O109" s="6" t="n"/>
-      <c r="P109" s="7" t="n"/>
-      <c r="Q109" s="6" t="n"/>
-      <c r="R109" s="6" t="n"/>
-      <c r="S109" s="7" t="n"/>
-      <c r="T109" s="3" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="U109" s="3" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>Minjee Kim</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>UCLA</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G110" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H110" s="4" t="inlineStr">
-        <is>
-          <t>UCLA</t>
-        </is>
-      </c>
-      <c r="I110" s="3" t="n">
-        <v>277</v>
-      </c>
-      <c r="J110" s="3" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="K110" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L110" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M110" s="6" t="n"/>
-      <c r="N110" s="6" t="n"/>
-      <c r="O110" s="6" t="n"/>
-      <c r="P110" s="7" t="n"/>
-      <c r="Q110" s="6" t="n"/>
-      <c r="R110" s="6" t="n"/>
-      <c r="S110" s="7" t="n"/>
-      <c r="T110" s="3" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
-      </c>
-      <c r="U110" s="3" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>Miriam Solis</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>University of Texas, Austin</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F111" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G111" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H111" s="4" t="inlineStr">
-        <is>
-          <t>University of Texas at Austin</t>
-        </is>
-      </c>
-      <c r="I111" s="3" t="n">
-        <v>153</v>
-      </c>
-      <c r="J111" s="3" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="K111" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L111" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M111" s="6" t="n"/>
-      <c r="N111" s="6" t="n"/>
-      <c r="O111" s="6" t="n"/>
-      <c r="P111" s="7" t="n"/>
-      <c r="Q111" s="6" t="n"/>
-      <c r="R111" s="6" t="n"/>
-      <c r="S111" s="7" t="n"/>
-      <c r="T111" s="3" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="U111" s="3" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>Nemoy Lewis</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>Toronto Metropolitan University</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F112" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G112" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H112" s="4" t="inlineStr">
-        <is>
-          <t>Toronto Metropolitan University</t>
-        </is>
-      </c>
-      <c r="I112" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="J112" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K112" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L112" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M112" s="6" t="n"/>
-      <c r="N112" s="6" t="n"/>
-      <c r="O112" s="6" t="n"/>
-      <c r="P112" s="7" t="n"/>
-      <c r="Q112" s="6" t="n"/>
-      <c r="R112" s="6" t="n"/>
-      <c r="S112" s="7" t="n"/>
-      <c r="T112" s="3" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="U112" s="3" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>Ricardo Cardoso</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>Ohio State University</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F113" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G113" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H113" s="4" t="inlineStr">
-        <is>
-          <t>The Ohio State University</t>
-        </is>
-      </c>
-      <c r="I113" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="J113" s="3" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="K113" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L113" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M113" s="6" t="n"/>
-      <c r="N113" s="6" t="n"/>
-      <c r="O113" s="6" t="n"/>
-      <c r="P113" s="7" t="n"/>
-      <c r="Q113" s="6" t="n"/>
-      <c r="R113" s="6" t="n"/>
-      <c r="S113" s="7" t="n"/>
-      <c r="T113" s="3" t="inlineStr">
-        <is>
-          <t>278</t>
-        </is>
-      </c>
-      <c r="U113" s="3" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>Sara Epp</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>University of Guelph</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F114" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G114" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H114" s="4" t="inlineStr">
-        <is>
-          <t>(no Scholar profile)</t>
-        </is>
-      </c>
-      <c r="I114" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="J114" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="K114" s="3" t="n"/>
-      <c r="L114" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M114" s="6" t="n"/>
-      <c r="N114" s="6" t="n"/>
-      <c r="O114" s="6" t="n"/>
-      <c r="P114" s="7" t="n"/>
-      <c r="Q114" s="6" t="n"/>
-      <c r="R114" s="6" t="n"/>
-      <c r="S114" s="7" t="n"/>
-      <c r="T114" s="3" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="U114" s="3" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>Sungmin Lee</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>Texas A&amp;M University</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F115" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H115" s="4" t="inlineStr">
-        <is>
-          <t>Texas A&amp;M University</t>
-        </is>
-      </c>
-      <c r="I115" s="3" t="n">
-        <v>981</v>
-      </c>
-      <c r="J115" s="3" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="K115" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L115" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M115" s="6" t="n"/>
-      <c r="N115" s="6" t="n"/>
-      <c r="O115" s="6" t="n"/>
-      <c r="P115" s="7" t="n"/>
-      <c r="Q115" s="6" t="n"/>
-      <c r="R115" s="6" t="n"/>
-      <c r="S115" s="7" t="n"/>
-      <c r="T115" s="3" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="U115" s="3" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>Xinyu Fu</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>Texas A&amp;M University</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F116" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G116" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H116" s="4" t="inlineStr">
-        <is>
-          <t>Texas A&amp;M University</t>
-        </is>
-      </c>
-      <c r="I116" s="3" t="n">
-        <v>1480</v>
-      </c>
-      <c r="J116" s="3" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="K116" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L116" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M116" s="6" t="n"/>
-      <c r="N116" s="6" t="n"/>
-      <c r="O116" s="6" t="n"/>
-      <c r="P116" s="7" t="n"/>
-      <c r="Q116" s="6" t="n"/>
-      <c r="R116" s="6" t="n"/>
-      <c r="S116" s="7" t="n"/>
-      <c r="T116" s="3" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="U116" s="3" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>Yemi Adediji</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>Toronto Metropolitan University</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F117" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H117" s="4" t="inlineStr">
-        <is>
-          <t>(no Scholar profile)</t>
-        </is>
-      </c>
-      <c r="I117" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="J117" s="3" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K117" s="3" t="n"/>
-      <c r="L117" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M117" s="6" t="n"/>
-      <c r="N117" s="6" t="n"/>
-      <c r="O117" s="6" t="n"/>
-      <c r="P117" s="7" t="n"/>
-      <c r="Q117" s="6" t="n"/>
-      <c r="R117" s="6" t="n"/>
-      <c r="S117" s="7" t="n"/>
-      <c r="T117" s="3" t="inlineStr">
-        <is>
-          <t>406</t>
-        </is>
-      </c>
-      <c r="U117" s="3" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>Zachary Lamb</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>UC Berkeley</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F118" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="G118" s="4" t="inlineStr">
-        <is>
-          <t>assistant 8 years after the 2018 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H118" s="4" t="inlineStr">
-        <is>
-          <t>Assistant Professor of City and Regional Planning, UC Berkeley</t>
-        </is>
-      </c>
-      <c r="I118" s="3" t="n">
-        <v>2141</v>
-      </c>
-      <c r="J118" s="3" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="K118" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L118" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M118" s="6" t="n"/>
-      <c r="N118" s="6" t="n"/>
-      <c r="O118" s="6" t="n"/>
-      <c r="P118" s="7" t="n"/>
-      <c r="Q118" s="6" t="n"/>
-      <c r="R118" s="6" t="n"/>
-      <c r="S118" s="7" t="n"/>
-      <c r="T118" s="3" t="inlineStr">
-        <is>
-          <t>443</t>
-        </is>
-      </c>
-      <c r="U118" s="3" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>Alejandra Reyes</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>UC Irvine</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F119" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G119" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H119" s="4" t="inlineStr">
-        <is>
-          <t>University of California, Irvine</t>
-        </is>
-      </c>
-      <c r="I119" s="3" t="n">
-        <v>234</v>
-      </c>
-      <c r="J119" s="3" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K119" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L119" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M119" s="6" t="n"/>
-      <c r="N119" s="6" t="n"/>
-      <c r="O119" s="6" t="n"/>
-      <c r="P119" s="7" t="n"/>
-      <c r="Q119" s="6" t="n"/>
-      <c r="R119" s="6" t="n"/>
-      <c r="S119" s="7" t="n"/>
-      <c r="T119" s="3" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="U119" s="3" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>Andrea Restrepo-Mieth</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>Rutgers University</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F120" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G120" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H120" s="4" t="inlineStr">
-        <is>
-          <t>Assistant Professor, Rutgers University</t>
-        </is>
-      </c>
-      <c r="I120" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J120" s="3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="K120" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L120" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M120" s="6" t="n"/>
-      <c r="N120" s="6" t="n"/>
-      <c r="O120" s="6" t="n"/>
-      <c r="P120" s="7" t="n"/>
-      <c r="Q120" s="6" t="n"/>
-      <c r="R120" s="6" t="n"/>
-      <c r="S120" s="7" t="n"/>
-      <c r="T120" s="3" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="U120" s="3" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>Andrew Guinn</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>Wayne State University</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F121" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G121" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H121" s="4" t="inlineStr">
-        <is>
-          <t>Assistant Professor of Urban Studies and Planning, Wayne State University</t>
-        </is>
-      </c>
-      <c r="I121" s="3" t="n">
-        <v>642</v>
-      </c>
-      <c r="J121" s="3" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="K121" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L121" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M121" s="6" t="n"/>
-      <c r="N121" s="6" t="n"/>
-      <c r="O121" s="6" t="n"/>
-      <c r="P121" s="7" t="n"/>
-      <c r="Q121" s="6" t="n"/>
-      <c r="R121" s="6" t="n"/>
-      <c r="S121" s="7" t="n"/>
-      <c r="T121" s="3" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="U121" s="3" t="inlineStr">
-        <is>
-          <t>1019</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>Ariadna Reyes-Sanchez</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>University of Texas, Arlington</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F122" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G122" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H122" s="4" t="inlineStr">
-        <is>
-          <t>University of Texas at Arlington</t>
-        </is>
-      </c>
-      <c r="I122" s="3" t="n">
-        <v>256</v>
-      </c>
-      <c r="J122" s="3" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="K122" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L122" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M122" s="6" t="n"/>
-      <c r="N122" s="6" t="n"/>
-      <c r="O122" s="6" t="n"/>
-      <c r="P122" s="7" t="n"/>
-      <c r="Q122" s="6" t="n"/>
-      <c r="R122" s="6" t="n"/>
-      <c r="S122" s="7" t="n"/>
-      <c r="T122" s="3" t="inlineStr">
-        <is>
-          <t>882</t>
-        </is>
-      </c>
-      <c r="U122" s="3" t="inlineStr">
-        <is>
-          <t>884</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>Caroline Collins</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>UC San Diego</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G123" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H123" s="4" t="inlineStr">
-        <is>
-          <t>(no Scholar profile)</t>
-        </is>
-      </c>
-      <c r="I123" s="3" t="n">
-        <v>141</v>
-      </c>
-      <c r="J123" s="3" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="K123" s="3" t="n"/>
-      <c r="L123" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M123" s="6" t="n"/>
-      <c r="N123" s="6" t="n"/>
-      <c r="O123" s="6" t="n"/>
-      <c r="P123" s="7" t="n"/>
-      <c r="Q123" s="6" t="n"/>
-      <c r="R123" s="6" t="n"/>
-      <c r="S123" s="7" t="n"/>
-      <c r="T123" s="3" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-      <c r="U123" s="3" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>Christine Wen</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>Toronto Metropolitan University</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F124" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G124" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>Assistant Professor, Toronto Metropolitan University</t>
-        </is>
-      </c>
-      <c r="I124" s="3" t="n">
-        <v>128</v>
-      </c>
-      <c r="J124" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K124" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L124" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M124" s="6" t="n"/>
-      <c r="N124" s="6" t="n"/>
-      <c r="O124" s="6" t="n"/>
-      <c r="P124" s="7" t="n"/>
-      <c r="Q124" s="6" t="n"/>
-      <c r="R124" s="6" t="n"/>
-      <c r="S124" s="7" t="n"/>
-      <c r="T124" s="3" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
-      </c>
-      <c r="U124" s="3" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>Cleary Larkin</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>University of Florida</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F125" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G125" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H125" s="4" t="inlineStr">
-        <is>
-          <t>(no Scholar profile)</t>
-        </is>
-      </c>
-      <c r="I125" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J125" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K125" s="3" t="n"/>
-      <c r="L125" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M125" s="6" t="n"/>
-      <c r="N125" s="6" t="n"/>
-      <c r="O125" s="6" t="n"/>
-      <c r="P125" s="7" t="n"/>
-      <c r="Q125" s="6" t="n"/>
-      <c r="R125" s="6" t="n"/>
-      <c r="S125" s="7" t="n"/>
-      <c r="T125" s="3" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="U125" s="3" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>Deepti Chatti</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>UC San Diego</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G126" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H126" s="4" t="inlineStr">
-        <is>
-          <t>(no Scholar profile)</t>
-        </is>
-      </c>
-      <c r="I126" s="3" t="n">
-        <v>194</v>
-      </c>
-      <c r="J126" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K126" s="3" t="n"/>
-      <c r="L126" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M126" s="6" t="n"/>
-      <c r="N126" s="6" t="n"/>
-      <c r="O126" s="6" t="n"/>
-      <c r="P126" s="7" t="n"/>
-      <c r="Q126" s="6" t="n"/>
-      <c r="R126" s="6" t="n"/>
-      <c r="S126" s="7" t="n"/>
-      <c r="T126" s="3" t="inlineStr">
-        <is>
-          <t>467</t>
-        </is>
-      </c>
-      <c r="U126" s="3" t="inlineStr">
-        <is>
-          <t>468</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>Emily Grisé</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>University of Alberta</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F127" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G127" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H127" s="4" t="inlineStr">
-        <is>
-          <t>University of Alberta School of Urban &amp; Regional Planning</t>
-        </is>
-      </c>
-      <c r="I127" s="3" t="n">
-        <v>1345</v>
-      </c>
-      <c r="J127" s="3" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K127" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L127" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M127" s="6" t="n"/>
-      <c r="N127" s="6" t="n"/>
-      <c r="O127" s="6" t="n"/>
-      <c r="P127" s="7" t="n"/>
-      <c r="Q127" s="6" t="n"/>
-      <c r="R127" s="6" t="n"/>
-      <c r="S127" s="7" t="n"/>
-      <c r="T127" s="3" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="U127" s="3" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>Hannah Teicher</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>Harvard University</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F128" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G128" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H128" s="4" t="inlineStr">
-        <is>
-          <t>Assistant Professor, Harvard University Graduate School of Design</t>
-        </is>
-      </c>
-      <c r="I128" s="3" t="n">
-        <v>1248</v>
-      </c>
-      <c r="J128" s="3" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="K128" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L128" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M128" s="6" t="n"/>
-      <c r="N128" s="6" t="n"/>
-      <c r="O128" s="6" t="n"/>
-      <c r="P128" s="7" t="n"/>
-      <c r="Q128" s="6" t="n"/>
-      <c r="R128" s="6" t="n"/>
-      <c r="S128" s="7" t="n"/>
-      <c r="T128" s="3" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="U128" s="3" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>Hassaan Furqan Khan</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>Tufts University</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F129" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G129" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H129" s="4" t="inlineStr">
-        <is>
-          <t>(no Scholar profile)</t>
-        </is>
-      </c>
-      <c r="I129" s="3" t="n">
-        <v>425</v>
-      </c>
-      <c r="J129" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K129" s="3" t="n"/>
-      <c r="L129" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M129" s="6" t="n"/>
-      <c r="N129" s="6" t="n"/>
-      <c r="O129" s="6" t="n"/>
-      <c r="P129" s="7" t="n"/>
-      <c r="Q129" s="6" t="n"/>
-      <c r="R129" s="6" t="n"/>
-      <c r="S129" s="7" t="n"/>
-      <c r="T129" s="3" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="U129" s="3" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>Hayden Shelby</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>University of Cincinnati</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G130" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H130" s="4" t="inlineStr">
-        <is>
-          <t>University of Cincinnati</t>
-        </is>
-      </c>
-      <c r="I130" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="J130" s="3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="K130" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L130" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M130" s="6" t="n"/>
-      <c r="N130" s="6" t="n"/>
-      <c r="O130" s="6" t="n"/>
-      <c r="P130" s="7" t="n"/>
-      <c r="Q130" s="6" t="n"/>
-      <c r="R130" s="6" t="n"/>
-      <c r="S130" s="7" t="n"/>
-      <c r="T130" s="3" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="U130" s="3" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>Jamaal Green</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>University of Pennsylvania</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F131" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G131" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H131" s="4" t="inlineStr">
-        <is>
-          <t>University of Pennsylvania</t>
-        </is>
-      </c>
-      <c r="I131" s="3" t="n">
-        <v>576</v>
-      </c>
-      <c r="J131" s="3" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="K131" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L131" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M131" s="6" t="n"/>
-      <c r="N131" s="6" t="n"/>
-      <c r="O131" s="6" t="n"/>
-      <c r="P131" s="7" t="n"/>
-      <c r="Q131" s="6" t="n"/>
-      <c r="R131" s="6" t="n"/>
-      <c r="S131" s="7" t="n"/>
-      <c r="T131" s="3" t="inlineStr">
-        <is>
-          <t>834</t>
-        </is>
-      </c>
-      <c r="U131" s="3" t="inlineStr">
-        <is>
-          <t>836</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>Kelly Gregg</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>University at Buffalo, The State University of New York</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F132" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G132" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="inlineStr">
-        <is>
-          <t>Assistant Professor Department of Urban and Regional Planning at University at Buffalo</t>
-        </is>
-      </c>
-      <c r="I132" s="3" t="n">
-        <v>291</v>
-      </c>
-      <c r="J132" s="3" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="K132" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L132" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M132" s="6" t="n"/>
-      <c r="N132" s="6" t="n"/>
-      <c r="O132" s="6" t="n"/>
-      <c r="P132" s="7" t="n"/>
-      <c r="Q132" s="6" t="n"/>
-      <c r="R132" s="6" t="n"/>
-      <c r="S132" s="7" t="n"/>
-      <c r="T132" s="3" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="U132" s="3" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>Lauren Fischer</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>University at Buffalo, The State University of New York</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F133" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G133" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H133" s="4" t="inlineStr">
-        <is>
-          <t>University at Buffalo, School of Architecture and Planning</t>
-        </is>
-      </c>
-      <c r="I133" s="3" t="n">
-        <v>454</v>
-      </c>
-      <c r="J133" s="3" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="K133" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L133" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M133" s="6" t="n"/>
-      <c r="N133" s="6" t="n"/>
-      <c r="O133" s="6" t="n"/>
-      <c r="P133" s="7" t="n"/>
-      <c r="Q133" s="6" t="n"/>
-      <c r="R133" s="6" t="n"/>
-      <c r="S133" s="7" t="n"/>
-      <c r="T133" s="3" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="U133" s="3" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>Maggie Low</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>University of British Columbia</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F134" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G134" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H134" s="4" t="inlineStr">
-        <is>
-          <t>(no Scholar profile)</t>
-        </is>
-      </c>
-      <c r="I134" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="J134" s="3" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K134" s="3" t="n"/>
-      <c r="L134" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M134" s="6" t="n"/>
-      <c r="N134" s="6" t="n"/>
-      <c r="O134" s="6" t="n"/>
-      <c r="P134" s="7" t="n"/>
-      <c r="Q134" s="6" t="n"/>
-      <c r="R134" s="6" t="n"/>
-      <c r="S134" s="7" t="n"/>
-      <c r="T134" s="3" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="U134" s="3" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>Miyuki Hino</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>UNC</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F135" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G135" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H135" s="4" t="inlineStr">
-        <is>
-          <t>University of North Carolina at Chapel Hill</t>
-        </is>
-      </c>
-      <c r="I135" s="3" t="n">
-        <v>2858</v>
-      </c>
-      <c r="J135" s="3" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K135" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L135" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M135" s="6" t="n"/>
-      <c r="N135" s="6" t="n"/>
-      <c r="O135" s="6" t="n"/>
-      <c r="P135" s="7" t="n"/>
-      <c r="Q135" s="6" t="n"/>
-      <c r="R135" s="6" t="n"/>
-      <c r="S135" s="7" t="n"/>
-      <c r="T135" s="3" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="U135" s="3" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>Patrick Cooper-McCann</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>Wayne State University</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F136" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G136" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H136" s="4" t="inlineStr">
-        <is>
-          <t>Assistant Professor, Wayne State University</t>
-        </is>
-      </c>
-      <c r="I136" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="J136" s="3" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="K136" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L136" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M136" s="6" t="n"/>
-      <c r="N136" s="6" t="n"/>
-      <c r="O136" s="6" t="n"/>
-      <c r="P136" s="7" t="n"/>
-      <c r="Q136" s="6" t="n"/>
-      <c r="R136" s="6" t="n"/>
-      <c r="S136" s="7" t="n"/>
-      <c r="T136" s="3" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="U136" s="3" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>Rylan Graham</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>University of Northern British Columbia</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F137" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G137" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H137" s="4" t="inlineStr">
-        <is>
-          <t>University of Northern British Columbia</t>
-        </is>
-      </c>
-      <c r="I137" s="3" t="n">
-        <v>116</v>
-      </c>
-      <c r="J137" s="3" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="K137" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L137" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M137" s="6" t="n"/>
-      <c r="N137" s="6" t="n"/>
-      <c r="O137" s="6" t="n"/>
-      <c r="P137" s="7" t="n"/>
-      <c r="Q137" s="6" t="n"/>
-      <c r="R137" s="6" t="n"/>
-      <c r="S137" s="7" t="n"/>
-      <c r="T137" s="3" t="inlineStr">
-        <is>
-          <t>804</t>
-        </is>
-      </c>
-      <c r="U137" s="3" t="inlineStr">
-        <is>
-          <t>806</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>Shruti Syal</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>Virginia Commonwealth University</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F138" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G138" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H138" s="4" t="inlineStr">
-        <is>
-          <t>Virginia Commonwealth University</t>
-        </is>
-      </c>
-      <c r="I138" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="J138" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K138" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L138" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M138" s="6" t="n"/>
-      <c r="N138" s="6" t="n"/>
-      <c r="O138" s="6" t="n"/>
-      <c r="P138" s="7" t="n"/>
-      <c r="Q138" s="6" t="n"/>
-      <c r="R138" s="6" t="n"/>
-      <c r="S138" s="7" t="n"/>
-      <c r="T138" s="3" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="U138" s="3" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>Stephen Kofi Diko</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>University of Memphis</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F139" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G139" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H139" s="4" t="inlineStr">
-        <is>
-          <t>University of Memphis</t>
-        </is>
-      </c>
-      <c r="I139" s="3" t="n">
-        <v>843</v>
-      </c>
-      <c r="J139" s="3" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="K139" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L139" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M139" s="6" t="n"/>
-      <c r="N139" s="6" t="n"/>
-      <c r="O139" s="6" t="n"/>
-      <c r="P139" s="7" t="n"/>
-      <c r="Q139" s="6" t="n"/>
-      <c r="R139" s="6" t="n"/>
-      <c r="S139" s="7" t="n"/>
-      <c r="T139" s="3" t="inlineStr">
-        <is>
-          <t>753</t>
-        </is>
-      </c>
-      <c r="U139" s="3" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>Youjung Kim</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>University of South Florida</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>assistant</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F140" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G140" s="4" t="inlineStr">
-        <is>
-          <t>assistant 7 years after the 2019 PhD; rank start not on record</t>
-        </is>
-      </c>
-      <c r="H140" s="4" t="inlineStr">
-        <is>
-          <t>University of South Florida</t>
-        </is>
-      </c>
-      <c r="I140" s="3" t="n">
-        <v>426</v>
-      </c>
-      <c r="J140" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K140" s="5" t="inlineStr">
-        <is>
-          <t>open profile</t>
-        </is>
-      </c>
-      <c r="L140" s="5" t="inlineStr">
-        <is>
-          <t>open site</t>
-        </is>
-      </c>
-      <c r="M140" s="6" t="n"/>
-      <c r="N140" s="6" t="n"/>
-      <c r="O140" s="6" t="n"/>
-      <c r="P140" s="7" t="n"/>
-      <c r="Q140" s="6" t="n"/>
-      <c r="R140" s="6" t="n"/>
-      <c r="S140" s="7" t="n"/>
-      <c r="T140" s="3" t="inlineStr">
-        <is>
-          <t>874</t>
-        </is>
-      </c>
-      <c r="U140" s="3" t="inlineStr">
-        <is>
           <t>876</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U140"/>
+  <autoFilter ref="A1:U100"/>
   <dataValidations count="1">
-    <dataValidation sqref="M2 M3 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 M46 M47 M48 M49 M50 M51 M52 M53 M54 M55 M56 M57 M58 M59 M60 M61 M62 M63 M64 M65 M66 M67 M68 M69 M70 M71 M72 M73 M74 M75 M76 M77 M78 M79 M80 M81 M82 M83 M84 M85 M86 M87 M88 M89 M90 M91 M92 M93 M94 M95 M96 M97 M98 M99 M100 M101 M102 M103 M104 M105 M106 M107 M108 M109 M110 M111 M112 M113 M114 M115 M116 M117 M118 M119 M120 M121 M122 M123 M124 M125 M126 M127 M128 M129 M130 M131 M132 M133 M134 M135 M136 M137 M138 M139 M140" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Actual rank" prompt="What the program website or profile shows today. Leave blank to decide later." type="list">
+    <dataValidation sqref="M2 M3 M4 M5 M6 M7 M8 M9 M10 M11 M12 M13 M14 M15 M16 M17 M18 M19 M20 M21 M22 M23 M24 M25 M26 M27 M28 M29 M30 M31 M32 M33 M34 M35 M36 M37 M38 M39 M40 M41 M42 M43 M44 M45 M46 M47 M48 M49 M50 M51 M52 M53 M54 M55 M56 M57 M58 M59 M60 M61 M62 M63 M64 M65 M66 M67 M68 M69 M70 M71 M72 M73 M74 M75 M76 M77 M78 M79 M80 M81 M82 M83 M84 M85 M86 M87 M88 M89 M90 M91 M92 M93 M94 M95 M96 M97 M98 M99 M100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Actual rank" prompt="What the program website or profile shows today. Leave blank to decide later." type="list">
       <formula1>"assistant,associate,full,emeritus,adjunct or lecturer,left the program,unclear"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10380,120 +7568,120 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K14" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K17" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K29" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K30" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K31" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K35" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K36" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K42" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K37" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K41" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K43" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K52" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K53" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K54" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K55" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K58" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K56" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K57" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K59" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K60" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K63" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K61" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K62" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K68" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K64" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K65" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K66" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K67" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K69" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K80" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K70" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K71" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K72" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K74" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K75" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K76" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K77" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K78" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K79" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K81" r:id="rId137"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId138"/>
@@ -10504,105 +7692,32 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K84" r:id="rId143"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K87" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K86" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId147"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K88" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K91" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K95" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K101" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K102" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K103" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K108" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K109" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K110" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L110" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K111" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L111" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K112" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L112" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K113" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L113" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L114" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K115" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L115" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K116" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L116" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L117" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K118" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L118" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K119" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L119" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K120" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L120" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K121" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L121" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K122" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L122" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L123" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K124" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L124" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L125" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L126" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K127" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L127" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K128" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L128" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L129" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K130" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L130" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K131" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L131" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K132" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L132" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K133" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L133" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L134" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K135" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L135" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K136" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L136" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K137" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L137" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K138" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L138" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K139" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L139" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K140" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L140" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K89" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K90" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K92" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K93" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K94" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K96" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K97" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K98" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K99" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K100" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId171"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10630,7 +7745,7 @@
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>139 faculty we hold as assistant or associate professor who have been at that rank for 7 years or more, or look that way. The site updates a rank only when a person's own Google Scholar profile states one, and many profiles never do, so promotions get missed. Most of these ranks came from a hand-kept spreadsheet and some are years out of date.</t>
+          <t>99 faculty we hold as assistant or associate professor who have been at that rank for 7 years or more, or look that way. The site updates a rank only when a person's own Google Scholar profile states one, and many profiles never do, so promotions get missed. Most of these ranks came from a hand-kept spreadsheet and some are years out of date.</t>
         </is>
       </c>
     </row>

--- a/data/review/rank_review.xlsx
+++ b/data/review/rank_review.xlsx
@@ -659,7 +659,7 @@
         <v>4</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="K2" s="3" t="n"/>
       <c r="L2" s="5" t="inlineStr">
@@ -726,7 +726,7 @@
         <v>84</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="5" t="inlineStr">
@@ -793,7 +793,7 @@
         <v>388</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="5" t="inlineStr">
@@ -860,7 +860,7 @@
         <v>118</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="5" t="inlineStr">
@@ -927,7 +927,7 @@
         <v>60</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="5" t="inlineStr">
@@ -994,7 +994,7 @@
         <v>1180</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>477</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>1207</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>859</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>615</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>437</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
@@ -1562,7 +1562,7 @@
         <v>603</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="K15" s="3" t="n"/>
       <c r="L15" s="5" t="inlineStr">
@@ -1629,7 +1629,7 @@
         <v>1843</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>518</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>561</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>1041</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="K19" s="3" t="n"/>
       <c r="L19" s="5" t="inlineStr">
@@ -1909,7 +1909,7 @@
         <v>1077</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>1457</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
         <v>394</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>227</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>82</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="K27" s="3" t="n"/>
       <c r="L27" s="5" t="inlineStr">
@@ -2465,7 +2465,7 @@
         <v>160</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>78</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>57</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
@@ -2749,7 +2749,7 @@
         <v>1560</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>516</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>3</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="K36" s="3" t="n"/>
       <c r="L36" s="5" t="inlineStr">
@@ -3096,7 +3096,7 @@
         <v>1631</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="5" t="inlineStr">
@@ -3305,7 +3305,7 @@
         <v>155</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>512</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         <v>177</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>137</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="K47" s="3" t="n"/>
       <c r="L47" s="5" t="inlineStr">
@@ -3861,7 +3861,7 @@
         <v>236</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>294</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>473</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="K50" s="3" t="n"/>
       <c r="L50" s="5" t="inlineStr">
@@ -4141,7 +4141,7 @@
         <v>975</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>397</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>196</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
@@ -4496,7 +4496,7 @@
         <v>46</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>105</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="K58" s="3" t="n"/>
       <c r="L58" s="5" t="inlineStr">
@@ -4634,7 +4634,7 @@
         <v>339</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>1094</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>841</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
@@ -4847,7 +4847,7 @@
         <v>149</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>60</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="K63" s="3" t="n"/>
       <c r="L63" s="5" t="inlineStr">
@@ -5056,7 +5056,7 @@
         <v>136</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
         <v>1228</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>863</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         <v>381</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>365</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>114</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="K73" s="3" t="n"/>
       <c r="L73" s="5" t="inlineStr">
@@ -5687,7 +5687,7 @@
         <v>223</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>277</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>98</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>197</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         <v>126</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>642</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>256</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="K84" s="5" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>141</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="K85" s="3" t="n"/>
       <c r="L85" s="5" t="inlineStr">
@@ -6531,7 +6531,7 @@
         <v>128</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="K86" s="5" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>194</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="K88" s="3" t="n"/>
       <c r="L88" s="5" t="inlineStr">
@@ -6736,7 +6736,7 @@
         <v>1345</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>1248</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>425</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="K91" s="3" t="n"/>
       <c r="L91" s="5" t="inlineStr">
@@ -6945,7 +6945,7 @@
         <v>576</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="K92" s="5" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
         <v>291</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>454</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>13</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="K95" s="3" t="n"/>
       <c r="L95" s="5" t="inlineStr">
@@ -7225,7 +7225,7 @@
         <v>73</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>116</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="K97" s="5" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>98</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
@@ -7438,7 +7438,7 @@
         <v>843</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>426</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="K100" s="5" t="inlineStr">
         <is>
